--- a/datos.xlsx
+++ b/datos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANGELA\Desktop\MiDashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANGELA\Desktop\MiDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE861265-14CB-4D09-ADB2-D3C2493142CC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A95609-A5CA-4F35-B4DB-4BF3FA9C1646}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="7470" windowHeight="8640" tabRatio="906" xr2:uid="{7D6B2630-CDD6-4E4F-8803-3B7521F27F6B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="97">
   <si>
     <t>N° DE OPERACIÓN</t>
   </si>
@@ -311,6 +311,12 @@
   <si>
     <t xml:space="preserve">Peso Neto Importado </t>
   </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peso Neto Manejado </t>
+  </si>
 </sst>
 </file>
 
@@ -319,7 +325,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -348,8 +354,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -368,8 +382,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor theme="6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -377,11 +397,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -409,6 +444,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -424,6 +461,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -433,7 +471,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -474,13 +511,13 @@
   <autoFilter ref="A1:I366" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{8E80F481-58A9-4EF5-9BD3-4DE99E71B7AE}" name="N° DE OPERACIÓN"/>
-    <tableColumn id="5" xr3:uid="{59A9AB34-6356-455A-B8FD-E74723C9892D}" name="FECHA" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{59A9AB34-6356-455A-B8FD-E74723C9892D}" name="FECHA" dataDxfId="7" totalsRowDxfId="3"/>
     <tableColumn id="6" xr3:uid="{66D4B823-3C30-44D5-A641-20D7BF6E166A}" name="TIPO DE CARGA"/>
     <tableColumn id="7" xr3:uid="{C3650C10-5CB4-45A7-9736-6A80A51D6F83}" name="TIPO DE SERVICIO"/>
-    <tableColumn id="15" xr3:uid="{99B5645B-5CD8-4042-833E-BE48D00BC86E}" name="LLENOS RECIBIDOS (EXPORTADOS)" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{99B5645B-5CD8-4042-833E-BE48D00BC86E}" name="LLENOS RECIBIDOS (EXPORTADOS)" dataDxfId="6" totalsRowDxfId="2"/>
     <tableColumn id="18" xr3:uid="{33E6F7D3-8F24-4F60-BCE9-4590974B7832}" name="CONTENIDO"/>
-    <tableColumn id="21" xr3:uid="{D64B384B-46A0-483C-8C32-5474495F7791}" name="Peso Neto Exportado" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="22" xr3:uid="{CD599142-04A2-4632-8A98-CA3F9CF4F273}" name="DESTINO " dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="21" xr3:uid="{D64B384B-46A0-483C-8C32-5474495F7791}" name="Peso Neto Exportado" dataDxfId="5" totalsRowDxfId="1"/>
+    <tableColumn id="22" xr3:uid="{CD599142-04A2-4632-8A98-CA3F9CF4F273}" name="DESTINO " dataDxfId="4" totalsRowDxfId="0"/>
     <tableColumn id="23" xr3:uid="{2EDED6B6-E583-4F20-89DA-9AA2F9B82EE1}" name="Peso Neto Importado "/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -804,7 +841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C559613-914B-4B50-8C5B-99B98A1D93DC}">
-  <dimension ref="A1:I366"/>
+  <dimension ref="A1:J366"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -816,9 +853,10 @@
     <col min="7" max="7" width="16.75" style="2" customWidth="1"/>
     <col min="8" max="8" width="32" style="2" customWidth="1"/>
     <col min="9" max="9" width="19.375" customWidth="1"/>
+    <col min="10" max="10" width="21.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24" customHeight="1">
+    <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -846,8 +884,11 @@
       <c r="I1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="24" customHeight="1">
+      <c r="J1" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="24" customHeight="1">
       <c r="A2">
         <v>1</v>
       </c>
@@ -875,8 +916,11 @@
       <c r="I2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J2" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="19.5" customHeight="1">
       <c r="A3">
         <v>2</v>
       </c>
@@ -904,8 +948,11 @@
       <c r="I3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J3" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="20.25" customHeight="1">
       <c r="A4">
         <v>3</v>
       </c>
@@ -933,8 +980,11 @@
       <c r="I4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J4" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="24.75" customHeight="1">
       <c r="A5">
         <v>4</v>
       </c>
@@ -962,8 +1012,11 @@
       <c r="I5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J5" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="21.75" customHeight="1">
       <c r="A6">
         <v>5</v>
       </c>
@@ -991,8 +1044,11 @@
       <c r="I6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J6" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1020,8 +1076,11 @@
       <c r="I7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="18" customHeight="1">
+      <c r="J7" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="18" customHeight="1">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1049,8 +1108,11 @@
       <c r="I8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="27" customHeight="1">
+      <c r="J8" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="27" customHeight="1">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1078,8 +1140,11 @@
       <c r="I9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="29.25" customHeight="1">
+      <c r="J9" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="29.25" customHeight="1">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1107,8 +1172,11 @@
       <c r="I10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J10" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="24.75" customHeight="1">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1136,8 +1204,11 @@
       <c r="I11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J11" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1165,8 +1236,11 @@
       <c r="I12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J12" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="22.5" customHeight="1">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1194,8 +1268,11 @@
       <c r="I13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J13" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="21.75" customHeight="1">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1223,8 +1300,11 @@
       <c r="I14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="29.25" customHeight="1">
+      <c r="J14" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="29.25" customHeight="1">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1252,8 +1332,11 @@
       <c r="I15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="18.75" customHeight="1">
+      <c r="J15" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="18.75" customHeight="1">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1281,8 +1364,11 @@
       <c r="I16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J16" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="21.75" customHeight="1">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1310,8 +1396,11 @@
       <c r="I17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J17" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="23.25" customHeight="1">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1339,8 +1428,11 @@
       <c r="I18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="24" customHeight="1">
+      <c r="J18" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="24" customHeight="1">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1368,8 +1460,11 @@
       <c r="I19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J19" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="22.5" customHeight="1">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1397,8 +1492,11 @@
       <c r="I20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J20" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1426,8 +1524,11 @@
       <c r="I21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="24" customHeight="1">
+      <c r="J21" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="24" customHeight="1">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1455,8 +1556,11 @@
       <c r="I22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J22" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="23.25" customHeight="1">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1484,8 +1588,11 @@
       <c r="I23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="27" customHeight="1">
+      <c r="J23" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="27" customHeight="1">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1513,8 +1620,11 @@
       <c r="I24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1">
+      <c r="J24" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1542,8 +1652,11 @@
       <c r="I25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J25" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="13.5" customHeight="1">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1571,8 +1684,11 @@
       <c r="I26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="14.25" customHeight="1">
+      <c r="J26" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="14.25" customHeight="1">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1600,8 +1716,11 @@
       <c r="I27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" ht="18.75" customHeight="1">
+      <c r="J27" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="18.75" customHeight="1">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1629,8 +1748,11 @@
       <c r="I28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J28" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="20.25" customHeight="1">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1658,8 +1780,11 @@
       <c r="I29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" ht="27.75" customHeight="1">
+      <c r="J29" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="27.75" customHeight="1">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1687,8 +1812,11 @@
       <c r="I30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="27" customHeight="1">
+      <c r="J30" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="27" customHeight="1">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1716,8 +1844,11 @@
       <c r="I31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J31" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="19.5" customHeight="1">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1745,8 +1876,11 @@
       <c r="I32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" ht="17.25" customHeight="1">
+      <c r="J32" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="17.25" customHeight="1">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1774,8 +1908,11 @@
       <c r="I33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:9">
+      <c r="J33" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1803,8 +1940,11 @@
       <c r="I34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" ht="14.25" customHeight="1">
+      <c r="J34" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="14.25" customHeight="1">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1832,8 +1972,11 @@
       <c r="I35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J35" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="20.25" customHeight="1">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1861,8 +2004,11 @@
       <c r="I36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:9">
+      <c r="J36" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1890,8 +2036,11 @@
       <c r="I37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:9">
+      <c r="J37" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1919,8 +2068,11 @@
       <c r="I38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:9">
+      <c r="J38" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1948,8 +2100,11 @@
       <c r="I39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:9">
+      <c r="J39" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1977,8 +2132,11 @@
       <c r="I40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:9">
+      <c r="J40" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2006,8 +2164,11 @@
       <c r="I41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:9">
+      <c r="J41" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2035,8 +2196,11 @@
       <c r="I42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:9">
+      <c r="J42" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2064,8 +2228,11 @@
       <c r="I43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:9">
+      <c r="J43" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2093,8 +2260,11 @@
       <c r="I44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:9">
+      <c r="J44" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2122,8 +2292,11 @@
       <c r="I45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" ht="15" customHeight="1">
+      <c r="J45" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15" customHeight="1">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2151,8 +2324,11 @@
       <c r="I46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J46" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="20.25" customHeight="1">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2180,8 +2356,11 @@
       <c r="I47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" ht="18.75" customHeight="1">
+      <c r="J47" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="18.75" customHeight="1">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2209,8 +2388,11 @@
       <c r="I48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J48" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="24.75" customHeight="1">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2238,8 +2420,11 @@
       <c r="I49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J49" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="22.5" customHeight="1">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2267,8 +2452,11 @@
       <c r="I50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" ht="24" customHeight="1">
+      <c r="J50" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="24" customHeight="1">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2296,8 +2484,11 @@
       <c r="I51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J51" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="15.75" customHeight="1">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2325,8 +2516,11 @@
       <c r="I52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" ht="17.25" customHeight="1">
+      <c r="J52" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="17.25" customHeight="1">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2354,8 +2548,11 @@
       <c r="I53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" ht="27" customHeight="1">
+      <c r="J53" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="27" customHeight="1">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2383,8 +2580,11 @@
       <c r="I54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J54" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="24.75" customHeight="1">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2412,8 +2612,11 @@
       <c r="I55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J55" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="26.25" customHeight="1">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2441,8 +2644,11 @@
       <c r="I56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" ht="34.5" customHeight="1">
+      <c r="J56" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="34.5" customHeight="1">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2470,8 +2676,11 @@
       <c r="I57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" ht="29.25" customHeight="1">
+      <c r="J57" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="29.25" customHeight="1">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2499,8 +2708,11 @@
       <c r="I58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" ht="34.5" customHeight="1">
+      <c r="J58" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="34.5" customHeight="1">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2528,8 +2740,11 @@
       <c r="I59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" ht="24" customHeight="1">
+      <c r="J59" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="24" customHeight="1">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2557,8 +2772,11 @@
       <c r="I60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" ht="24" customHeight="1">
+      <c r="J60" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="24" customHeight="1">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2586,8 +2804,11 @@
       <c r="I61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" ht="31.5" customHeight="1">
+      <c r="J61" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="31.5" customHeight="1">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2615,8 +2836,11 @@
       <c r="I62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" ht="36.75" customHeight="1">
+      <c r="J62" s="12">
+        <v>26250</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="36.75" customHeight="1">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2644,8 +2868,11 @@
       <c r="I63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J63" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="26.25" customHeight="1">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2673,8 +2900,11 @@
       <c r="I64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" ht="38.25" customHeight="1">
+      <c r="J64" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="38.25" customHeight="1">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2702,8 +2932,11 @@
       <c r="I65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J65" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="24.75" customHeight="1">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2731,8 +2964,11 @@
       <c r="I66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" ht="29.25" customHeight="1">
+      <c r="J66" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="29.25" customHeight="1">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2760,8 +2996,11 @@
       <c r="I67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" ht="45.75" customHeight="1">
+      <c r="J67" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="45.75" customHeight="1">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2789,8 +3028,11 @@
       <c r="I68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" ht="36" customHeight="1">
+      <c r="J68" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="36" customHeight="1">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2818,8 +3060,11 @@
       <c r="I69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:9">
+      <c r="J69" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2847,8 +3092,11 @@
       <c r="I70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" ht="18" customHeight="1">
+      <c r="J70" s="12">
+        <v>22500</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="18" customHeight="1">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2876,8 +3124,11 @@
       <c r="I71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" ht="18.75" customHeight="1">
+      <c r="J71" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="18.75" customHeight="1">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2905,8 +3156,11 @@
       <c r="I72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" ht="15" customHeight="1">
+      <c r="J72" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="15" customHeight="1">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2934,8 +3188,11 @@
       <c r="I73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J73" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="20.25" customHeight="1">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2963,8 +3220,11 @@
       <c r="I74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" ht="30" customHeight="1">
+      <c r="J74" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="30" customHeight="1">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2992,8 +3252,11 @@
       <c r="I75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J75" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="23.25" customHeight="1">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3021,8 +3284,11 @@
       <c r="I76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J76" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="26.25" customHeight="1">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3050,8 +3316,11 @@
       <c r="I77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J77" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="26.25" customHeight="1">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3079,8 +3348,11 @@
       <c r="I78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:9" ht="32.25" customHeight="1">
+      <c r="J78" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="32.25" customHeight="1">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3108,8 +3380,11 @@
       <c r="I79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J79" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="26.25" customHeight="1">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3137,8 +3412,11 @@
       <c r="I80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" ht="31.5" customHeight="1">
+      <c r="J80" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="31.5" customHeight="1">
       <c r="A81">
         <v>80</v>
       </c>
@@ -3166,8 +3444,11 @@
       <c r="I81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" ht="33.75" customHeight="1">
+      <c r="J81" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="33.75" customHeight="1">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3195,8 +3476,11 @@
       <c r="I82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J82" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="24.75" customHeight="1">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3224,8 +3508,11 @@
       <c r="I83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J83" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="24.75" customHeight="1">
       <c r="A84">
         <v>83</v>
       </c>
@@ -3253,8 +3540,11 @@
       <c r="I84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J84" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="22.5" customHeight="1">
       <c r="A85">
         <v>84</v>
       </c>
@@ -3282,8 +3572,11 @@
       <c r="I85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" ht="27" customHeight="1">
+      <c r="J85" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="27" customHeight="1">
       <c r="A86">
         <v>85</v>
       </c>
@@ -3311,8 +3604,11 @@
       <c r="I86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J86" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="22.5" customHeight="1">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3340,8 +3636,11 @@
       <c r="I87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J87" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="19.5" customHeight="1">
       <c r="A88">
         <v>87</v>
       </c>
@@ -3369,8 +3668,11 @@
       <c r="I88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J88" s="12">
+        <v>26250</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="19.5" customHeight="1">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3398,8 +3700,11 @@
       <c r="I89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J89" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="24.75" customHeight="1">
       <c r="A90">
         <v>89</v>
       </c>
@@ -3427,8 +3732,11 @@
       <c r="I90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" ht="32.25" customHeight="1">
+      <c r="J90" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="32.25" customHeight="1">
       <c r="A91">
         <v>90</v>
       </c>
@@ -3456,8 +3764,11 @@
       <c r="I91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:9" ht="24" customHeight="1">
+      <c r="J91" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="24" customHeight="1">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3485,8 +3796,11 @@
       <c r="I92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J92" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="21.75" customHeight="1">
       <c r="A93">
         <v>92</v>
       </c>
@@ -3514,8 +3828,11 @@
       <c r="I93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J93" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="13.5" customHeight="1">
       <c r="A94">
         <v>93</v>
       </c>
@@ -3543,8 +3860,11 @@
       <c r="I94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J94" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="19.5" customHeight="1">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3572,8 +3892,11 @@
       <c r="I95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" ht="37.5" customHeight="1">
+      <c r="J95" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="37.5" customHeight="1">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3601,8 +3924,11 @@
       <c r="I96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J96" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="20.25" customHeight="1">
       <c r="A97">
         <v>96</v>
       </c>
@@ -3630,8 +3956,11 @@
       <c r="I97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J97" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="24.75" customHeight="1">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3659,8 +3988,11 @@
       <c r="I98">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J98" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="22.5" customHeight="1">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3688,8 +4020,11 @@
       <c r="I99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J99" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="23.25" customHeight="1">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3717,8 +4052,11 @@
       <c r="I100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:9" ht="36" customHeight="1">
+      <c r="J100" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="36" customHeight="1">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3746,8 +4084,11 @@
       <c r="I101">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:9" ht="24" customHeight="1">
+      <c r="J101" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="24" customHeight="1">
       <c r="A102">
         <v>101</v>
       </c>
@@ -3775,8 +4116,11 @@
       <c r="I102">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:9" ht="27.75" customHeight="1">
+      <c r="J102" s="12">
+        <v>41250</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="27.75" customHeight="1">
       <c r="A103">
         <v>102</v>
       </c>
@@ -3804,8 +4148,11 @@
       <c r="I103">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:9" ht="27.75" customHeight="1">
+      <c r="J103" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="27.75" customHeight="1">
       <c r="A104">
         <v>103</v>
       </c>
@@ -3833,8 +4180,11 @@
       <c r="I104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J104" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="21.75" customHeight="1">
       <c r="A105">
         <v>104</v>
       </c>
@@ -3862,8 +4212,11 @@
       <c r="I105">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J105" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="22.5" customHeight="1">
       <c r="A106">
         <v>105</v>
       </c>
@@ -3891,8 +4244,11 @@
       <c r="I106">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J106" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="22.5" customHeight="1">
       <c r="A107">
         <v>106</v>
       </c>
@@ -3920,8 +4276,11 @@
       <c r="I107">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" ht="30" customHeight="1">
+      <c r="J107" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="30" customHeight="1">
       <c r="A108">
         <v>107</v>
       </c>
@@ -3949,8 +4308,11 @@
       <c r="I108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J108" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="20.25" customHeight="1">
       <c r="A109">
         <v>108</v>
       </c>
@@ -3978,8 +4340,11 @@
       <c r="I109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:9" ht="30" customHeight="1">
+      <c r="J109" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="30" customHeight="1">
       <c r="A110">
         <v>109</v>
       </c>
@@ -4007,8 +4372,11 @@
       <c r="I110">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:9" ht="24" customHeight="1">
+      <c r="J110" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="24" customHeight="1">
       <c r="A111">
         <v>110</v>
       </c>
@@ -4036,8 +4404,11 @@
       <c r="I111">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J111" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="26.25" customHeight="1">
       <c r="A112">
         <v>111</v>
       </c>
@@ -4065,8 +4436,11 @@
       <c r="I112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:9" ht="31.5" customHeight="1">
+      <c r="J112" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="31.5" customHeight="1">
       <c r="A113">
         <v>112</v>
       </c>
@@ -4094,8 +4468,11 @@
       <c r="I113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J113" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="19.5" customHeight="1">
       <c r="A114">
         <v>113</v>
       </c>
@@ -4123,8 +4500,11 @@
       <c r="I114">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J114" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="24.75" customHeight="1">
       <c r="A115">
         <v>114</v>
       </c>
@@ -4152,8 +4532,11 @@
       <c r="I115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J115" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="20.25" customHeight="1">
       <c r="A116">
         <v>115</v>
       </c>
@@ -4181,8 +4564,11 @@
       <c r="I116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J116" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="21.75" customHeight="1">
       <c r="A117">
         <v>116</v>
       </c>
@@ -4210,8 +4596,11 @@
       <c r="I117">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:9" ht="17.25" customHeight="1">
+      <c r="J117" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="17.25" customHeight="1">
       <c r="A118">
         <v>117</v>
       </c>
@@ -4239,8 +4628,11 @@
       <c r="I118">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J118" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="20.25" customHeight="1">
       <c r="A119">
         <v>118</v>
       </c>
@@ -4268,8 +4660,11 @@
       <c r="I119">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J119" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="24.75" customHeight="1">
       <c r="A120">
         <v>119</v>
       </c>
@@ -4297,8 +4692,11 @@
       <c r="I120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J120" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="23.25" customHeight="1">
       <c r="A121">
         <v>120</v>
       </c>
@@ -4326,8 +4724,11 @@
       <c r="I121">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J121" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="21.75" customHeight="1">
       <c r="A122">
         <v>121</v>
       </c>
@@ -4355,8 +4756,11 @@
       <c r="I122">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:9" ht="18.75" customHeight="1">
+      <c r="J122" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="18.75" customHeight="1">
       <c r="A123">
         <v>122</v>
       </c>
@@ -4384,8 +4788,11 @@
       <c r="I123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:9" ht="18.75" customHeight="1">
+      <c r="J123" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="18.75" customHeight="1">
       <c r="A124">
         <v>123</v>
       </c>
@@ -4413,8 +4820,11 @@
       <c r="I124">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J124" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="15.75" customHeight="1">
       <c r="A125">
         <v>124</v>
       </c>
@@ -4442,8 +4852,11 @@
       <c r="I125">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J125" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="20.25" customHeight="1">
       <c r="A126">
         <v>125</v>
       </c>
@@ -4471,8 +4884,11 @@
       <c r="I126">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:9" ht="14.25" customHeight="1">
+      <c r="J126" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="14.25" customHeight="1">
       <c r="A127">
         <v>126</v>
       </c>
@@ -4500,8 +4916,11 @@
       <c r="I127">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J127" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="21.75" customHeight="1">
       <c r="A128">
         <v>127</v>
       </c>
@@ -4529,8 +4948,11 @@
       <c r="I128">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:9" ht="18.75" customHeight="1">
+      <c r="J128" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="18.75" customHeight="1">
       <c r="A129">
         <v>128</v>
       </c>
@@ -4558,8 +4980,11 @@
       <c r="I129">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J129" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="15.75" customHeight="1">
       <c r="A130">
         <v>129</v>
       </c>
@@ -4587,8 +5012,11 @@
       <c r="I130">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J130" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="21.75" customHeight="1">
       <c r="A131">
         <v>130</v>
       </c>
@@ -4616,8 +5044,11 @@
       <c r="I131">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J131" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="19.5" customHeight="1">
       <c r="A132">
         <v>131</v>
       </c>
@@ -4645,8 +5076,11 @@
       <c r="I132">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J132" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="22.5" customHeight="1">
       <c r="A133">
         <v>132</v>
       </c>
@@ -4674,8 +5108,11 @@
       <c r="I133">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J133" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="24.75" customHeight="1">
       <c r="A134">
         <v>133</v>
       </c>
@@ -4703,8 +5140,11 @@
       <c r="I134">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:9" ht="31.5" customHeight="1">
+      <c r="J134" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="31.5" customHeight="1">
       <c r="A135">
         <v>134</v>
       </c>
@@ -4732,8 +5172,11 @@
       <c r="I135">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:9" ht="24" customHeight="1">
+      <c r="J135" s="12">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="24" customHeight="1">
       <c r="A136">
         <v>135</v>
       </c>
@@ -4761,8 +5204,11 @@
       <c r="I136">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:9" ht="27.75" customHeight="1">
+      <c r="J136" s="12">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="27.75" customHeight="1">
       <c r="A137">
         <v>136</v>
       </c>
@@ -4790,8 +5236,11 @@
       <c r="I137">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:9" ht="29.25" customHeight="1">
+      <c r="J137" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="29.25" customHeight="1">
       <c r="A138">
         <v>137</v>
       </c>
@@ -4819,8 +5268,11 @@
       <c r="I138">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:9" ht="27" customHeight="1">
+      <c r="J138" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="27" customHeight="1">
       <c r="A139">
         <v>138</v>
       </c>
@@ -4848,8 +5300,11 @@
       <c r="I139">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J139" s="12">
+        <v>77500</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="19.5" customHeight="1">
       <c r="A140">
         <v>139</v>
       </c>
@@ -4877,8 +5332,11 @@
       <c r="I140">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J140" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="24.75" customHeight="1">
       <c r="A141">
         <v>140</v>
       </c>
@@ -4906,8 +5364,11 @@
       <c r="I141">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J141" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="26.25" customHeight="1">
       <c r="A142">
         <v>141</v>
       </c>
@@ -4935,8 +5396,11 @@
       <c r="I142">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J142" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="19.5" customHeight="1">
       <c r="A143">
         <v>142</v>
       </c>
@@ -4964,8 +5428,11 @@
       <c r="I143">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J143" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="19.5" customHeight="1">
       <c r="A144">
         <v>143</v>
       </c>
@@ -4993,8 +5460,11 @@
       <c r="I144">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J144" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="21.75" customHeight="1">
       <c r="A145">
         <v>144</v>
       </c>
@@ -5022,8 +5492,11 @@
       <c r="I145">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J145" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="20.25" customHeight="1">
       <c r="A146">
         <v>145</v>
       </c>
@@ -5051,8 +5524,11 @@
       <c r="I146">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J146" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="20.25" customHeight="1">
       <c r="A147">
         <v>146</v>
       </c>
@@ -5080,8 +5556,11 @@
       <c r="I147">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J147" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="19.5" customHeight="1">
       <c r="A148">
         <v>147</v>
       </c>
@@ -5109,8 +5588,11 @@
       <c r="I148">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J148" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="26.25" customHeight="1">
       <c r="A149">
         <v>148</v>
       </c>
@@ -5138,8 +5620,11 @@
       <c r="I149">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J149" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="20.25" customHeight="1">
       <c r="A150">
         <v>149</v>
       </c>
@@ -5167,8 +5652,11 @@
       <c r="I150">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J150" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="22.5" customHeight="1">
       <c r="A151">
         <v>150</v>
       </c>
@@ -5196,8 +5684,11 @@
       <c r="I151">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J151" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="22.5" customHeight="1">
       <c r="A152">
         <v>151</v>
       </c>
@@ -5225,8 +5716,11 @@
       <c r="I152">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:9" ht="32.25" customHeight="1">
+      <c r="J152" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="32.25" customHeight="1">
       <c r="A153">
         <v>152</v>
       </c>
@@ -5254,8 +5748,11 @@
       <c r="I153">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J153" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="22.5" customHeight="1">
       <c r="A154">
         <v>153</v>
       </c>
@@ -5283,8 +5780,11 @@
       <c r="I154">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J154" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="19.5" customHeight="1">
       <c r="A155">
         <v>154</v>
       </c>
@@ -5312,8 +5812,11 @@
       <c r="I155">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J155" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="23.25" customHeight="1">
       <c r="A156">
         <v>155</v>
       </c>
@@ -5341,8 +5844,11 @@
       <c r="I156">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:9" ht="27.75" customHeight="1">
+      <c r="J156" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="27.75" customHeight="1">
       <c r="A157">
         <v>156</v>
       </c>
@@ -5370,8 +5876,11 @@
       <c r="I157">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:9" ht="14.25" customHeight="1">
+      <c r="J157" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="14.25" customHeight="1">
       <c r="A158">
         <v>157</v>
       </c>
@@ -5399,8 +5908,11 @@
       <c r="I158">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:9" ht="18.75" customHeight="1">
+      <c r="J158" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="18.75" customHeight="1">
       <c r="A159">
         <v>158</v>
       </c>
@@ -5428,8 +5940,11 @@
       <c r="I159">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:9" ht="29.25" customHeight="1">
+      <c r="J159" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="29.25" customHeight="1">
       <c r="A160">
         <v>159</v>
       </c>
@@ -5457,8 +5972,11 @@
       <c r="I160">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:9" ht="28.5" customHeight="1">
+      <c r="J160" s="12">
+        <v>18750</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="28.5" customHeight="1">
       <c r="A161">
         <v>160</v>
       </c>
@@ -5486,8 +6004,11 @@
       <c r="I161">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J161" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="19.5" customHeight="1">
       <c r="A162">
         <v>161</v>
       </c>
@@ -5515,8 +6036,11 @@
       <c r="I162">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J162" s="12">
+        <v>292500</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="24.75" customHeight="1">
       <c r="A163">
         <v>162</v>
       </c>
@@ -5544,8 +6068,11 @@
       <c r="I163">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J163" s="12">
+        <v>292500</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" ht="15.75" customHeight="1">
       <c r="A164">
         <v>163</v>
       </c>
@@ -5573,8 +6100,11 @@
       <c r="I164">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:9" ht="24" customHeight="1">
+      <c r="J164" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" ht="24" customHeight="1">
       <c r="A165">
         <v>164</v>
       </c>
@@ -5602,8 +6132,11 @@
       <c r="I165">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="1:9" ht="17.25" customHeight="1">
+      <c r="J165" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" ht="17.25" customHeight="1">
       <c r="A166">
         <v>165</v>
       </c>
@@ -5631,8 +6164,11 @@
       <c r="I166">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J166" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" ht="22.5" customHeight="1">
       <c r="A167">
         <v>166</v>
       </c>
@@ -5660,8 +6196,11 @@
       <c r="I167">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:9" ht="28.5" customHeight="1">
+      <c r="J167" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" ht="28.5" customHeight="1">
       <c r="A168">
         <v>167</v>
       </c>
@@ -5689,8 +6228,11 @@
       <c r="I168">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J168" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" ht="21.75" customHeight="1">
       <c r="A169">
         <v>168</v>
       </c>
@@ -5718,8 +6260,11 @@
       <c r="I169">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:9" ht="28.5" customHeight="1">
+      <c r="J169" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" ht="28.5" customHeight="1">
       <c r="A170">
         <v>169</v>
       </c>
@@ -5747,8 +6292,11 @@
       <c r="I170">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J170" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" ht="23.25" customHeight="1">
       <c r="A171">
         <v>170</v>
       </c>
@@ -5776,8 +6324,11 @@
       <c r="I171">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J171" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" ht="23.25" customHeight="1">
       <c r="A172">
         <v>171</v>
       </c>
@@ -5805,8 +6356,11 @@
       <c r="I172">
         <v>0</v>
       </c>
-    </row>
-    <row r="173" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J172" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" ht="20.25" customHeight="1">
       <c r="A173">
         <v>172</v>
       </c>
@@ -5834,8 +6388,11 @@
       <c r="I173">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:9" ht="28.5" customHeight="1">
+      <c r="J173" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="28.5" customHeight="1">
       <c r="A174">
         <v>173</v>
       </c>
@@ -5863,8 +6420,11 @@
       <c r="I174">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J174" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="24.75" customHeight="1">
       <c r="A175">
         <v>174</v>
       </c>
@@ -5892,8 +6452,11 @@
       <c r="I175">
         <v>0</v>
       </c>
-    </row>
-    <row r="176" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J175" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" ht="21.75" customHeight="1">
       <c r="A176">
         <v>175</v>
       </c>
@@ -5921,8 +6484,11 @@
       <c r="I176">
         <v>0</v>
       </c>
-    </row>
-    <row r="177" spans="1:9" ht="30" customHeight="1">
+      <c r="J176" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="30" customHeight="1">
       <c r="A177">
         <v>176</v>
       </c>
@@ -5950,8 +6516,11 @@
       <c r="I177">
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J177" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="21.75" customHeight="1">
       <c r="A178">
         <v>177</v>
       </c>
@@ -5979,8 +6548,11 @@
       <c r="I178">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:9" ht="30" customHeight="1">
+      <c r="J178" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="30" customHeight="1">
       <c r="A179">
         <v>178</v>
       </c>
@@ -6008,8 +6580,11 @@
       <c r="I179">
         <v>0</v>
       </c>
-    </row>
-    <row r="180" spans="1:9" ht="18" customHeight="1">
+      <c r="J179" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" ht="18" customHeight="1">
       <c r="A180">
         <v>179</v>
       </c>
@@ -6037,8 +6612,11 @@
       <c r="I180">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J180" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" ht="21.75" customHeight="1">
       <c r="A181">
         <v>180</v>
       </c>
@@ -6066,8 +6644,11 @@
       <c r="I181">
         <v>0</v>
       </c>
-    </row>
-    <row r="182" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J181" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" ht="22.5" customHeight="1">
       <c r="A182">
         <v>181</v>
       </c>
@@ -6095,8 +6676,11 @@
       <c r="I182">
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="1:9" ht="36" customHeight="1">
+      <c r="J182" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" ht="36" customHeight="1">
       <c r="A183">
         <v>182</v>
       </c>
@@ -6124,8 +6708,11 @@
       <c r="I183">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:9" ht="27" customHeight="1">
+      <c r="J183" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" ht="27" customHeight="1">
       <c r="A184">
         <v>183</v>
       </c>
@@ -6153,8 +6740,11 @@
       <c r="I184">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J184" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" ht="26.25" customHeight="1">
       <c r="A185">
         <v>184</v>
       </c>
@@ -6182,8 +6772,11 @@
       <c r="I185">
         <v>0</v>
       </c>
-    </row>
-    <row r="186" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J185" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" ht="20.25" customHeight="1">
       <c r="A186">
         <v>185</v>
       </c>
@@ -6211,8 +6804,11 @@
       <c r="I186">
         <v>0</v>
       </c>
-    </row>
-    <row r="187" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J186" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="23.25" customHeight="1">
       <c r="A187">
         <v>186</v>
       </c>
@@ -6240,8 +6836,11 @@
       <c r="I187">
         <v>0</v>
       </c>
-    </row>
-    <row r="188" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J187" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="24.75" customHeight="1">
       <c r="A188">
         <v>187</v>
       </c>
@@ -6269,8 +6868,11 @@
       <c r="I188">
         <v>0</v>
       </c>
-    </row>
-    <row r="189" spans="1:9" ht="33.75" customHeight="1">
+      <c r="J188" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" ht="33.75" customHeight="1">
       <c r="A189">
         <v>188</v>
       </c>
@@ -6298,8 +6900,11 @@
       <c r="I189">
         <v>0</v>
       </c>
-    </row>
-    <row r="190" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J189" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" ht="23.25" customHeight="1">
       <c r="A190">
         <v>189</v>
       </c>
@@ -6327,8 +6932,11 @@
       <c r="I190">
         <v>0</v>
       </c>
-    </row>
-    <row r="191" spans="1:9" ht="30" customHeight="1">
+      <c r="J190" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" ht="30" customHeight="1">
       <c r="A191">
         <v>190</v>
       </c>
@@ -6356,8 +6964,11 @@
       <c r="I191">
         <v>0</v>
       </c>
-    </row>
-    <row r="192" spans="1:9" ht="18" customHeight="1">
+      <c r="J191" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" ht="18" customHeight="1">
       <c r="A192">
         <v>191</v>
       </c>
@@ -6385,8 +6996,11 @@
       <c r="I192">
         <v>0</v>
       </c>
-    </row>
-    <row r="193" spans="1:9" ht="18.75" customHeight="1">
+      <c r="J192" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" ht="18.75" customHeight="1">
       <c r="A193">
         <v>192</v>
       </c>
@@ -6414,8 +7028,11 @@
       <c r="I193">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:9" ht="12.75" customHeight="1">
+      <c r="J193" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" ht="12.75" customHeight="1">
       <c r="A194">
         <v>193</v>
       </c>
@@ -6443,8 +7060,11 @@
       <c r="I194">
         <v>0</v>
       </c>
-    </row>
-    <row r="195" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J194" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" ht="22.5" customHeight="1">
       <c r="A195">
         <v>194</v>
       </c>
@@ -6472,8 +7092,11 @@
       <c r="I195">
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="1:9" ht="27.75" customHeight="1">
+      <c r="J195" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" ht="27.75" customHeight="1">
       <c r="A196">
         <v>195</v>
       </c>
@@ -6501,8 +7124,11 @@
       <c r="I196">
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J196" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" ht="15.75" customHeight="1">
       <c r="A197">
         <v>196</v>
       </c>
@@ -6530,8 +7156,11 @@
       <c r="I197">
         <v>0</v>
       </c>
-    </row>
-    <row r="198" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J197" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" ht="13.5" customHeight="1">
       <c r="A198">
         <v>197</v>
       </c>
@@ -6559,8 +7188,11 @@
       <c r="I198">
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="1:9" ht="24" customHeight="1">
+      <c r="J198" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" ht="24" customHeight="1">
       <c r="A199">
         <v>198</v>
       </c>
@@ -6588,8 +7220,11 @@
       <c r="I199">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J199" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" ht="13.5" customHeight="1">
       <c r="A200">
         <v>199</v>
       </c>
@@ -6617,8 +7252,11 @@
       <c r="I200">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:9">
+      <c r="J200" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10">
       <c r="A201">
         <v>200</v>
       </c>
@@ -6646,8 +7284,11 @@
       <c r="I201">
         <v>0</v>
       </c>
-    </row>
-    <row r="202" spans="1:9" ht="27" customHeight="1">
+      <c r="J201" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" ht="27" customHeight="1">
       <c r="A202">
         <v>201</v>
       </c>
@@ -6675,8 +7316,11 @@
       <c r="I202">
         <v>0</v>
       </c>
-    </row>
-    <row r="203" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J202" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" ht="21.75" customHeight="1">
       <c r="A203">
         <v>202</v>
       </c>
@@ -6704,8 +7348,11 @@
       <c r="I203">
         <v>0</v>
       </c>
-    </row>
-    <row r="204" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J203" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" ht="19.5" customHeight="1">
       <c r="A204">
         <v>203</v>
       </c>
@@ -6733,8 +7380,11 @@
       <c r="I204">
         <v>0</v>
       </c>
-    </row>
-    <row r="205" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J204" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" ht="22.5" customHeight="1">
       <c r="A205">
         <v>204</v>
       </c>
@@ -6762,8 +7412,11 @@
       <c r="I205">
         <v>0</v>
       </c>
-    </row>
-    <row r="206" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J205" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" ht="26.25" customHeight="1">
       <c r="A206">
         <v>205</v>
       </c>
@@ -6791,8 +7444,11 @@
       <c r="I206">
         <v>0</v>
       </c>
-    </row>
-    <row r="207" spans="1:9" ht="18" customHeight="1">
+      <c r="J206" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" ht="18" customHeight="1">
       <c r="A207">
         <v>206</v>
       </c>
@@ -6820,8 +7476,11 @@
       <c r="I207">
         <v>0</v>
       </c>
-    </row>
-    <row r="208" spans="1:9" ht="24" customHeight="1">
+      <c r="J207" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" ht="24" customHeight="1">
       <c r="A208">
         <v>207</v>
       </c>
@@ -6849,8 +7508,11 @@
       <c r="I208">
         <v>0</v>
       </c>
-    </row>
-    <row r="209" spans="1:9" ht="27" customHeight="1">
+      <c r="J208" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" ht="27" customHeight="1">
       <c r="A209">
         <v>208</v>
       </c>
@@ -6878,8 +7540,11 @@
       <c r="I209">
         <v>0</v>
       </c>
-    </row>
-    <row r="210" spans="1:9" ht="24" customHeight="1">
+      <c r="J209" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" ht="24" customHeight="1">
       <c r="A210">
         <v>209</v>
       </c>
@@ -6907,8 +7572,11 @@
       <c r="I210">
         <v>0</v>
       </c>
-    </row>
-    <row r="211" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J210" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" ht="26.25" customHeight="1">
       <c r="A211">
         <v>210</v>
       </c>
@@ -6936,8 +7604,11 @@
       <c r="I211">
         <v>0</v>
       </c>
-    </row>
-    <row r="212" spans="1:9" ht="24" customHeight="1">
+      <c r="J211" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" ht="24" customHeight="1">
       <c r="A212">
         <v>211</v>
       </c>
@@ -6965,8 +7636,11 @@
       <c r="I212">
         <v>0</v>
       </c>
-    </row>
-    <row r="213" spans="1:9" ht="18.75" customHeight="1">
+      <c r="J212" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" ht="18.75" customHeight="1">
       <c r="A213">
         <v>212</v>
       </c>
@@ -6994,8 +7668,11 @@
       <c r="I213">
         <v>0</v>
       </c>
-    </row>
-    <row r="214" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J213" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" ht="26.25" customHeight="1">
       <c r="A214">
         <v>213</v>
       </c>
@@ -7023,8 +7700,11 @@
       <c r="I214">
         <v>0</v>
       </c>
-    </row>
-    <row r="215" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J214" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" ht="26.25" customHeight="1">
       <c r="A215">
         <v>214</v>
       </c>
@@ -7052,8 +7732,11 @@
       <c r="I215">
         <v>0</v>
       </c>
-    </row>
-    <row r="216" spans="1:9" ht="27.75" customHeight="1">
+      <c r="J215" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" ht="27.75" customHeight="1">
       <c r="A216">
         <v>215</v>
       </c>
@@ -7081,8 +7764,11 @@
       <c r="I216">
         <v>0</v>
       </c>
-    </row>
-    <row r="217" spans="1:9" ht="27" customHeight="1">
+      <c r="J216" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" ht="27" customHeight="1">
       <c r="A217">
         <v>216</v>
       </c>
@@ -7110,8 +7796,11 @@
       <c r="I217">
         <v>0</v>
       </c>
-    </row>
-    <row r="218" spans="1:9" ht="39" customHeight="1">
+      <c r="J217" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" ht="39" customHeight="1">
       <c r="A218">
         <v>217</v>
       </c>
@@ -7139,8 +7828,11 @@
       <c r="I218">
         <v>0</v>
       </c>
-    </row>
-    <row r="219" spans="1:9" ht="48" customHeight="1">
+      <c r="J218" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" ht="48" customHeight="1">
       <c r="A219">
         <v>218</v>
       </c>
@@ -7168,8 +7860,11 @@
       <c r="I219">
         <v>0</v>
       </c>
-    </row>
-    <row r="220" spans="1:9" ht="33.75" customHeight="1">
+      <c r="J219" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" ht="33.75" customHeight="1">
       <c r="A220">
         <v>219</v>
       </c>
@@ -7197,8 +7892,11 @@
       <c r="I220">
         <v>0</v>
       </c>
-    </row>
-    <row r="221" spans="1:9" ht="28.5" customHeight="1">
+      <c r="J220" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" ht="28.5" customHeight="1">
       <c r="A221">
         <v>220</v>
       </c>
@@ -7226,8 +7924,11 @@
       <c r="I221">
         <v>0</v>
       </c>
-    </row>
-    <row r="222" spans="1:9" ht="37.5" customHeight="1">
+      <c r="J221" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" ht="37.5" customHeight="1">
       <c r="A222">
         <v>221</v>
       </c>
@@ -7255,8 +7956,11 @@
       <c r="I222">
         <v>0</v>
       </c>
-    </row>
-    <row r="223" spans="1:9" ht="34.5" customHeight="1">
+      <c r="J222" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" ht="34.5" customHeight="1">
       <c r="A223">
         <v>222</v>
       </c>
@@ -7284,8 +7988,11 @@
       <c r="I223">
         <v>0</v>
       </c>
-    </row>
-    <row r="224" spans="1:9" ht="40.5" customHeight="1">
+      <c r="J223" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" ht="40.5" customHeight="1">
       <c r="A224">
         <v>223</v>
       </c>
@@ -7313,8 +8020,11 @@
       <c r="I224">
         <v>0</v>
       </c>
-    </row>
-    <row r="225" spans="1:9" ht="38.25" customHeight="1">
+      <c r="J224" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" ht="38.25" customHeight="1">
       <c r="A225">
         <v>224</v>
       </c>
@@ -7342,8 +8052,11 @@
       <c r="I225">
         <v>0</v>
       </c>
-    </row>
-    <row r="226" spans="1:9" ht="36" customHeight="1">
+      <c r="J225" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" ht="36" customHeight="1">
       <c r="A226">
         <v>225</v>
       </c>
@@ -7371,8 +8084,11 @@
       <c r="I226">
         <v>0</v>
       </c>
-    </row>
-    <row r="227" spans="1:9" ht="31.5" customHeight="1">
+      <c r="J226" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" ht="31.5" customHeight="1">
       <c r="A227">
         <v>226</v>
       </c>
@@ -7400,8 +8116,11 @@
       <c r="I227">
         <v>0</v>
       </c>
-    </row>
-    <row r="228" spans="1:9" ht="32.25" customHeight="1">
+      <c r="J227" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" ht="32.25" customHeight="1">
       <c r="A228">
         <v>227</v>
       </c>
@@ -7429,8 +8148,11 @@
       <c r="I228">
         <v>0</v>
       </c>
-    </row>
-    <row r="229" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J228" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" ht="23.25" customHeight="1">
       <c r="A229">
         <v>228</v>
       </c>
@@ -7458,8 +8180,11 @@
       <c r="I229">
         <v>0</v>
       </c>
-    </row>
-    <row r="230" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J229" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" ht="22.5" customHeight="1">
       <c r="A230">
         <v>229</v>
       </c>
@@ -7487,8 +8212,11 @@
       <c r="I230">
         <v>0</v>
       </c>
-    </row>
-    <row r="231" spans="1:9" ht="40.5" customHeight="1">
+      <c r="J230" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" ht="40.5" customHeight="1">
       <c r="A231">
         <v>230</v>
       </c>
@@ -7516,8 +8244,11 @@
       <c r="I231">
         <v>0</v>
       </c>
-    </row>
-    <row r="232" spans="1:9" ht="41.25" customHeight="1">
+      <c r="J231" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" ht="41.25" customHeight="1">
       <c r="A232">
         <v>231</v>
       </c>
@@ -7545,8 +8276,11 @@
       <c r="I232">
         <v>0</v>
       </c>
-    </row>
-    <row r="233" spans="1:9" ht="36.75" customHeight="1">
+      <c r="J232" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" ht="36.75" customHeight="1">
       <c r="A233">
         <v>232</v>
       </c>
@@ -7574,8 +8308,11 @@
       <c r="I233">
         <v>0</v>
       </c>
-    </row>
-    <row r="234" spans="1:9" ht="37.5" customHeight="1">
+      <c r="J233" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" ht="37.5" customHeight="1">
       <c r="A234">
         <v>233</v>
       </c>
@@ -7603,8 +8340,11 @@
       <c r="I234">
         <v>0</v>
       </c>
-    </row>
-    <row r="235" spans="1:9" ht="33.75" customHeight="1">
+      <c r="J234" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" ht="33.75" customHeight="1">
       <c r="A235">
         <v>234</v>
       </c>
@@ -7632,8 +8372,11 @@
       <c r="I235">
         <v>0</v>
       </c>
-    </row>
-    <row r="236" spans="1:9" ht="30" customHeight="1">
+      <c r="J235" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" ht="30" customHeight="1">
       <c r="A236">
         <v>235</v>
       </c>
@@ -7661,8 +8404,11 @@
       <c r="I236">
         <v>0</v>
       </c>
-    </row>
-    <row r="237" spans="1:9" ht="47.25" customHeight="1">
+      <c r="J236" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" ht="47.25" customHeight="1">
       <c r="A237">
         <v>236</v>
       </c>
@@ -7690,8 +8436,11 @@
       <c r="I237">
         <v>0</v>
       </c>
-    </row>
-    <row r="238" spans="1:9" ht="37.5" customHeight="1">
+      <c r="J237" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" ht="37.5" customHeight="1">
       <c r="A238">
         <v>237</v>
       </c>
@@ -7719,8 +8468,11 @@
       <c r="I238">
         <v>0</v>
       </c>
-    </row>
-    <row r="239" spans="1:9" ht="27.75" customHeight="1">
+      <c r="J238" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" ht="27.75" customHeight="1">
       <c r="A239">
         <v>238</v>
       </c>
@@ -7748,8 +8500,11 @@
       <c r="I239">
         <v>0</v>
       </c>
-    </row>
-    <row r="240" spans="1:9" ht="34.5" customHeight="1">
+      <c r="J239" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" ht="34.5" customHeight="1">
       <c r="A240">
         <v>239</v>
       </c>
@@ -7777,8 +8532,11 @@
       <c r="I240">
         <v>0</v>
       </c>
-    </row>
-    <row r="241" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J240" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" ht="24.75" customHeight="1">
       <c r="A241">
         <v>240</v>
       </c>
@@ -7806,8 +8564,11 @@
       <c r="I241">
         <v>0</v>
       </c>
-    </row>
-    <row r="242" spans="1:9" ht="31.5" customHeight="1">
+      <c r="J241" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" ht="31.5" customHeight="1">
       <c r="A242">
         <v>241</v>
       </c>
@@ -7835,8 +8596,11 @@
       <c r="I242">
         <v>0</v>
       </c>
-    </row>
-    <row r="243" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J242" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" ht="23.25" customHeight="1">
       <c r="A243">
         <v>242</v>
       </c>
@@ -7864,8 +8628,11 @@
       <c r="I243">
         <v>0</v>
       </c>
-    </row>
-    <row r="244" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J243" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" ht="26.25" customHeight="1">
       <c r="A244">
         <v>243</v>
       </c>
@@ -7893,8 +8660,11 @@
       <c r="I244">
         <v>0</v>
       </c>
-    </row>
-    <row r="245" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J244" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" ht="23.25" customHeight="1">
       <c r="A245">
         <v>244</v>
       </c>
@@ -7922,8 +8692,11 @@
       <c r="I245">
         <v>0</v>
       </c>
-    </row>
-    <row r="246" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J245" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" ht="19.5" customHeight="1">
       <c r="A246">
         <v>245</v>
       </c>
@@ -7951,8 +8724,11 @@
       <c r="I246">
         <v>0</v>
       </c>
-    </row>
-    <row r="247" spans="1:9" ht="45.75" customHeight="1">
+      <c r="J246" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" ht="45.75" customHeight="1">
       <c r="A247">
         <v>246</v>
       </c>
@@ -7980,8 +8756,11 @@
       <c r="I247">
         <v>0</v>
       </c>
-    </row>
-    <row r="248" spans="1:9" ht="36" customHeight="1">
+      <c r="J247" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" ht="36" customHeight="1">
       <c r="A248">
         <v>247</v>
       </c>
@@ -8009,8 +8788,11 @@
       <c r="I248">
         <v>0</v>
       </c>
-    </row>
-    <row r="249" spans="1:9" ht="36.75" customHeight="1">
+      <c r="J248" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" ht="36.75" customHeight="1">
       <c r="A249">
         <v>248</v>
       </c>
@@ -8038,8 +8820,11 @@
       <c r="I249">
         <v>0</v>
       </c>
-    </row>
-    <row r="250" spans="1:9" ht="30" customHeight="1">
+      <c r="J249" s="12">
+        <v>97500</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" ht="30" customHeight="1">
       <c r="A250">
         <v>249</v>
       </c>
@@ -8067,8 +8852,11 @@
       <c r="I250">
         <v>7500</v>
       </c>
-    </row>
-    <row r="251" spans="1:9" ht="33.75" customHeight="1">
+      <c r="J250" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" ht="33.75" customHeight="1">
       <c r="A251">
         <v>250</v>
       </c>
@@ -8096,8 +8884,11 @@
       <c r="I251">
         <v>4721</v>
       </c>
-    </row>
-    <row r="252" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J251" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" ht="26.25" customHeight="1">
       <c r="A252">
         <v>251</v>
       </c>
@@ -8125,8 +8916,11 @@
       <c r="I252">
         <v>7500</v>
       </c>
-    </row>
-    <row r="253" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J252" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" ht="22.5" customHeight="1">
       <c r="A253">
         <v>252</v>
       </c>
@@ -8154,8 +8948,11 @@
       <c r="I253">
         <v>7500</v>
       </c>
-    </row>
-    <row r="254" spans="1:9" ht="29.25" customHeight="1">
+      <c r="J253" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" ht="29.25" customHeight="1">
       <c r="A254">
         <v>253</v>
       </c>
@@ -8183,8 +8980,11 @@
       <c r="I254">
         <v>7500</v>
       </c>
-    </row>
-    <row r="255" spans="1:9" ht="18" customHeight="1">
+      <c r="J254" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" ht="18" customHeight="1">
       <c r="A255">
         <v>254</v>
       </c>
@@ -8212,8 +9012,11 @@
       <c r="I255">
         <v>7500</v>
       </c>
-    </row>
-    <row r="256" spans="1:9" ht="32.25" customHeight="1">
+      <c r="J255" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" ht="32.25" customHeight="1">
       <c r="A256">
         <v>255</v>
       </c>
@@ -8241,8 +9044,11 @@
       <c r="I256">
         <v>7500</v>
       </c>
-    </row>
-    <row r="257" spans="1:9" ht="24" customHeight="1">
+      <c r="J256" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" ht="24" customHeight="1">
       <c r="A257">
         <v>256</v>
       </c>
@@ -8270,8 +9076,11 @@
       <c r="I257">
         <v>6000</v>
       </c>
-    </row>
-    <row r="258" spans="1:9" ht="33" customHeight="1">
+      <c r="J257" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" ht="33" customHeight="1">
       <c r="A258">
         <v>257</v>
       </c>
@@ -8299,8 +9108,11 @@
       <c r="I258">
         <v>3600</v>
       </c>
-    </row>
-    <row r="259" spans="1:9" ht="18.75" customHeight="1">
+      <c r="J258" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" ht="18.75" customHeight="1">
       <c r="A259">
         <v>258</v>
       </c>
@@ -8328,8 +9140,11 @@
       <c r="I259">
         <v>0</v>
       </c>
-    </row>
-    <row r="260" spans="1:9" ht="28.5" customHeight="1">
+      <c r="J259" s="12">
+        <v>97500</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" ht="28.5" customHeight="1">
       <c r="A260">
         <v>259</v>
       </c>
@@ -8357,8 +9172,11 @@
       <c r="I260">
         <v>0</v>
       </c>
-    </row>
-    <row r="261" spans="1:9" ht="18.75" customHeight="1">
+      <c r="J260" s="12">
+        <v>97500</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" ht="18.75" customHeight="1">
       <c r="A261">
         <v>260</v>
       </c>
@@ -8386,8 +9204,11 @@
       <c r="I261">
         <v>0</v>
       </c>
-    </row>
-    <row r="262" spans="1:9">
+      <c r="J261" s="12">
+        <v>97500</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10">
       <c r="A262">
         <v>261</v>
       </c>
@@ -8415,8 +9236,11 @@
       <c r="I262">
         <v>0</v>
       </c>
-    </row>
-    <row r="263" spans="1:9">
+      <c r="J262" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10">
       <c r="A263">
         <v>262</v>
       </c>
@@ -8444,8 +9268,11 @@
       <c r="I263">
         <v>0</v>
       </c>
-    </row>
-    <row r="264" spans="1:9">
+      <c r="J263" s="12">
+        <v>97500</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10">
       <c r="A264">
         <v>263</v>
       </c>
@@ -8473,8 +9300,11 @@
       <c r="I264">
         <v>0</v>
       </c>
-    </row>
-    <row r="265" spans="1:9">
+      <c r="J264" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10">
       <c r="A265">
         <v>264</v>
       </c>
@@ -8502,8 +9332,11 @@
       <c r="I265">
         <v>0</v>
       </c>
-    </row>
-    <row r="266" spans="1:9">
+      <c r="J265" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10">
       <c r="A266">
         <v>265</v>
       </c>
@@ -8531,8 +9364,11 @@
       <c r="I266">
         <v>0</v>
       </c>
-    </row>
-    <row r="267" spans="1:9">
+      <c r="J266" s="12">
+        <v>44360</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10">
       <c r="A267">
         <v>266</v>
       </c>
@@ -8560,8 +9396,11 @@
       <c r="I267">
         <v>0</v>
       </c>
-    </row>
-    <row r="268" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J267" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" ht="22.5" customHeight="1">
       <c r="A268">
         <v>267</v>
       </c>
@@ -8589,8 +9428,11 @@
       <c r="I268">
         <v>0</v>
       </c>
-    </row>
-    <row r="269" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J268" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" ht="21.75" customHeight="1">
       <c r="A269">
         <v>268</v>
       </c>
@@ -8618,8 +9460,11 @@
       <c r="I269">
         <v>0</v>
       </c>
-    </row>
-    <row r="270" spans="1:9" ht="29.25" customHeight="1">
+      <c r="J269" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" ht="29.25" customHeight="1">
       <c r="A270">
         <v>269</v>
       </c>
@@ -8647,8 +9492,11 @@
       <c r="I270">
         <v>0</v>
       </c>
-    </row>
-    <row r="271" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J270" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" ht="22.5" customHeight="1">
       <c r="A271">
         <v>270</v>
       </c>
@@ -8676,8 +9524,11 @@
       <c r="I271">
         <v>0</v>
       </c>
-    </row>
-    <row r="272" spans="1:9" ht="33.75" customHeight="1">
+      <c r="J271" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" ht="33.75" customHeight="1">
       <c r="A272">
         <v>271</v>
       </c>
@@ -8705,8 +9556,11 @@
       <c r="I272">
         <v>0</v>
       </c>
-    </row>
-    <row r="273" spans="1:9">
+      <c r="J272" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10">
       <c r="A273">
         <v>272</v>
       </c>
@@ -8734,8 +9588,11 @@
       <c r="I273">
         <v>0</v>
       </c>
-    </row>
-    <row r="274" spans="1:9" ht="27.75" customHeight="1">
+      <c r="J273" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" ht="27.75" customHeight="1">
       <c r="A274">
         <v>273</v>
       </c>
@@ -8763,8 +9620,11 @@
       <c r="I274">
         <v>0</v>
       </c>
-    </row>
-    <row r="275" spans="1:9">
+      <c r="J274" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10">
       <c r="A275">
         <v>274</v>
       </c>
@@ -8792,8 +9652,11 @@
       <c r="I275">
         <v>0</v>
       </c>
-    </row>
-    <row r="276" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J275" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" ht="19.5" customHeight="1">
       <c r="A276">
         <v>275</v>
       </c>
@@ -8821,8 +9684,11 @@
       <c r="I276">
         <v>0</v>
       </c>
-    </row>
-    <row r="277" spans="1:9" ht="30" customHeight="1">
+      <c r="J276" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" ht="30" customHeight="1">
       <c r="A277">
         <v>276</v>
       </c>
@@ -8850,8 +9716,11 @@
       <c r="I277">
         <v>0</v>
       </c>
-    </row>
-    <row r="278" spans="1:9">
+      <c r="J277" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10">
       <c r="A278">
         <v>277</v>
       </c>
@@ -8879,8 +9748,11 @@
       <c r="I278">
         <v>0</v>
       </c>
-    </row>
-    <row r="279" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J278" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" ht="26.25" customHeight="1">
       <c r="A279">
         <v>278</v>
       </c>
@@ -8908,8 +9780,11 @@
       <c r="I279">
         <v>0</v>
       </c>
-    </row>
-    <row r="280" spans="1:9">
+      <c r="J279" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10">
       <c r="A280">
         <v>279</v>
       </c>
@@ -8937,8 +9812,11 @@
       <c r="I280">
         <v>0</v>
       </c>
-    </row>
-    <row r="281" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J280" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" ht="19.5" customHeight="1">
       <c r="A281">
         <v>280</v>
       </c>
@@ -8966,8 +9844,11 @@
       <c r="I281">
         <v>0</v>
       </c>
-    </row>
-    <row r="282" spans="1:9">
+      <c r="J281" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10">
       <c r="A282">
         <v>281</v>
       </c>
@@ -8995,8 +9876,11 @@
       <c r="I282">
         <v>0</v>
       </c>
-    </row>
-    <row r="283" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J282" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" ht="22.5" customHeight="1">
       <c r="A283">
         <v>282</v>
       </c>
@@ -9024,8 +9908,11 @@
       <c r="I283">
         <v>0</v>
       </c>
-    </row>
-    <row r="284" spans="1:9" ht="24.75" customHeight="1">
+      <c r="J283" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" ht="24.75" customHeight="1">
       <c r="A284">
         <v>283</v>
       </c>
@@ -9053,8 +9940,11 @@
       <c r="I284">
         <v>0</v>
       </c>
-    </row>
-    <row r="285" spans="1:9" ht="24" customHeight="1">
+      <c r="J284" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" ht="24" customHeight="1">
       <c r="A285">
         <v>284</v>
       </c>
@@ -9082,8 +9972,11 @@
       <c r="I285">
         <v>0</v>
       </c>
-    </row>
-    <row r="286" spans="1:9">
+      <c r="J285" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10">
       <c r="A286">
         <v>285</v>
       </c>
@@ -9111,8 +10004,11 @@
       <c r="I286">
         <v>0</v>
       </c>
-    </row>
-    <row r="287" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J286" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" ht="23.25" customHeight="1">
       <c r="A287">
         <v>286</v>
       </c>
@@ -9140,8 +10036,11 @@
       <c r="I287">
         <v>0</v>
       </c>
-    </row>
-    <row r="288" spans="1:9" ht="27.75" customHeight="1">
+      <c r="J287" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10" ht="27.75" customHeight="1">
       <c r="A288">
         <v>287</v>
       </c>
@@ -9169,8 +10068,11 @@
       <c r="I288">
         <v>7500</v>
       </c>
-    </row>
-    <row r="289" spans="1:9" ht="14.25" customHeight="1">
+      <c r="J288" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" ht="14.25" customHeight="1">
       <c r="A289">
         <v>288</v>
       </c>
@@ -9198,8 +10100,11 @@
       <c r="I289">
         <v>7500</v>
       </c>
-    </row>
-    <row r="290" spans="1:9" ht="32.25" customHeight="1">
+      <c r="J289" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" ht="32.25" customHeight="1">
       <c r="A290">
         <v>289</v>
       </c>
@@ -9227,8 +10132,11 @@
       <c r="I290">
         <v>7500</v>
       </c>
-    </row>
-    <row r="291" spans="1:9" ht="34.5" customHeight="1">
+      <c r="J290" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" ht="34.5" customHeight="1">
       <c r="A291">
         <v>290</v>
       </c>
@@ -9256,8 +10164,11 @@
       <c r="I291">
         <v>7500</v>
       </c>
-    </row>
-    <row r="292" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J291" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" ht="26.25" customHeight="1">
       <c r="A292">
         <v>291</v>
       </c>
@@ -9285,8 +10196,11 @@
       <c r="I292">
         <v>7500</v>
       </c>
-    </row>
-    <row r="293" spans="1:9" ht="34.5" customHeight="1">
+      <c r="J292" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" ht="34.5" customHeight="1">
       <c r="A293">
         <v>292</v>
       </c>
@@ -9314,8 +10228,11 @@
       <c r="I293">
         <v>7500</v>
       </c>
-    </row>
-    <row r="294" spans="1:9" ht="34.5" customHeight="1">
+      <c r="J293" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" ht="34.5" customHeight="1">
       <c r="A294">
         <v>293</v>
       </c>
@@ -9343,8 +10260,11 @@
       <c r="I294">
         <v>7500</v>
       </c>
-    </row>
-    <row r="295" spans="1:9" ht="27" customHeight="1">
+      <c r="J294" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" ht="27" customHeight="1">
       <c r="A295">
         <v>294</v>
       </c>
@@ -9372,8 +10292,11 @@
       <c r="I295">
         <v>3000</v>
       </c>
-    </row>
-    <row r="296" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J295" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" ht="19.5" customHeight="1">
       <c r="A296">
         <v>295</v>
       </c>
@@ -9401,8 +10324,11 @@
       <c r="I296">
         <v>4246</v>
       </c>
-    </row>
-    <row r="297" spans="1:9" ht="15">
+      <c r="J296" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" ht="15">
       <c r="A297">
         <v>296</v>
       </c>
@@ -9430,8 +10356,11 @@
       <c r="I297">
         <v>0</v>
       </c>
-    </row>
-    <row r="298" spans="1:9">
+      <c r="J297" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10">
       <c r="A298">
         <v>297</v>
       </c>
@@ -9459,8 +10388,11 @@
       <c r="I298">
         <v>0</v>
       </c>
-    </row>
-    <row r="299" spans="1:9" ht="27.75" customHeight="1">
+      <c r="J298" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" ht="27.75" customHeight="1">
       <c r="A299">
         <v>298</v>
       </c>
@@ -9488,8 +10420,11 @@
       <c r="I299">
         <v>0</v>
       </c>
-    </row>
-    <row r="300" spans="1:9" ht="36.75" customHeight="1">
+      <c r="J299" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" ht="36.75" customHeight="1">
       <c r="A300">
         <v>299</v>
       </c>
@@ -9517,8 +10452,11 @@
       <c r="I300">
         <v>0</v>
       </c>
-    </row>
-    <row r="301" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J300" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" ht="23.25" customHeight="1">
       <c r="A301">
         <v>300</v>
       </c>
@@ -9546,8 +10484,11 @@
       <c r="I301">
         <v>0</v>
       </c>
-    </row>
-    <row r="302" spans="1:9">
+      <c r="J301" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10">
       <c r="A302">
         <v>301</v>
       </c>
@@ -9575,8 +10516,11 @@
       <c r="I302">
         <v>0</v>
       </c>
-    </row>
-    <row r="303" spans="1:9">
+      <c r="J302" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10">
       <c r="A303">
         <v>302</v>
       </c>
@@ -9604,8 +10548,11 @@
       <c r="I303">
         <v>0</v>
       </c>
-    </row>
-    <row r="304" spans="1:9">
+      <c r="J303" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10">
       <c r="A304">
         <v>303</v>
       </c>
@@ -9633,8 +10580,11 @@
       <c r="I304">
         <v>0</v>
       </c>
-    </row>
-    <row r="305" spans="1:9">
+      <c r="J304" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10">
       <c r="A305">
         <v>304</v>
       </c>
@@ -9662,8 +10612,11 @@
       <c r="I305">
         <v>0</v>
       </c>
-    </row>
-    <row r="306" spans="1:9" ht="17.25" customHeight="1">
+      <c r="J305" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" ht="17.25" customHeight="1">
       <c r="A306">
         <v>305</v>
       </c>
@@ -9691,8 +10644,11 @@
       <c r="I306">
         <v>0</v>
       </c>
-    </row>
-    <row r="307" spans="1:9" ht="27" customHeight="1">
+      <c r="J306" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10" ht="27" customHeight="1">
       <c r="A307">
         <v>306</v>
       </c>
@@ -9720,8 +10676,11 @@
       <c r="I307">
         <v>0</v>
       </c>
-    </row>
-    <row r="308" spans="1:9" ht="18.75" customHeight="1">
+      <c r="J307" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" ht="18.75" customHeight="1">
       <c r="A308">
         <v>307</v>
       </c>
@@ -9749,8 +10708,11 @@
       <c r="I308">
         <v>0</v>
       </c>
-    </row>
-    <row r="309" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J308" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" ht="26.25" customHeight="1">
       <c r="A309">
         <v>308</v>
       </c>
@@ -9778,8 +10740,11 @@
       <c r="I309">
         <v>5875</v>
       </c>
-    </row>
-    <row r="310" spans="1:9" ht="33" customHeight="1">
+      <c r="J309" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" ht="33" customHeight="1">
       <c r="A310">
         <v>309</v>
       </c>
@@ -9807,8 +10772,11 @@
       <c r="I310">
         <v>1152</v>
       </c>
-    </row>
-    <row r="311" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J310" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" ht="20.25" customHeight="1">
       <c r="A311">
         <v>310</v>
       </c>
@@ -9836,8 +10804,11 @@
       <c r="I311">
         <v>6915</v>
       </c>
-    </row>
-    <row r="312" spans="1:9" ht="29.25" customHeight="1">
+      <c r="J311" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" ht="29.25" customHeight="1">
       <c r="A312">
         <v>311</v>
       </c>
@@ -9865,8 +10836,11 @@
       <c r="I312">
         <v>0</v>
       </c>
-    </row>
-    <row r="313" spans="1:9" ht="18" customHeight="1">
+      <c r="J312" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10" ht="18" customHeight="1">
       <c r="A313">
         <v>312</v>
       </c>
@@ -9894,8 +10868,11 @@
       <c r="I313" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="314" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J313" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10" ht="26.25" customHeight="1">
       <c r="A314">
         <v>313</v>
       </c>
@@ -9923,8 +10900,11 @@
       <c r="I314">
         <v>0</v>
       </c>
-    </row>
-    <row r="315" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J314" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" ht="13.5" customHeight="1">
       <c r="A315">
         <v>314</v>
       </c>
@@ -9952,8 +10932,11 @@
       <c r="I315">
         <v>0</v>
       </c>
-    </row>
-    <row r="316" spans="1:9" ht="18" customHeight="1">
+      <c r="J315" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" ht="18" customHeight="1">
       <c r="A316">
         <v>315</v>
       </c>
@@ -9981,8 +10964,11 @@
       <c r="I316">
         <v>0</v>
       </c>
-    </row>
-    <row r="317" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J316" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" ht="19.5" customHeight="1">
       <c r="A317">
         <v>316</v>
       </c>
@@ -10010,8 +10996,11 @@
       <c r="I317">
         <v>0</v>
       </c>
-    </row>
-    <row r="318" spans="1:9" ht="21.75" customHeight="1">
+      <c r="J317" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10" ht="21.75" customHeight="1">
       <c r="A318">
         <v>317</v>
       </c>
@@ -10039,8 +11028,11 @@
       <c r="I318">
         <v>0</v>
       </c>
-    </row>
-    <row r="319" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J318" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" ht="13.5" customHeight="1">
       <c r="A319">
         <v>318</v>
       </c>
@@ -10068,8 +11060,11 @@
       <c r="I319">
         <v>0</v>
       </c>
-    </row>
-    <row r="320" spans="1:9" ht="20.25" customHeight="1">
+      <c r="J319" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" ht="20.25" customHeight="1">
       <c r="A320">
         <v>319</v>
       </c>
@@ -10097,8 +11092,11 @@
       <c r="I320">
         <v>0</v>
       </c>
-    </row>
-    <row r="321" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J320" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" ht="23.25" customHeight="1">
       <c r="A321">
         <v>320</v>
       </c>
@@ -10126,8 +11124,11 @@
       <c r="I321">
         <v>0</v>
       </c>
-    </row>
-    <row r="322" spans="1:9" ht="27" customHeight="1">
+      <c r="J321" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10" ht="27" customHeight="1">
       <c r="A322">
         <v>321</v>
       </c>
@@ -10155,8 +11156,11 @@
       <c r="I322">
         <v>0</v>
       </c>
-    </row>
-    <row r="323" spans="1:9" ht="23.25" customHeight="1">
+      <c r="J322" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:10" ht="23.25" customHeight="1">
       <c r="A323">
         <v>322</v>
       </c>
@@ -10184,8 +11188,11 @@
       <c r="I323">
         <v>0</v>
       </c>
-    </row>
-    <row r="324" spans="1:9" ht="26.25" customHeight="1">
+      <c r="J323" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:10" ht="26.25" customHeight="1">
       <c r="A324">
         <v>323</v>
       </c>
@@ -10213,8 +11220,11 @@
       <c r="I324">
         <v>0</v>
       </c>
-    </row>
-    <row r="325" spans="1:9" ht="27" customHeight="1">
+      <c r="J324" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10" ht="27" customHeight="1">
       <c r="A325">
         <v>324</v>
       </c>
@@ -10242,8 +11252,11 @@
       <c r="I325">
         <v>0</v>
       </c>
-    </row>
-    <row r="326" spans="1:9" ht="30" customHeight="1">
+      <c r="J325" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10" ht="30" customHeight="1">
       <c r="A326">
         <v>325</v>
       </c>
@@ -10271,8 +11284,11 @@
       <c r="I326">
         <v>0</v>
       </c>
-    </row>
-    <row r="327" spans="1:9" ht="18" customHeight="1">
+      <c r="J326" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10" ht="18" customHeight="1">
       <c r="A327">
         <v>326</v>
       </c>
@@ -10300,8 +11316,11 @@
       <c r="I327">
         <v>0</v>
       </c>
-    </row>
-    <row r="328" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J327" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:10" ht="22.5" customHeight="1">
       <c r="A328">
         <v>327</v>
       </c>
@@ -10329,8 +11348,11 @@
       <c r="I328">
         <v>0</v>
       </c>
-    </row>
-    <row r="329" spans="1:9" ht="24" customHeight="1">
+      <c r="J328" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:10" ht="24" customHeight="1">
       <c r="A329">
         <v>328</v>
       </c>
@@ -10358,8 +11380,11 @@
       <c r="I329">
         <v>0</v>
       </c>
-    </row>
-    <row r="330" spans="1:9">
+      <c r="J329" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:10">
       <c r="A330">
         <v>329</v>
       </c>
@@ -10387,8 +11412,11 @@
       <c r="I330">
         <v>0</v>
       </c>
-    </row>
-    <row r="331" spans="1:9">
+      <c r="J330" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10">
       <c r="A331">
         <v>330</v>
       </c>
@@ -10416,8 +11444,11 @@
       <c r="I331">
         <v>0</v>
       </c>
-    </row>
-    <row r="332" spans="1:9" ht="12.75" customHeight="1">
+      <c r="J331" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:10" ht="12.75" customHeight="1">
       <c r="A332">
         <v>331</v>
       </c>
@@ -10445,8 +11476,11 @@
       <c r="I332">
         <v>0</v>
       </c>
-    </row>
-    <row r="333" spans="1:9">
+      <c r="J332" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:10">
       <c r="A333">
         <v>332</v>
       </c>
@@ -10474,8 +11508,11 @@
       <c r="I333">
         <v>0</v>
       </c>
-    </row>
-    <row r="334" spans="1:9">
+      <c r="J333" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:10">
       <c r="A334">
         <v>333</v>
       </c>
@@ -10503,8 +11540,11 @@
       <c r="I334">
         <v>0</v>
       </c>
-    </row>
-    <row r="335" spans="1:9" ht="18" customHeight="1">
+      <c r="J334" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10" ht="18" customHeight="1">
       <c r="A335">
         <v>334</v>
       </c>
@@ -10532,8 +11572,11 @@
       <c r="I335">
         <v>1985</v>
       </c>
-    </row>
-    <row r="336" spans="1:9">
+      <c r="J335" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:10">
       <c r="A336">
         <v>335</v>
       </c>
@@ -10561,8 +11604,11 @@
       <c r="I336">
         <v>0</v>
       </c>
-    </row>
-    <row r="337" spans="1:9" ht="18" customHeight="1">
+      <c r="J336" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" ht="18" customHeight="1">
       <c r="A337">
         <v>336</v>
       </c>
@@ -10590,8 +11636,11 @@
       <c r="I337">
         <v>0</v>
       </c>
-    </row>
-    <row r="338" spans="1:9" ht="18" customHeight="1">
+      <c r="J337" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:10" ht="18" customHeight="1">
       <c r="A338">
         <v>337</v>
       </c>
@@ -10619,8 +11668,11 @@
       <c r="I338">
         <v>0</v>
       </c>
-    </row>
-    <row r="339" spans="1:9" ht="18" customHeight="1">
+      <c r="J338" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10" ht="18" customHeight="1">
       <c r="A339">
         <v>338</v>
       </c>
@@ -10648,8 +11700,11 @@
       <c r="I339">
         <v>0</v>
       </c>
-    </row>
-    <row r="340" spans="1:9" ht="18" customHeight="1">
+      <c r="J339" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:10" ht="18" customHeight="1">
       <c r="A340">
         <v>339</v>
       </c>
@@ -10677,8 +11732,11 @@
       <c r="I340">
         <v>0</v>
       </c>
-    </row>
-    <row r="341" spans="1:9" ht="18" customHeight="1">
+      <c r="J340" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10" ht="18" customHeight="1">
       <c r="A341">
         <v>340</v>
       </c>
@@ -10706,8 +11764,11 @@
       <c r="I341">
         <v>0</v>
       </c>
-    </row>
-    <row r="342" spans="1:9" ht="18" customHeight="1">
+      <c r="J341" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" ht="18" customHeight="1">
       <c r="A342">
         <v>341</v>
       </c>
@@ -10735,8 +11796,11 @@
       <c r="I342">
         <v>0</v>
       </c>
-    </row>
-    <row r="343" spans="1:9" ht="18" customHeight="1">
+      <c r="J342" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:10" ht="18" customHeight="1">
       <c r="A343">
         <v>342</v>
       </c>
@@ -10764,8 +11828,11 @@
       <c r="I343">
         <v>0</v>
       </c>
-    </row>
-    <row r="344" spans="1:9" ht="18" customHeight="1">
+      <c r="J343" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:10" ht="18" customHeight="1">
       <c r="A344">
         <v>343</v>
       </c>
@@ -10793,8 +11860,11 @@
       <c r="I344">
         <v>0</v>
       </c>
-    </row>
-    <row r="345" spans="1:9" ht="18" customHeight="1">
+      <c r="J344" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:10" ht="18" customHeight="1">
       <c r="A345">
         <v>344</v>
       </c>
@@ -10822,8 +11892,11 @@
       <c r="I345">
         <v>0</v>
       </c>
-    </row>
-    <row r="346" spans="1:9" ht="18" customHeight="1">
+      <c r="J345" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10" ht="18" customHeight="1">
       <c r="A346">
         <v>345</v>
       </c>
@@ -10851,8 +11924,11 @@
       <c r="I346">
         <v>0</v>
       </c>
-    </row>
-    <row r="347" spans="1:9" ht="18" customHeight="1">
+      <c r="J346" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:10" ht="18" customHeight="1">
       <c r="A347">
         <v>346</v>
       </c>
@@ -10880,8 +11956,11 @@
       <c r="I347">
         <v>0</v>
       </c>
-    </row>
-    <row r="348" spans="1:9" ht="18" customHeight="1">
+      <c r="J347" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:10" ht="18" customHeight="1">
       <c r="A348">
         <v>347</v>
       </c>
@@ -10909,8 +11988,11 @@
       <c r="I348">
         <v>0</v>
       </c>
-    </row>
-    <row r="349" spans="1:9" ht="18" customHeight="1">
+      <c r="J348" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:10" ht="18" customHeight="1">
       <c r="A349">
         <v>348</v>
       </c>
@@ -10938,8 +12020,11 @@
       <c r="I349">
         <v>0</v>
       </c>
-    </row>
-    <row r="350" spans="1:9" ht="18" customHeight="1">
+      <c r="J349" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:10" ht="18" customHeight="1">
       <c r="A350">
         <v>349</v>
       </c>
@@ -10967,8 +12052,11 @@
       <c r="I350">
         <v>0</v>
       </c>
-    </row>
-    <row r="351" spans="1:9" ht="18" customHeight="1">
+      <c r="J350" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:10" ht="18" customHeight="1">
       <c r="A351">
         <v>350</v>
       </c>
@@ -10996,8 +12084,11 @@
       <c r="I351">
         <v>0</v>
       </c>
-    </row>
-    <row r="352" spans="1:9" ht="18" customHeight="1">
+      <c r="J351" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:10" ht="18" customHeight="1">
       <c r="A352">
         <v>351</v>
       </c>
@@ -11025,8 +12116,11 @@
       <c r="I352">
         <v>0</v>
       </c>
-    </row>
-    <row r="353" spans="1:9" ht="18" customHeight="1">
+      <c r="J352" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:10" ht="18" customHeight="1">
       <c r="A353">
         <v>352</v>
       </c>
@@ -11054,8 +12148,11 @@
       <c r="I353">
         <v>0</v>
       </c>
-    </row>
-    <row r="354" spans="1:9" ht="18" customHeight="1">
+      <c r="J353" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" ht="18" customHeight="1">
       <c r="A354">
         <v>353</v>
       </c>
@@ -11083,8 +12180,11 @@
       <c r="I354">
         <v>0</v>
       </c>
-    </row>
-    <row r="355" spans="1:9" ht="18" customHeight="1">
+      <c r="J354" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:10" ht="18" customHeight="1">
       <c r="A355">
         <v>354</v>
       </c>
@@ -11112,8 +12212,11 @@
       <c r="I355">
         <v>0</v>
       </c>
-    </row>
-    <row r="356" spans="1:9" ht="18" customHeight="1">
+      <c r="J355" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10" ht="18" customHeight="1">
       <c r="A356">
         <v>355</v>
       </c>
@@ -11141,8 +12244,11 @@
       <c r="I356">
         <v>0</v>
       </c>
-    </row>
-    <row r="357" spans="1:9" ht="18" customHeight="1">
+      <c r="J356" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10" ht="18" customHeight="1">
       <c r="A357">
         <v>356</v>
       </c>
@@ -11170,8 +12276,11 @@
       <c r="I357">
         <v>0</v>
       </c>
-    </row>
-    <row r="358" spans="1:9" ht="18" customHeight="1">
+      <c r="J357" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:10" ht="18" customHeight="1">
       <c r="A358">
         <v>357</v>
       </c>
@@ -11199,8 +12308,11 @@
       <c r="I358">
         <v>0</v>
       </c>
-    </row>
-    <row r="359" spans="1:9" ht="18" customHeight="1">
+      <c r="J358" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:10" ht="18" customHeight="1">
       <c r="A359">
         <v>358</v>
       </c>
@@ -11228,8 +12340,11 @@
       <c r="I359">
         <v>0</v>
       </c>
-    </row>
-    <row r="360" spans="1:9" ht="18" customHeight="1">
+      <c r="J359" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10" ht="18" customHeight="1">
       <c r="A360">
         <v>359</v>
       </c>
@@ -11257,8 +12372,11 @@
       <c r="I360">
         <v>0</v>
       </c>
-    </row>
-    <row r="361" spans="1:9">
+      <c r="J360" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10">
       <c r="A361">
         <v>360</v>
       </c>
@@ -11286,8 +12404,11 @@
       <c r="I361">
         <v>0</v>
       </c>
-    </row>
-    <row r="362" spans="1:9">
+      <c r="J361" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10">
       <c r="A362">
         <v>361</v>
       </c>
@@ -11315,8 +12436,11 @@
       <c r="I362">
         <v>0</v>
       </c>
-    </row>
-    <row r="363" spans="1:9">
+      <c r="J362" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10">
       <c r="A363">
         <v>362</v>
       </c>
@@ -11344,8 +12468,11 @@
       <c r="I363">
         <v>0</v>
       </c>
-    </row>
-    <row r="364" spans="1:9">
+      <c r="J363" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10">
       <c r="A364">
         <v>363</v>
       </c>
@@ -11373,8 +12500,11 @@
       <c r="I364">
         <v>0</v>
       </c>
-    </row>
-    <row r="365" spans="1:9">
+      <c r="J364" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10">
       <c r="A365">
         <v>364</v>
       </c>
@@ -11402,8 +12532,11 @@
       <c r="I365">
         <v>0</v>
       </c>
-    </row>
-    <row r="366" spans="1:9">
+      <c r="J365" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10">
       <c r="A366">
         <v>365</v>
       </c>
@@ -11430,6 +12563,9 @@
       </c>
       <c r="I366">
         <v>0</v>
+      </c>
+      <c r="J366" s="12" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANGELA\Desktop\MiDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A95609-A5CA-4F35-B4DB-4BF3FA9C1646}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F66304-3A04-4207-8FCF-F23537932B2E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="7470" windowHeight="8640" tabRatio="906" xr2:uid="{7D6B2630-CDD6-4E4F-8803-3B7521F27F6B}"/>
   </bookViews>
@@ -461,7 +461,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -471,6 +470,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -511,13 +511,13 @@
   <autoFilter ref="A1:I366" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{8E80F481-58A9-4EF5-9BD3-4DE99E71B7AE}" name="N° DE OPERACIÓN"/>
-    <tableColumn id="5" xr3:uid="{59A9AB34-6356-455A-B8FD-E74723C9892D}" name="FECHA" dataDxfId="7" totalsRowDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{59A9AB34-6356-455A-B8FD-E74723C9892D}" name="FECHA" dataDxfId="7" totalsRowDxfId="6"/>
     <tableColumn id="6" xr3:uid="{66D4B823-3C30-44D5-A641-20D7BF6E166A}" name="TIPO DE CARGA"/>
     <tableColumn id="7" xr3:uid="{C3650C10-5CB4-45A7-9736-6A80A51D6F83}" name="TIPO DE SERVICIO"/>
-    <tableColumn id="15" xr3:uid="{99B5645B-5CD8-4042-833E-BE48D00BC86E}" name="LLENOS RECIBIDOS (EXPORTADOS)" dataDxfId="6" totalsRowDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{99B5645B-5CD8-4042-833E-BE48D00BC86E}" name="LLENOS RECIBIDOS (EXPORTADOS)" dataDxfId="5" totalsRowDxfId="4"/>
     <tableColumn id="18" xr3:uid="{33E6F7D3-8F24-4F60-BCE9-4590974B7832}" name="CONTENIDO"/>
-    <tableColumn id="21" xr3:uid="{D64B384B-46A0-483C-8C32-5474495F7791}" name="Peso Neto Exportado" dataDxfId="5" totalsRowDxfId="1"/>
-    <tableColumn id="22" xr3:uid="{CD599142-04A2-4632-8A98-CA3F9CF4F273}" name="DESTINO " dataDxfId="4" totalsRowDxfId="0"/>
+    <tableColumn id="21" xr3:uid="{D64B384B-46A0-483C-8C32-5474495F7791}" name="Peso Neto Exportado" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="22" xr3:uid="{CD599142-04A2-4632-8A98-CA3F9CF4F273}" name="DESTINO " dataDxfId="1" totalsRowDxfId="0"/>
     <tableColumn id="23" xr3:uid="{2EDED6B6-E583-4F20-89DA-9AA2F9B82EE1}" name="Peso Neto Importado "/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANGELA\Desktop\MiDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A3C61C-184C-41D2-975E-C967FED6F1B9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12997FE4-2A65-428B-8FA9-DD4DCD8D4ABA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="7470" windowHeight="8640" tabRatio="906" xr2:uid="{7D6B2630-CDD6-4E4F-8803-3B7521F27F6B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="106">
   <si>
     <t>N° DE OPERACIÓN</t>
   </si>
@@ -296,6 +296,54 @@
   <si>
     <t>Te instantaneo en Polvo y bebida energetica</t>
   </si>
+  <si>
+    <t xml:space="preserve">Frijol Mungo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">café verde </t>
+  </si>
+  <si>
+    <t xml:space="preserve">café vede </t>
+  </si>
+  <si>
+    <t>REPUBLICA CHECA</t>
+  </si>
+  <si>
+    <t>RUSIA</t>
+  </si>
+  <si>
+    <t>NO CONTENERIZADA (AEREA)</t>
+  </si>
+  <si>
+    <t>TAUREL</t>
+  </si>
+  <si>
+    <t>FIRST INTERNATIONAL</t>
+  </si>
+  <si>
+    <t>BARRAEZ &amp; ASOC.</t>
+  </si>
+  <si>
+    <t>FIRST INTERNATIONAL TRANSPORT</t>
+  </si>
+  <si>
+    <t>CHINA</t>
+  </si>
+  <si>
+    <t>PERU</t>
+  </si>
+  <si>
+    <t>PAISES BAJOS</t>
+  </si>
+  <si>
+    <t>4998.00</t>
+  </si>
+  <si>
+    <t>9834.00</t>
+  </si>
+  <si>
+    <t>5440.00</t>
+  </si>
 </sst>
 </file>
 
@@ -395,7 +443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -425,6 +473,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,19 +487,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -457,6 +498,19 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -493,21 +547,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}" name="Tabla1" displayName="Tabla1" ref="A1:J367" totalsRowShown="0" totalsRowDxfId="10">
-  <autoFilter ref="A1:J367" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}" name="Tabla1" displayName="Tabla1" ref="A1:J407" totalsRowCount="1" totalsRowDxfId="10">
+  <autoFilter ref="A1:J406" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{8E80F481-58A9-4EF5-9BD3-4DE99E71B7AE}" name="N° DE OPERACIÓN"/>
-    <tableColumn id="5" xr3:uid="{59A9AB34-6356-455A-B8FD-E74723C9892D}" name="FECHA" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{59A9AB34-6356-455A-B8FD-E74723C9892D}" name="FECHA" dataDxfId="9" totalsRowDxfId="4"/>
     <tableColumn id="6" xr3:uid="{66D4B823-3C30-44D5-A641-20D7BF6E166A}" name="TIPO DE CARGA"/>
     <tableColumn id="7" xr3:uid="{C3650C10-5CB4-45A7-9736-6A80A51D6F83}" name="TIPO DE SERVICIO"/>
-    <tableColumn id="15" xr3:uid="{99B5645B-5CD8-4042-833E-BE48D00BC86E}" name="LLENOS RECIBIDOS (EXPORTADOS)" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{99B5645B-5CD8-4042-833E-BE48D00BC86E}" name="LLENOS RECIBIDOS (EXPORTADOS)" dataDxfId="8" totalsRowDxfId="3"/>
     <tableColumn id="18" xr3:uid="{33E6F7D3-8F24-4F60-BCE9-4590974B7832}" name="CONTENIDO"/>
-    <tableColumn id="21" xr3:uid="{D64B384B-46A0-483C-8C32-5474495F7791}" name="Peso Neto Exportado" dataDxfId="0" totalsRowDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{D32BEFD5-B821-4C9D-9A95-EA7B65F72C1A}" name="Peso Neto Exportado2" dataDxfId="2" totalsRowDxfId="3">
+    <tableColumn id="21" xr3:uid="{D64B384B-46A0-483C-8C32-5474495F7791}" name="Peso Neto Exportado" dataDxfId="7" totalsRowDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{D32BEFD5-B821-4C9D-9A95-EA7B65F72C1A}" name="Peso Neto Exportado2" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="1">
       <calculatedColumnFormula>G2/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CD599142-04A2-4632-8A98-CA3F9CF4F273}" name="DESTINO " dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="23" xr3:uid="{2EDED6B6-E583-4F20-89DA-9AA2F9B82EE1}" name="Peso Neto Importado "/>
+    <tableColumn id="22" xr3:uid="{CD599142-04A2-4632-8A98-CA3F9CF4F273}" name="DESTINO " dataDxfId="5" totalsRowDxfId="0"/>
+    <tableColumn id="23" xr3:uid="{2EDED6B6-E583-4F20-89DA-9AA2F9B82EE1}" name="Peso Neto Importado " totalsRowFunction="custom">
+      <totalsRowFormula>SUBTOTAL(109,Tabla1[[Peso Neto Importado ]])/1000</totalsRowFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -830,7 +886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C559613-914B-4B50-8C5B-99B98A1D93DC}">
-  <dimension ref="A1:K367"/>
+  <dimension ref="A1:K407"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -840,7 +896,7 @@
     <col min="5" max="5" width="31" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.625" customWidth="1"/>
     <col min="7" max="7" width="16.75" style="2" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="19.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.875" style="13" customWidth="1"/>
     <col min="9" max="9" width="32" style="2" customWidth="1"/>
     <col min="10" max="10" width="19.375" customWidth="1"/>
     <col min="11" max="11" width="21.375" customWidth="1"/>
@@ -868,7 +924,7 @@
       <c r="G1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="13" t="s">
         <v>87</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -903,8 +959,8 @@
       <c r="G2" s="2">
         <v>378000</v>
       </c>
-      <c r="H2" s="2">
-        <f>G2/1000</f>
+      <c r="H2" s="13">
+        <f t="shared" ref="H2:H65" si="0">G2/1000</f>
         <v>378</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -939,8 +995,8 @@
       <c r="G3" s="2">
         <v>151200</v>
       </c>
-      <c r="H3" s="2">
-        <f>G3/1000</f>
+      <c r="H3" s="13">
+        <f t="shared" si="0"/>
         <v>151.19999999999999</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -975,8 +1031,8 @@
       <c r="G4" s="2">
         <v>252000</v>
       </c>
-      <c r="H4" s="2">
-        <f>G4/1000</f>
+      <c r="H4" s="13">
+        <f t="shared" si="0"/>
         <v>252</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -1011,8 +1067,8 @@
       <c r="G5" s="2">
         <v>252000</v>
       </c>
-      <c r="H5" s="2">
-        <f>G5/1000</f>
+      <c r="H5" s="13">
+        <f t="shared" si="0"/>
         <v>252</v>
       </c>
       <c r="I5" s="2" t="s">
@@ -1047,8 +1103,8 @@
       <c r="G6" s="2">
         <v>201600</v>
       </c>
-      <c r="H6" s="2">
-        <f>G6/1000</f>
+      <c r="H6" s="13">
+        <f t="shared" si="0"/>
         <v>201.6</v>
       </c>
       <c r="I6" s="2" t="s">
@@ -1083,8 +1139,8 @@
       <c r="G7" s="2">
         <v>50400</v>
       </c>
-      <c r="H7" s="2">
-        <f>G7/1000</f>
+      <c r="H7" s="13">
+        <f t="shared" si="0"/>
         <v>50.4</v>
       </c>
       <c r="I7" s="2" t="s">
@@ -1119,8 +1175,8 @@
       <c r="G8" s="2">
         <v>352800</v>
       </c>
-      <c r="H8" s="2">
-        <f>G8/1000</f>
+      <c r="H8" s="13">
+        <f t="shared" si="0"/>
         <v>352.8</v>
       </c>
       <c r="I8" s="2" t="s">
@@ -1155,8 +1211,8 @@
       <c r="G9" s="2">
         <v>252000</v>
       </c>
-      <c r="H9" s="2">
-        <f>G9/1000</f>
+      <c r="H9" s="13">
+        <f t="shared" si="0"/>
         <v>252</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -1191,8 +1247,8 @@
       <c r="G10" s="2">
         <v>126000</v>
       </c>
-      <c r="H10" s="2">
-        <f>G10/1000</f>
+      <c r="H10" s="13">
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
@@ -1227,8 +1283,8 @@
       <c r="G11" s="2">
         <v>252000</v>
       </c>
-      <c r="H11" s="2">
-        <f>G11/1000</f>
+      <c r="H11" s="13">
+        <f t="shared" si="0"/>
         <v>252</v>
       </c>
       <c r="I11" s="2" t="s">
@@ -1263,8 +1319,8 @@
       <c r="G12" s="2">
         <v>201600</v>
       </c>
-      <c r="H12" s="2">
-        <f>G12/1000</f>
+      <c r="H12" s="13">
+        <f t="shared" si="0"/>
         <v>201.6</v>
       </c>
       <c r="I12" s="2" t="s">
@@ -1299,8 +1355,8 @@
       <c r="G13" s="2">
         <v>50400</v>
       </c>
-      <c r="H13" s="2">
-        <f>G13/1000</f>
+      <c r="H13" s="13">
+        <f t="shared" si="0"/>
         <v>50.4</v>
       </c>
       <c r="I13" s="2" t="s">
@@ -1335,8 +1391,8 @@
       <c r="G14" s="2">
         <v>25200</v>
       </c>
-      <c r="H14" s="2">
-        <f>G14/1000</f>
+      <c r="H14" s="13">
+        <f t="shared" si="0"/>
         <v>25.2</v>
       </c>
       <c r="I14" s="2" t="s">
@@ -1371,8 +1427,8 @@
       <c r="G15" s="2">
         <v>126000</v>
       </c>
-      <c r="H15" s="2">
-        <f>G15/1000</f>
+      <c r="H15" s="13">
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
@@ -1407,8 +1463,8 @@
       <c r="G16" s="2">
         <v>25200</v>
       </c>
-      <c r="H16" s="2">
-        <f>G16/1000</f>
+      <c r="H16" s="13">
+        <f t="shared" si="0"/>
         <v>25.2</v>
       </c>
       <c r="I16" s="2" t="s">
@@ -1443,8 +1499,8 @@
       <c r="G17" s="2">
         <v>25200</v>
       </c>
-      <c r="H17" s="2">
-        <f>G17/1000</f>
+      <c r="H17" s="13">
+        <f t="shared" si="0"/>
         <v>25.2</v>
       </c>
       <c r="I17" s="2" t="s">
@@ -1479,8 +1535,8 @@
       <c r="G18" s="2">
         <v>75600</v>
       </c>
-      <c r="H18" s="2">
-        <f>G18/1000</f>
+      <c r="H18" s="13">
+        <f t="shared" si="0"/>
         <v>75.599999999999994</v>
       </c>
       <c r="I18" s="2" t="s">
@@ -1515,8 +1571,8 @@
       <c r="G19" s="2">
         <v>126000</v>
       </c>
-      <c r="H19" s="2">
-        <f>G19/1000</f>
+      <c r="H19" s="13">
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
@@ -1551,8 +1607,8 @@
       <c r="G20" s="2">
         <v>25200</v>
       </c>
-      <c r="H20" s="2">
-        <f>G20/1000</f>
+      <c r="H20" s="13">
+        <f t="shared" si="0"/>
         <v>25.2</v>
       </c>
       <c r="I20" s="2" t="s">
@@ -1587,8 +1643,8 @@
       <c r="G21" s="2">
         <v>302400</v>
       </c>
-      <c r="H21" s="2">
-        <f>G21/1000</f>
+      <c r="H21" s="13">
+        <f t="shared" si="0"/>
         <v>302.39999999999998</v>
       </c>
       <c r="I21" s="2" t="s">
@@ -1623,8 +1679,8 @@
       <c r="G22" s="2">
         <v>201600</v>
       </c>
-      <c r="H22" s="2">
-        <f>G22/1000</f>
+      <c r="H22" s="13">
+        <f t="shared" si="0"/>
         <v>201.6</v>
       </c>
       <c r="I22" s="2" t="s">
@@ -1659,8 +1715,8 @@
       <c r="G23" s="2">
         <v>126000</v>
       </c>
-      <c r="H23" s="2">
-        <f>G23/1000</f>
+      <c r="H23" s="13">
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="I23" s="2" t="s">
@@ -1695,8 +1751,8 @@
       <c r="G24" s="2">
         <v>100800</v>
       </c>
-      <c r="H24" s="2">
-        <f>G24/1000</f>
+      <c r="H24" s="13">
+        <f t="shared" si="0"/>
         <v>100.8</v>
       </c>
       <c r="I24" s="2" t="s">
@@ -1731,8 +1787,8 @@
       <c r="G25" s="2">
         <v>126000</v>
       </c>
-      <c r="H25" s="2">
-        <f>G25/1000</f>
+      <c r="H25" s="13">
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="I25" s="2" t="s">
@@ -1767,8 +1823,8 @@
       <c r="G26" s="2">
         <v>100800</v>
       </c>
-      <c r="H26" s="2">
-        <f>G26/1000</f>
+      <c r="H26" s="13">
+        <f t="shared" si="0"/>
         <v>100.8</v>
       </c>
       <c r="I26" s="2" t="s">
@@ -1803,8 +1859,8 @@
       <c r="G27" s="2">
         <v>100800</v>
       </c>
-      <c r="H27" s="2">
-        <f>G27/1000</f>
+      <c r="H27" s="13">
+        <f t="shared" si="0"/>
         <v>100.8</v>
       </c>
       <c r="I27" s="2" t="s">
@@ -1839,8 +1895,8 @@
       <c r="G28" s="2">
         <v>50400</v>
       </c>
-      <c r="H28" s="2">
-        <f>G28/1000</f>
+      <c r="H28" s="13">
+        <f t="shared" si="0"/>
         <v>50.4</v>
       </c>
       <c r="I28" s="2" t="s">
@@ -1875,8 +1931,8 @@
       <c r="G29" s="2">
         <v>50400</v>
       </c>
-      <c r="H29" s="2">
-        <f>G29/1000</f>
+      <c r="H29" s="13">
+        <f t="shared" si="0"/>
         <v>50.4</v>
       </c>
       <c r="I29" s="2" t="s">
@@ -1911,8 +1967,8 @@
       <c r="G30" s="2">
         <v>201600</v>
       </c>
-      <c r="H30" s="2">
-        <f>G30/1000</f>
+      <c r="H30" s="13">
+        <f t="shared" si="0"/>
         <v>201.6</v>
       </c>
       <c r="I30" s="2" t="s">
@@ -1947,8 +2003,8 @@
       <c r="G31" s="2">
         <v>126000</v>
       </c>
-      <c r="H31" s="2">
-        <f>G31/1000</f>
+      <c r="H31" s="13">
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="I31" s="2" t="s">
@@ -1983,8 +2039,8 @@
       <c r="G32" s="2">
         <v>50400</v>
       </c>
-      <c r="H32" s="2">
-        <f>G32/1000</f>
+      <c r="H32" s="13">
+        <f t="shared" si="0"/>
         <v>50.4</v>
       </c>
       <c r="I32" s="2" t="s">
@@ -2019,8 +2075,8 @@
       <c r="G33" s="2">
         <v>75600</v>
       </c>
-      <c r="H33" s="2">
-        <f>G33/1000</f>
+      <c r="H33" s="13">
+        <f t="shared" si="0"/>
         <v>75.599999999999994</v>
       </c>
       <c r="I33" s="2" t="s">
@@ -2055,8 +2111,8 @@
       <c r="G34" s="2">
         <v>126000</v>
       </c>
-      <c r="H34" s="2">
-        <f>G34/1000</f>
+      <c r="H34" s="13">
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="I34" s="2" t="s">
@@ -2091,8 +2147,8 @@
       <c r="G35" s="2">
         <v>17370</v>
       </c>
-      <c r="H35" s="2">
-        <f>G35/1000</f>
+      <c r="H35" s="13">
+        <f t="shared" si="0"/>
         <v>17.37</v>
       </c>
       <c r="I35" s="2" t="s">
@@ -2127,8 +2183,8 @@
       <c r="G36" s="2">
         <v>45758</v>
       </c>
-      <c r="H36" s="2">
-        <f>G36/1000</f>
+      <c r="H36" s="13">
+        <f t="shared" si="0"/>
         <v>45.758000000000003</v>
       </c>
       <c r="I36" s="2" t="s">
@@ -2163,8 +2219,8 @@
       <c r="G37" s="2">
         <v>88100</v>
       </c>
-      <c r="H37" s="2">
-        <f>G37/1000</f>
+      <c r="H37" s="13">
+        <f t="shared" si="0"/>
         <v>88.1</v>
       </c>
       <c r="I37" s="2" t="s">
@@ -2199,8 +2255,8 @@
       <c r="G38" s="2">
         <v>70200</v>
       </c>
-      <c r="H38" s="2">
-        <f>G38/1000</f>
+      <c r="H38" s="13">
+        <f t="shared" si="0"/>
         <v>70.2</v>
       </c>
       <c r="I38" s="2" t="s">
@@ -2235,8 +2291,8 @@
       <c r="G39" s="2">
         <v>23480</v>
       </c>
-      <c r="H39" s="2">
-        <f>G39/1000</f>
+      <c r="H39" s="13">
+        <f t="shared" si="0"/>
         <v>23.48</v>
       </c>
       <c r="I39" s="2" t="s">
@@ -2271,8 +2327,8 @@
       <c r="G40" s="2">
         <v>119220</v>
       </c>
-      <c r="H40" s="2">
-        <f>G40/1000</f>
+      <c r="H40" s="13">
+        <f t="shared" si="0"/>
         <v>119.22</v>
       </c>
       <c r="I40" s="2" t="s">
@@ -2307,8 +2363,8 @@
       <c r="G41" s="2">
         <v>75250</v>
       </c>
-      <c r="H41" s="2">
-        <f>G41/1000</f>
+      <c r="H41" s="13">
+        <f t="shared" si="0"/>
         <v>75.25</v>
       </c>
       <c r="I41" s="2" t="s">
@@ -2343,8 +2399,8 @@
       <c r="G42" s="2">
         <v>70766</v>
       </c>
-      <c r="H42" s="2">
-        <f>G42/1000</f>
+      <c r="H42" s="13">
+        <f t="shared" si="0"/>
         <v>70.766000000000005</v>
       </c>
       <c r="I42" s="2" t="s">
@@ -2379,8 +2435,8 @@
       <c r="G43" s="2">
         <v>211998</v>
       </c>
-      <c r="H43" s="2">
-        <f>G43/1000</f>
+      <c r="H43" s="13">
+        <f t="shared" si="0"/>
         <v>211.99799999999999</v>
       </c>
       <c r="I43" s="2" t="s">
@@ -2415,8 +2471,8 @@
       <c r="G44" s="2">
         <v>141332</v>
       </c>
-      <c r="H44" s="2">
-        <f>G44/1000</f>
+      <c r="H44" s="13">
+        <f t="shared" si="0"/>
         <v>141.33199999999999</v>
       </c>
       <c r="I44" s="2" t="s">
@@ -2451,8 +2507,8 @@
       <c r="G45" s="2">
         <v>70666</v>
       </c>
-      <c r="H45" s="2">
-        <f>G45/1000</f>
+      <c r="H45" s="13">
+        <f t="shared" si="0"/>
         <v>70.665999999999997</v>
       </c>
       <c r="I45" s="2" t="s">
@@ -2487,8 +2543,8 @@
       <c r="G46" s="2">
         <v>71000</v>
       </c>
-      <c r="H46" s="2">
-        <f>G46/1000</f>
+      <c r="H46" s="13">
+        <f t="shared" si="0"/>
         <v>71</v>
       </c>
       <c r="I46" s="2" t="s">
@@ -2523,8 +2579,8 @@
       <c r="G47" s="2">
         <v>23940</v>
       </c>
-      <c r="H47" s="2">
-        <f>G47/1000</f>
+      <c r="H47" s="13">
+        <f t="shared" si="0"/>
         <v>23.94</v>
       </c>
       <c r="I47" s="2" t="s">
@@ -2559,8 +2615,8 @@
       <c r="G48" s="2">
         <v>30136.400000000001</v>
       </c>
-      <c r="H48" s="2">
-        <f>G48/1000</f>
+      <c r="H48" s="13">
+        <f t="shared" si="0"/>
         <v>30.136400000000002</v>
       </c>
       <c r="I48" s="2" t="s">
@@ -2595,8 +2651,8 @@
       <c r="G49" s="2">
         <v>100190.32</v>
       </c>
-      <c r="H49" s="2">
-        <f>G49/1000</f>
+      <c r="H49" s="13">
+        <f t="shared" si="0"/>
         <v>100.19032000000001</v>
       </c>
       <c r="I49" s="2" t="s">
@@ -2631,8 +2687,8 @@
       <c r="G50" s="2">
         <v>100880</v>
       </c>
-      <c r="H50" s="2">
-        <f>G50/1000</f>
+      <c r="H50" s="13">
+        <f t="shared" si="0"/>
         <v>100.88</v>
       </c>
       <c r="I50" s="2" t="s">
@@ -2667,8 +2723,8 @@
       <c r="G51" s="2">
         <v>100800</v>
       </c>
-      <c r="H51" s="2">
-        <f>G51/1000</f>
+      <c r="H51" s="13">
+        <f t="shared" si="0"/>
         <v>100.8</v>
       </c>
       <c r="I51" s="2" t="s">
@@ -2703,8 +2759,8 @@
       <c r="G52" s="2">
         <v>201600</v>
       </c>
-      <c r="H52" s="2">
-        <f>G52/1000</f>
+      <c r="H52" s="13">
+        <f t="shared" si="0"/>
         <v>201.6</v>
       </c>
       <c r="I52" s="2" t="s">
@@ -2739,8 +2795,8 @@
       <c r="G53" s="2">
         <v>25200</v>
       </c>
-      <c r="H53" s="2">
-        <f>G53/1000</f>
+      <c r="H53" s="13">
+        <f t="shared" si="0"/>
         <v>25.2</v>
       </c>
       <c r="I53" s="2" t="s">
@@ -2775,8 +2831,8 @@
       <c r="G54" s="2">
         <v>75300</v>
       </c>
-      <c r="H54" s="2">
-        <f>G54/1000</f>
+      <c r="H54" s="13">
+        <f t="shared" si="0"/>
         <v>75.3</v>
       </c>
       <c r="I54" s="2" t="s">
@@ -2811,8 +2867,8 @@
       <c r="G55" s="2">
         <v>151200</v>
       </c>
-      <c r="H55" s="2">
-        <f>G55/1000</f>
+      <c r="H55" s="13">
+        <f t="shared" si="0"/>
         <v>151.19999999999999</v>
       </c>
       <c r="I55" s="2" t="s">
@@ -2847,8 +2903,8 @@
       <c r="G56" s="2">
         <v>25100</v>
       </c>
-      <c r="H56" s="2">
-        <f>G56/1000</f>
+      <c r="H56" s="13">
+        <f t="shared" si="0"/>
         <v>25.1</v>
       </c>
       <c r="I56" s="2" t="s">
@@ -2883,8 +2939,8 @@
       <c r="G57" s="2">
         <v>201600</v>
       </c>
-      <c r="H57" s="2">
-        <f>G57/1000</f>
+      <c r="H57" s="13">
+        <f t="shared" si="0"/>
         <v>201.6</v>
       </c>
       <c r="I57" s="2" t="s">
@@ -2919,8 +2975,8 @@
       <c r="G58" s="2">
         <v>28000</v>
       </c>
-      <c r="H58" s="2">
-        <f>G58/1000</f>
+      <c r="H58" s="13">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="I58" s="2" t="s">
@@ -2955,8 +3011,8 @@
       <c r="G59" s="2">
         <v>28000</v>
       </c>
-      <c r="H59" s="2">
-        <f>G59/1000</f>
+      <c r="H59" s="13">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="I59" s="2" t="s">
@@ -2991,8 +3047,8 @@
       <c r="G60" s="2">
         <v>28000</v>
       </c>
-      <c r="H60" s="2">
-        <f>G60/1000</f>
+      <c r="H60" s="13">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="I60" s="2" t="s">
@@ -3027,8 +3083,8 @@
       <c r="G61" s="2">
         <v>56280.000000000007</v>
       </c>
-      <c r="H61" s="2">
-        <f>G61/1000</f>
+      <c r="H61" s="13">
+        <f t="shared" si="0"/>
         <v>56.280000000000008</v>
       </c>
       <c r="I61" s="2" t="s">
@@ -3063,8 +3119,8 @@
       <c r="G62" s="2">
         <v>0</v>
       </c>
-      <c r="H62" s="2">
-        <f>G62/1000</f>
+      <c r="H62" s="13">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I62" t="s">
@@ -3099,8 +3155,8 @@
       <c r="G63" s="2">
         <v>25280</v>
       </c>
-      <c r="H63" s="2">
-        <f>G63/1000</f>
+      <c r="H63" s="13">
+        <f t="shared" si="0"/>
         <v>25.28</v>
       </c>
       <c r="I63" s="2" t="s">
@@ -3135,8 +3191,8 @@
       <c r="G64" s="2">
         <v>101220</v>
       </c>
-      <c r="H64" s="2">
-        <f>G64/1000</f>
+      <c r="H64" s="13">
+        <f t="shared" si="0"/>
         <v>101.22</v>
       </c>
       <c r="I64" s="2" t="s">
@@ -3171,8 +3227,8 @@
       <c r="G65" s="2">
         <v>25560</v>
       </c>
-      <c r="H65" s="2">
-        <f>G65/1000</f>
+      <c r="H65" s="13">
+        <f t="shared" si="0"/>
         <v>25.56</v>
       </c>
       <c r="I65" s="2" t="s">
@@ -3207,8 +3263,8 @@
       <c r="G66" s="2">
         <v>25360</v>
       </c>
-      <c r="H66" s="2">
-        <f>G66/1000</f>
+      <c r="H66" s="13">
+        <f t="shared" ref="H66:H129" si="1">G66/1000</f>
         <v>25.36</v>
       </c>
       <c r="I66" s="2" t="s">
@@ -3243,8 +3299,8 @@
       <c r="G67" s="2">
         <v>28880</v>
       </c>
-      <c r="H67" s="2">
-        <f>G67/1000</f>
+      <c r="H67" s="13">
+        <f t="shared" si="1"/>
         <v>28.88</v>
       </c>
       <c r="I67" s="2" t="s">
@@ -3279,8 +3335,8 @@
       <c r="G68" s="2">
         <v>50960</v>
       </c>
-      <c r="H68" s="2">
-        <f>G68/1000</f>
+      <c r="H68" s="13">
+        <f t="shared" si="1"/>
         <v>50.96</v>
       </c>
       <c r="I68" s="2" t="s">
@@ -3315,8 +3371,8 @@
       <c r="G69" s="2">
         <v>26820</v>
       </c>
-      <c r="H69" s="2">
-        <f>G69/1000</f>
+      <c r="H69" s="13">
+        <f t="shared" si="1"/>
         <v>26.82</v>
       </c>
       <c r="I69" s="2" t="s">
@@ -3351,8 +3407,8 @@
       <c r="G70" s="2">
         <v>0</v>
       </c>
-      <c r="H70" s="2">
-        <f>G70/1000</f>
+      <c r="H70" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I70" t="s">
@@ -3387,8 +3443,8 @@
       <c r="G71" s="2">
         <v>28000</v>
       </c>
-      <c r="H71" s="2">
-        <f>G71/1000</f>
+      <c r="H71" s="13">
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="I71" s="2" t="s">
@@ -3423,8 +3479,8 @@
       <c r="G72" s="2">
         <v>112560.00000000001</v>
       </c>
-      <c r="H72" s="2">
-        <f>G72/1000</f>
+      <c r="H72" s="13">
+        <f t="shared" si="1"/>
         <v>112.56000000000002</v>
       </c>
       <c r="I72" s="2" t="s">
@@ -3459,8 +3515,8 @@
       <c r="G73" s="2">
         <v>63100</v>
       </c>
-      <c r="H73" s="2">
-        <f>G73/1000</f>
+      <c r="H73" s="13">
+        <f t="shared" si="1"/>
         <v>63.1</v>
       </c>
       <c r="I73" s="2" t="s">
@@ -3495,8 +3551,8 @@
       <c r="G74" s="2">
         <v>253876</v>
       </c>
-      <c r="H74" s="2">
-        <f>G74/1000</f>
+      <c r="H74" s="13">
+        <f t="shared" si="1"/>
         <v>253.876</v>
       </c>
       <c r="I74" s="2" t="s">
@@ -3531,8 +3587,8 @@
       <c r="G75" s="2">
         <v>100860</v>
       </c>
-      <c r="H75" s="2">
-        <f>G75/1000</f>
+      <c r="H75" s="13">
+        <f t="shared" si="1"/>
         <v>100.86</v>
       </c>
       <c r="I75" s="2" t="s">
@@ -3567,8 +3623,8 @@
       <c r="G76" s="2">
         <v>25540</v>
       </c>
-      <c r="H76" s="2">
-        <f>G76/1000</f>
+      <c r="H76" s="13">
+        <f t="shared" si="1"/>
         <v>25.54</v>
       </c>
       <c r="I76" s="2" t="s">
@@ -3603,8 +3659,8 @@
       <c r="G77" s="2">
         <v>50500</v>
       </c>
-      <c r="H77" s="2">
-        <f>G77/1000</f>
+      <c r="H77" s="13">
+        <f t="shared" si="1"/>
         <v>50.5</v>
       </c>
       <c r="I77" s="2" t="s">
@@ -3639,8 +3695,8 @@
       <c r="G78" s="2">
         <v>50740</v>
       </c>
-      <c r="H78" s="2">
-        <f>G78/1000</f>
+      <c r="H78" s="13">
+        <f t="shared" si="1"/>
         <v>50.74</v>
       </c>
       <c r="I78" s="2" t="s">
@@ -3675,8 +3731,8 @@
       <c r="G79" s="2">
         <v>50580</v>
       </c>
-      <c r="H79" s="2">
-        <f>G79/1000</f>
+      <c r="H79" s="13">
+        <f t="shared" si="1"/>
         <v>50.58</v>
       </c>
       <c r="I79" s="2" t="s">
@@ -3711,8 +3767,8 @@
       <c r="G80" s="2">
         <v>151260</v>
       </c>
-      <c r="H80" s="2">
-        <f>G80/1000</f>
+      <c r="H80" s="13">
+        <f t="shared" si="1"/>
         <v>151.26</v>
       </c>
       <c r="I80" s="2" t="s">
@@ -3747,8 +3803,8 @@
       <c r="G81" s="2">
         <v>138530</v>
       </c>
-      <c r="H81" s="2">
-        <f>G81/1000</f>
+      <c r="H81" s="13">
+        <f t="shared" si="1"/>
         <v>138.53</v>
       </c>
       <c r="I81" s="2" t="s">
@@ -3783,8 +3839,8 @@
       <c r="G82" s="2">
         <v>253560</v>
       </c>
-      <c r="H82" s="2">
-        <f>G82/1000</f>
+      <c r="H82" s="13">
+        <f t="shared" si="1"/>
         <v>253.56</v>
       </c>
       <c r="I82" s="2" t="s">
@@ -3819,8 +3875,8 @@
       <c r="G83" s="2">
         <v>100860</v>
       </c>
-      <c r="H83" s="2">
-        <f>G83/1000</f>
+      <c r="H83" s="13">
+        <f t="shared" si="1"/>
         <v>100.86</v>
       </c>
       <c r="I83" s="2" t="s">
@@ -3855,8 +3911,8 @@
       <c r="G84" s="2">
         <v>379610</v>
       </c>
-      <c r="H84" s="2">
-        <f>G84/1000</f>
+      <c r="H84" s="13">
+        <f t="shared" si="1"/>
         <v>379.61</v>
       </c>
       <c r="I84" s="2" t="s">
@@ -3891,8 +3947,8 @@
       <c r="G85" s="2">
         <v>50420</v>
       </c>
-      <c r="H85" s="2">
-        <f>G85/1000</f>
+      <c r="H85" s="13">
+        <f t="shared" si="1"/>
         <v>50.42</v>
       </c>
       <c r="I85" s="2" t="s">
@@ -3927,8 +3983,8 @@
       <c r="G86" s="2">
         <v>252440</v>
       </c>
-      <c r="H86" s="2">
-        <f>G86/1000</f>
+      <c r="H86" s="13">
+        <f t="shared" si="1"/>
         <v>252.44</v>
       </c>
       <c r="I86" s="2" t="s">
@@ -3963,8 +4019,8 @@
       <c r="G87" s="2">
         <v>50400</v>
       </c>
-      <c r="H87" s="2">
-        <f>G87/1000</f>
+      <c r="H87" s="13">
+        <f t="shared" si="1"/>
         <v>50.4</v>
       </c>
       <c r="I87" s="2" t="s">
@@ -3999,8 +4055,8 @@
       <c r="G88" s="2">
         <v>0</v>
       </c>
-      <c r="H88" s="2">
-        <f>G88/1000</f>
+      <c r="H88" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I88" t="s">
@@ -4035,8 +4091,8 @@
       <c r="G89" s="2">
         <v>126760</v>
       </c>
-      <c r="H89" s="2">
-        <f>G89/1000</f>
+      <c r="H89" s="13">
+        <f t="shared" si="1"/>
         <v>126.76</v>
       </c>
       <c r="I89" s="2" t="s">
@@ -4071,8 +4127,8 @@
       <c r="G90" s="2">
         <v>227280</v>
       </c>
-      <c r="H90" s="2">
-        <f>G90/1000</f>
+      <c r="H90" s="13">
+        <f t="shared" si="1"/>
         <v>227.28</v>
       </c>
       <c r="I90" s="2" t="s">
@@ -4107,8 +4163,8 @@
       <c r="G91" s="2">
         <v>126160</v>
       </c>
-      <c r="H91" s="2">
-        <f>G91/1000</f>
+      <c r="H91" s="13">
+        <f t="shared" si="1"/>
         <v>126.16</v>
       </c>
       <c r="I91" s="2" t="s">
@@ -4143,8 +4199,8 @@
       <c r="G92" s="2">
         <v>126050</v>
       </c>
-      <c r="H92" s="2">
-        <f>G92/1000</f>
+      <c r="H92" s="13">
+        <f t="shared" si="1"/>
         <v>126.05</v>
       </c>
       <c r="I92" s="2" t="s">
@@ -4179,8 +4235,8 @@
       <c r="G93" s="2">
         <v>126360</v>
       </c>
-      <c r="H93" s="2">
-        <f>G93/1000</f>
+      <c r="H93" s="13">
+        <f t="shared" si="1"/>
         <v>126.36</v>
       </c>
       <c r="I93" s="2" t="s">
@@ -4215,8 +4271,8 @@
       <c r="G94" s="2">
         <v>25680</v>
       </c>
-      <c r="H94" s="2">
-        <f>G94/1000</f>
+      <c r="H94" s="13">
+        <f t="shared" si="1"/>
         <v>25.68</v>
       </c>
       <c r="I94" s="2" t="s">
@@ -4251,8 +4307,8 @@
       <c r="G95" s="2">
         <v>25380</v>
       </c>
-      <c r="H95" s="2">
-        <f>G95/1000</f>
+      <c r="H95" s="13">
+        <f t="shared" si="1"/>
         <v>25.38</v>
       </c>
       <c r="I95" s="2" t="s">
@@ -4287,8 +4343,8 @@
       <c r="G96" s="2">
         <v>25280</v>
       </c>
-      <c r="H96" s="2">
-        <f>G96/1000</f>
+      <c r="H96" s="13">
+        <f t="shared" si="1"/>
         <v>25.28</v>
       </c>
       <c r="I96" s="2" t="s">
@@ -4323,8 +4379,8 @@
       <c r="G97" s="2">
         <v>26660</v>
       </c>
-      <c r="H97" s="2">
-        <f>G97/1000</f>
+      <c r="H97" s="13">
+        <f t="shared" si="1"/>
         <v>26.66</v>
       </c>
       <c r="I97" s="2" t="s">
@@ -4359,8 +4415,8 @@
       <c r="G98" s="2">
         <v>157980</v>
       </c>
-      <c r="H98" s="2">
-        <f>G98/1000</f>
+      <c r="H98" s="13">
+        <f t="shared" si="1"/>
         <v>157.97999999999999</v>
       </c>
       <c r="I98" s="2" t="s">
@@ -4395,8 +4451,8 @@
       <c r="G99" s="2">
         <v>151740</v>
       </c>
-      <c r="H99" s="2">
-        <f>G99/1000</f>
+      <c r="H99" s="13">
+        <f t="shared" si="1"/>
         <v>151.74</v>
       </c>
       <c r="I99" s="2" t="s">
@@ -4431,8 +4487,8 @@
       <c r="G100" s="2">
         <v>75640</v>
       </c>
-      <c r="H100" s="2">
-        <f>G100/1000</f>
+      <c r="H100" s="13">
+        <f t="shared" si="1"/>
         <v>75.64</v>
       </c>
       <c r="I100" s="2" t="s">
@@ -4467,8 +4523,8 @@
       <c r="G101" s="2">
         <v>24200</v>
       </c>
-      <c r="H101" s="2">
-        <f>G101/1000</f>
+      <c r="H101" s="13">
+        <f t="shared" si="1"/>
         <v>24.2</v>
       </c>
       <c r="I101" s="2" t="s">
@@ -4503,8 +4559,8 @@
       <c r="G102" s="2">
         <v>0</v>
       </c>
-      <c r="H102" s="2">
-        <f>G102/1000</f>
+      <c r="H102" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I102" t="s">
@@ -4539,8 +4595,8 @@
       <c r="G103" s="2">
         <v>252080</v>
       </c>
-      <c r="H103" s="2">
-        <f>G103/1000</f>
+      <c r="H103" s="13">
+        <f t="shared" si="1"/>
         <v>252.08</v>
       </c>
       <c r="I103" s="2" t="s">
@@ -4575,8 +4631,8 @@
       <c r="G104" s="2">
         <v>100870</v>
       </c>
-      <c r="H104" s="2">
-        <f>G104/1000</f>
+      <c r="H104" s="13">
+        <f t="shared" si="1"/>
         <v>100.87</v>
       </c>
       <c r="I104" s="2" t="s">
@@ -4611,8 +4667,8 @@
       <c r="G105" s="2">
         <v>252980</v>
       </c>
-      <c r="H105" s="2">
-        <f>G105/1000</f>
+      <c r="H105" s="13">
+        <f t="shared" si="1"/>
         <v>252.98</v>
       </c>
       <c r="I105" s="2" t="s">
@@ -4647,8 +4703,8 @@
       <c r="G106" s="2">
         <v>126020</v>
       </c>
-      <c r="H106" s="2">
-        <f>G106/1000</f>
+      <c r="H106" s="13">
+        <f t="shared" si="1"/>
         <v>126.02</v>
       </c>
       <c r="I106" s="2" t="s">
@@ -4683,8 +4739,8 @@
       <c r="G107" s="2">
         <v>126580</v>
       </c>
-      <c r="H107" s="2">
-        <f>G107/1000</f>
+      <c r="H107" s="13">
+        <f t="shared" si="1"/>
         <v>126.58</v>
       </c>
       <c r="I107" s="2" t="s">
@@ -4719,8 +4775,8 @@
       <c r="G108" s="2">
         <v>21620</v>
       </c>
-      <c r="H108" s="2">
-        <f>G108/1000</f>
+      <c r="H108" s="13">
+        <f t="shared" si="1"/>
         <v>21.62</v>
       </c>
       <c r="I108" s="2" t="s">
@@ -4755,8 +4811,8 @@
       <c r="G109" s="2">
         <v>55310</v>
       </c>
-      <c r="H109" s="2">
-        <f>G109/1000</f>
+      <c r="H109" s="13">
+        <f t="shared" si="1"/>
         <v>55.31</v>
       </c>
       <c r="I109" s="2" t="s">
@@ -4791,8 +4847,8 @@
       <c r="G110" s="2">
         <v>100820</v>
       </c>
-      <c r="H110" s="2">
-        <f>G110/1000</f>
+      <c r="H110" s="13">
+        <f t="shared" si="1"/>
         <v>100.82</v>
       </c>
       <c r="I110" s="2" t="s">
@@ -4827,8 +4883,8 @@
       <c r="G111" s="2">
         <v>54560</v>
       </c>
-      <c r="H111" s="2">
-        <f>G111/1000</f>
+      <c r="H111" s="13">
+        <f t="shared" si="1"/>
         <v>54.56</v>
       </c>
       <c r="I111" s="2" t="s">
@@ -4863,8 +4919,8 @@
       <c r="G112" s="2">
         <v>21700</v>
       </c>
-      <c r="H112" s="2">
-        <f>G112/1000</f>
+      <c r="H112" s="13">
+        <f t="shared" si="1"/>
         <v>21.7</v>
       </c>
       <c r="I112" s="2" t="s">
@@ -4899,8 +4955,8 @@
       <c r="G113" s="2">
         <v>252290</v>
       </c>
-      <c r="H113" s="2">
-        <f>G113/1000</f>
+      <c r="H113" s="13">
+        <f t="shared" si="1"/>
         <v>252.29</v>
       </c>
       <c r="I113" s="2" t="s">
@@ -4935,8 +4991,8 @@
       <c r="G114" s="2">
         <v>252190</v>
       </c>
-      <c r="H114" s="2">
-        <f>G114/1000</f>
+      <c r="H114" s="13">
+        <f t="shared" si="1"/>
         <v>252.19</v>
       </c>
       <c r="I114" s="2" t="s">
@@ -4971,8 +5027,8 @@
       <c r="G115" s="2">
         <v>126360</v>
       </c>
-      <c r="H115" s="2">
-        <f>G115/1000</f>
+      <c r="H115" s="13">
+        <f t="shared" si="1"/>
         <v>126.36</v>
       </c>
       <c r="I115" s="2" t="s">
@@ -5007,8 +5063,8 @@
       <c r="G116" s="2">
         <v>100820</v>
       </c>
-      <c r="H116" s="2">
-        <f>G116/1000</f>
+      <c r="H116" s="13">
+        <f t="shared" si="1"/>
         <v>100.82</v>
       </c>
       <c r="I116" s="2" t="s">
@@ -5043,8 +5099,8 @@
       <c r="G117" s="2">
         <v>126240</v>
       </c>
-      <c r="H117" s="2">
-        <f>G117/1000</f>
+      <c r="H117" s="13">
+        <f t="shared" si="1"/>
         <v>126.24</v>
       </c>
       <c r="I117" s="2" t="s">
@@ -5079,8 +5135,8 @@
       <c r="G118" s="2">
         <v>126020</v>
       </c>
-      <c r="H118" s="2">
-        <f>G118/1000</f>
+      <c r="H118" s="13">
+        <f t="shared" si="1"/>
         <v>126.02</v>
       </c>
       <c r="I118" s="2" t="s">
@@ -5115,8 +5171,8 @@
       <c r="G119" s="2">
         <v>21700</v>
       </c>
-      <c r="H119" s="2">
-        <f>G119/1000</f>
+      <c r="H119" s="13">
+        <f t="shared" si="1"/>
         <v>21.7</v>
       </c>
       <c r="I119" s="2" t="s">
@@ -5151,8 +5207,8 @@
       <c r="G120" s="2">
         <v>151450</v>
       </c>
-      <c r="H120" s="2">
-        <f>G120/1000</f>
+      <c r="H120" s="13">
+        <f t="shared" si="1"/>
         <v>151.44999999999999</v>
       </c>
       <c r="I120" s="2" t="s">
@@ -5187,8 +5243,8 @@
       <c r="G121" s="2">
         <v>25200</v>
       </c>
-      <c r="H121" s="2">
-        <f>G121/1000</f>
+      <c r="H121" s="13">
+        <f t="shared" si="1"/>
         <v>25.2</v>
       </c>
       <c r="I121" s="2" t="s">
@@ -5223,8 +5279,8 @@
       <c r="G122" s="2">
         <v>126430</v>
       </c>
-      <c r="H122" s="2">
-        <f>G122/1000</f>
+      <c r="H122" s="13">
+        <f t="shared" si="1"/>
         <v>126.43</v>
       </c>
       <c r="I122" s="2" t="s">
@@ -5259,8 +5315,8 @@
       <c r="G123" s="2">
         <v>202110</v>
       </c>
-      <c r="H123" s="2">
-        <f>G123/1000</f>
+      <c r="H123" s="13">
+        <f t="shared" si="1"/>
         <v>202.11</v>
       </c>
       <c r="I123" s="2" t="s">
@@ -5295,8 +5351,8 @@
       <c r="G124" s="2">
         <v>126160</v>
       </c>
-      <c r="H124" s="2">
-        <f>G124/1000</f>
+      <c r="H124" s="13">
+        <f t="shared" si="1"/>
         <v>126.16</v>
       </c>
       <c r="I124" s="2" t="s">
@@ -5331,8 +5387,8 @@
       <c r="G125" s="2">
         <v>126090</v>
       </c>
-      <c r="H125" s="2">
-        <f>G125/1000</f>
+      <c r="H125" s="13">
+        <f t="shared" si="1"/>
         <v>126.09</v>
       </c>
       <c r="I125" s="2" t="s">
@@ -5367,8 +5423,8 @@
       <c r="G126" s="2">
         <v>119140</v>
       </c>
-      <c r="H126" s="2">
-        <f>G126/1000</f>
+      <c r="H126" s="13">
+        <f t="shared" si="1"/>
         <v>119.14</v>
       </c>
       <c r="I126" s="2" t="s">
@@ -5403,8 +5459,8 @@
       <c r="G127" s="2">
         <v>126070</v>
       </c>
-      <c r="H127" s="2">
-        <f>G127/1000</f>
+      <c r="H127" s="13">
+        <f t="shared" si="1"/>
         <v>126.07</v>
       </c>
       <c r="I127" s="2" t="s">
@@ -5439,8 +5495,8 @@
       <c r="G128" s="2">
         <v>76160</v>
       </c>
-      <c r="H128" s="2">
-        <f>G128/1000</f>
+      <c r="H128" s="13">
+        <f t="shared" si="1"/>
         <v>76.16</v>
       </c>
       <c r="I128" s="2" t="s">
@@ -5475,8 +5531,8 @@
       <c r="G129" s="2">
         <v>100950</v>
       </c>
-      <c r="H129" s="2">
-        <f>G129/1000</f>
+      <c r="H129" s="13">
+        <f t="shared" si="1"/>
         <v>100.95</v>
       </c>
       <c r="I129" s="2" t="s">
@@ -5511,8 +5567,8 @@
       <c r="G130" s="2">
         <v>126070</v>
       </c>
-      <c r="H130" s="2">
-        <f>G130/1000</f>
+      <c r="H130" s="13">
+        <f t="shared" ref="H130:H193" si="2">G130/1000</f>
         <v>126.07</v>
       </c>
       <c r="I130" s="2" t="s">
@@ -5547,8 +5603,8 @@
       <c r="G131" s="2">
         <v>126100</v>
       </c>
-      <c r="H131" s="2">
-        <f>G131/1000</f>
+      <c r="H131" s="13">
+        <f t="shared" si="2"/>
         <v>126.1</v>
       </c>
       <c r="I131" s="2" t="s">
@@ -5583,8 +5639,8 @@
       <c r="G132" s="2">
         <v>126000</v>
       </c>
-      <c r="H132" s="2">
-        <f>G132/1000</f>
+      <c r="H132" s="13">
+        <f t="shared" si="2"/>
         <v>126</v>
       </c>
       <c r="I132" s="2" t="s">
@@ -5619,8 +5675,8 @@
       <c r="G133" s="2">
         <v>75600</v>
       </c>
-      <c r="H133" s="2">
-        <f>G133/1000</f>
+      <c r="H133" s="13">
+        <f t="shared" si="2"/>
         <v>75.599999999999994</v>
       </c>
       <c r="I133" s="2" t="s">
@@ -5655,8 +5711,8 @@
       <c r="G134" s="2">
         <v>50400</v>
       </c>
-      <c r="H134" s="2">
-        <f>G134/1000</f>
+      <c r="H134" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I134" s="2" t="s">
@@ -5691,8 +5747,8 @@
       <c r="G135" s="2">
         <v>0</v>
       </c>
-      <c r="H135" s="2">
-        <f>G135/1000</f>
+      <c r="H135" s="13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I135" t="s">
@@ -5727,8 +5783,8 @@
       <c r="G136" s="2">
         <v>0</v>
       </c>
-      <c r="H136" s="2">
-        <f>G136/1000</f>
+      <c r="H136" s="13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I136" t="s">
@@ -5763,8 +5819,8 @@
       <c r="G137" s="2">
         <v>151200</v>
       </c>
-      <c r="H137" s="2">
-        <f>G137/1000</f>
+      <c r="H137" s="13">
+        <f t="shared" si="2"/>
         <v>151.19999999999999</v>
       </c>
       <c r="I137" s="2" t="s">
@@ -5799,8 +5855,8 @@
       <c r="G138" s="2">
         <v>25200</v>
       </c>
-      <c r="H138" s="2">
-        <f>G138/1000</f>
+      <c r="H138" s="13">
+        <f t="shared" si="2"/>
         <v>25.2</v>
       </c>
       <c r="I138" s="2" t="s">
@@ -5835,8 +5891,8 @@
       <c r="G139" s="2">
         <v>0</v>
       </c>
-      <c r="H139" s="2">
-        <f>G139/1000</f>
+      <c r="H139" s="13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I139" t="s">
@@ -5871,8 +5927,8 @@
       <c r="G140" s="2">
         <v>100800</v>
       </c>
-      <c r="H140" s="2">
-        <f>G140/1000</f>
+      <c r="H140" s="13">
+        <f t="shared" si="2"/>
         <v>100.8</v>
       </c>
       <c r="I140" s="2" t="s">
@@ -5907,8 +5963,8 @@
       <c r="G141" s="2">
         <v>48788</v>
       </c>
-      <c r="H141" s="2">
-        <f>G141/1000</f>
+      <c r="H141" s="13">
+        <f t="shared" si="2"/>
         <v>48.787999999999997</v>
       </c>
       <c r="I141" s="2" t="s">
@@ -5943,8 +5999,8 @@
       <c r="G142" s="2">
         <v>126000</v>
       </c>
-      <c r="H142" s="2">
-        <f>G142/1000</f>
+      <c r="H142" s="13">
+        <f t="shared" si="2"/>
         <v>126</v>
       </c>
       <c r="I142" s="2" t="s">
@@ -5979,8 +6035,8 @@
       <c r="G143" s="2">
         <v>25200</v>
       </c>
-      <c r="H143" s="2">
-        <f>G143/1000</f>
+      <c r="H143" s="13">
+        <f t="shared" si="2"/>
         <v>25.2</v>
       </c>
       <c r="I143" s="2" t="s">
@@ -6015,8 +6071,8 @@
       <c r="G144" s="2">
         <v>7854</v>
       </c>
-      <c r="H144" s="2">
-        <f>G144/1000</f>
+      <c r="H144" s="13">
+        <f t="shared" si="2"/>
         <v>7.8540000000000001</v>
       </c>
       <c r="I144" s="2" t="s">
@@ -6051,8 +6107,8 @@
       <c r="G145" s="2">
         <v>252000</v>
       </c>
-      <c r="H145" s="2">
-        <f>G145/1000</f>
+      <c r="H145" s="13">
+        <f t="shared" si="2"/>
         <v>252</v>
       </c>
       <c r="I145" s="2" t="s">
@@ -6087,8 +6143,8 @@
       <c r="G146" s="2">
         <v>50400</v>
       </c>
-      <c r="H146" s="2">
-        <f>G146/1000</f>
+      <c r="H146" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I146" s="2" t="s">
@@ -6123,8 +6179,8 @@
       <c r="G147" s="2">
         <v>50400</v>
       </c>
-      <c r="H147" s="2">
-        <f>G147/1000</f>
+      <c r="H147" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I147" s="2" t="s">
@@ -6159,8 +6215,8 @@
       <c r="G148" s="2">
         <v>126000</v>
       </c>
-      <c r="H148" s="2">
-        <f>G148/1000</f>
+      <c r="H148" s="13">
+        <f t="shared" si="2"/>
         <v>126</v>
       </c>
       <c r="I148" s="2" t="s">
@@ -6195,8 +6251,8 @@
       <c r="G149" s="2">
         <v>75600</v>
       </c>
-      <c r="H149" s="2">
-        <f>G149/1000</f>
+      <c r="H149" s="13">
+        <f t="shared" si="2"/>
         <v>75.599999999999994</v>
       </c>
       <c r="I149" s="2" t="s">
@@ -6231,8 +6287,8 @@
       <c r="G150" s="2">
         <v>50400</v>
       </c>
-      <c r="H150" s="2">
-        <f>G150/1000</f>
+      <c r="H150" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I150" s="2" t="s">
@@ -6267,8 +6323,8 @@
       <c r="G151" s="2">
         <v>252000</v>
       </c>
-      <c r="H151" s="2">
-        <f>G151/1000</f>
+      <c r="H151" s="13">
+        <f t="shared" si="2"/>
         <v>252</v>
       </c>
       <c r="I151" s="2" t="s">
@@ -6303,8 +6359,8 @@
       <c r="G152" s="2">
         <v>252000</v>
       </c>
-      <c r="H152" s="2">
-        <f>G152/1000</f>
+      <c r="H152" s="13">
+        <f t="shared" si="2"/>
         <v>252</v>
       </c>
       <c r="I152" s="2" t="s">
@@ -6339,8 +6395,8 @@
       <c r="G153" s="2">
         <v>50400</v>
       </c>
-      <c r="H153" s="2">
-        <f>G153/1000</f>
+      <c r="H153" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I153" s="2" t="s">
@@ -6375,8 +6431,8 @@
       <c r="G154" s="2">
         <v>126000</v>
       </c>
-      <c r="H154" s="2">
-        <f>G154/1000</f>
+      <c r="H154" s="13">
+        <f t="shared" si="2"/>
         <v>126</v>
       </c>
       <c r="I154" s="2" t="s">
@@ -6411,8 +6467,8 @@
       <c r="G155" s="2">
         <v>252000</v>
       </c>
-      <c r="H155" s="2">
-        <f>G155/1000</f>
+      <c r="H155" s="13">
+        <f t="shared" si="2"/>
         <v>252</v>
       </c>
       <c r="I155" s="2" t="s">
@@ -6447,8 +6503,8 @@
       <c r="G156" s="2">
         <v>252000</v>
       </c>
-      <c r="H156" s="2">
-        <f>G156/1000</f>
+      <c r="H156" s="13">
+        <f t="shared" si="2"/>
         <v>252</v>
       </c>
       <c r="I156" s="2" t="s">
@@ -6483,8 +6539,8 @@
       <c r="G157" s="2">
         <v>25200</v>
       </c>
-      <c r="H157" s="2">
-        <f>G157/1000</f>
+      <c r="H157" s="13">
+        <f t="shared" si="2"/>
         <v>25.2</v>
       </c>
       <c r="I157" s="2" t="s">
@@ -6519,8 +6575,8 @@
       <c r="G158" s="2">
         <v>75600</v>
       </c>
-      <c r="H158" s="2">
-        <f>G158/1000</f>
+      <c r="H158" s="13">
+        <f t="shared" si="2"/>
         <v>75.599999999999994</v>
       </c>
       <c r="I158" s="2" t="s">
@@ -6555,8 +6611,8 @@
       <c r="G159" s="2">
         <v>50400</v>
       </c>
-      <c r="H159" s="2">
-        <f>G159/1000</f>
+      <c r="H159" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I159" s="2" t="s">
@@ -6591,8 +6647,8 @@
       <c r="G160" s="2">
         <v>0</v>
       </c>
-      <c r="H160" s="2">
-        <f>G160/1000</f>
+      <c r="H160" s="13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I160" t="s">
@@ -6627,8 +6683,8 @@
       <c r="G161" s="2">
         <v>252000</v>
       </c>
-      <c r="H161" s="2">
-        <f>G161/1000</f>
+      <c r="H161" s="13">
+        <f t="shared" si="2"/>
         <v>252</v>
       </c>
       <c r="I161" s="2" t="s">
@@ -6663,8 +6719,8 @@
       <c r="G162" s="2">
         <v>0</v>
       </c>
-      <c r="H162" s="2">
-        <f>G162/1000</f>
+      <c r="H162" s="13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I162" t="s">
@@ -6699,8 +6755,8 @@
       <c r="G163" s="2">
         <v>0</v>
       </c>
-      <c r="H163" s="2">
-        <f>G163/1000</f>
+      <c r="H163" s="13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I163" t="s">
@@ -6735,8 +6791,8 @@
       <c r="G164" s="2">
         <v>50400</v>
       </c>
-      <c r="H164" s="2">
-        <f>G164/1000</f>
+      <c r="H164" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I164" s="2" t="s">
@@ -6771,8 +6827,8 @@
       <c r="G165" s="2">
         <v>50400</v>
       </c>
-      <c r="H165" s="2">
-        <f>G165/1000</f>
+      <c r="H165" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I165" s="2" t="s">
@@ -6807,8 +6863,8 @@
       <c r="G166" s="2">
         <v>151200</v>
       </c>
-      <c r="H166" s="2">
-        <f>G166/1000</f>
+      <c r="H166" s="13">
+        <f t="shared" si="2"/>
         <v>151.19999999999999</v>
       </c>
       <c r="I166" s="2" t="s">
@@ -6843,8 +6899,8 @@
       <c r="G167" s="2">
         <v>25960</v>
       </c>
-      <c r="H167" s="2">
-        <f>G167/1000</f>
+      <c r="H167" s="13">
+        <f t="shared" si="2"/>
         <v>25.96</v>
       </c>
       <c r="I167" s="2" t="s">
@@ -6879,8 +6935,8 @@
       <c r="G168" s="2">
         <v>8938</v>
       </c>
-      <c r="H168" s="2">
-        <f>G168/1000</f>
+      <c r="H168" s="13">
+        <f t="shared" si="2"/>
         <v>8.9380000000000006</v>
       </c>
       <c r="I168" s="2" t="s">
@@ -6915,8 +6971,8 @@
       <c r="G169" s="2">
         <v>100800</v>
       </c>
-      <c r="H169" s="2">
-        <f>G169/1000</f>
+      <c r="H169" s="13">
+        <f t="shared" si="2"/>
         <v>100.8</v>
       </c>
       <c r="I169" s="2" t="s">
@@ -6951,8 +7007,8 @@
       <c r="G170" s="2">
         <v>75600</v>
       </c>
-      <c r="H170" s="2">
-        <f>G170/1000</f>
+      <c r="H170" s="13">
+        <f t="shared" si="2"/>
         <v>75.599999999999994</v>
       </c>
       <c r="I170" s="2" t="s">
@@ -6987,8 +7043,8 @@
       <c r="G171" s="2">
         <v>62900</v>
       </c>
-      <c r="H171" s="2">
-        <f>G171/1000</f>
+      <c r="H171" s="13">
+        <f t="shared" si="2"/>
         <v>62.9</v>
       </c>
       <c r="I171" s="2" t="s">
@@ -7023,8 +7079,8 @@
       <c r="G172" s="2">
         <v>102290</v>
       </c>
-      <c r="H172" s="2">
-        <f>G172/1000</f>
+      <c r="H172" s="13">
+        <f t="shared" si="2"/>
         <v>102.29</v>
       </c>
       <c r="I172" s="2" t="s">
@@ -7059,8 +7115,8 @@
       <c r="G173" s="2">
         <v>189720</v>
       </c>
-      <c r="H173" s="2">
-        <f>G173/1000</f>
+      <c r="H173" s="13">
+        <f t="shared" si="2"/>
         <v>189.72</v>
       </c>
       <c r="I173" s="2" t="s">
@@ -7095,8 +7151,8 @@
       <c r="G174" s="2">
         <v>36870</v>
       </c>
-      <c r="H174" s="2">
-        <f>G174/1000</f>
+      <c r="H174" s="13">
+        <f t="shared" si="2"/>
         <v>36.869999999999997</v>
       </c>
       <c r="I174" s="2" t="s">
@@ -7131,8 +7187,8 @@
       <c r="G175" s="2">
         <v>40000</v>
       </c>
-      <c r="H175" s="2">
-        <f>G175/1000</f>
+      <c r="H175" s="13">
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="I175" s="2" t="s">
@@ -7167,8 +7223,8 @@
       <c r="G176" s="2">
         <v>25200</v>
       </c>
-      <c r="H176" s="2">
-        <f>G176/1000</f>
+      <c r="H176" s="13">
+        <f t="shared" si="2"/>
         <v>25.2</v>
       </c>
       <c r="I176" s="2" t="s">
@@ -7203,8 +7259,8 @@
       <c r="G177" s="2">
         <v>53900</v>
       </c>
-      <c r="H177" s="2">
-        <f>G177/1000</f>
+      <c r="H177" s="13">
+        <f t="shared" si="2"/>
         <v>53.9</v>
       </c>
       <c r="I177" s="2" t="s">
@@ -7239,8 +7295,8 @@
       <c r="G178" s="2">
         <v>28010</v>
       </c>
-      <c r="H178" s="2">
-        <f>G178/1000</f>
+      <c r="H178" s="13">
+        <f t="shared" si="2"/>
         <v>28.01</v>
       </c>
       <c r="I178" s="2" t="s">
@@ -7275,8 +7331,8 @@
       <c r="G179" s="2">
         <v>118248</v>
       </c>
-      <c r="H179" s="2">
-        <f>G179/1000</f>
+      <c r="H179" s="13">
+        <f t="shared" si="2"/>
         <v>118.248</v>
       </c>
       <c r="I179" s="2" t="s">
@@ -7311,8 +7367,8 @@
       <c r="G180" s="2">
         <v>5036</v>
       </c>
-      <c r="H180" s="2">
-        <f>G180/1000</f>
+      <c r="H180" s="13">
+        <f t="shared" si="2"/>
         <v>5.0359999999999996</v>
       </c>
       <c r="I180" s="2" t="s">
@@ -7347,8 +7403,8 @@
       <c r="G181" s="2">
         <v>28150</v>
       </c>
-      <c r="H181" s="2">
-        <f>G181/1000</f>
+      <c r="H181" s="13">
+        <f t="shared" si="2"/>
         <v>28.15</v>
       </c>
       <c r="I181" s="2" t="s">
@@ -7383,8 +7439,8 @@
       <c r="G182" s="2">
         <v>28150</v>
       </c>
-      <c r="H182" s="2">
-        <f>G182/1000</f>
+      <c r="H182" s="13">
+        <f t="shared" si="2"/>
         <v>28.15</v>
       </c>
       <c r="I182" s="2" t="s">
@@ -7419,8 +7475,8 @@
       <c r="G183" s="2">
         <v>60400</v>
       </c>
-      <c r="H183" s="2">
-        <f>G183/1000</f>
+      <c r="H183" s="13">
+        <f t="shared" si="2"/>
         <v>60.4</v>
       </c>
       <c r="I183" s="2" t="s">
@@ -7455,8 +7511,8 @@
       <c r="G184" s="2">
         <v>127173.11</v>
       </c>
-      <c r="H184" s="2">
-        <f>G184/1000</f>
+      <c r="H184" s="13">
+        <f t="shared" si="2"/>
         <v>127.17310999999999</v>
       </c>
       <c r="I184" s="2" t="s">
@@ -7491,8 +7547,8 @@
       <c r="G185" s="2">
         <v>80908</v>
       </c>
-      <c r="H185" s="2">
-        <f>G185/1000</f>
+      <c r="H185" s="13">
+        <f t="shared" si="2"/>
         <v>80.908000000000001</v>
       </c>
       <c r="I185" s="2" t="s">
@@ -7527,8 +7583,8 @@
       <c r="G186" s="2">
         <v>126000</v>
       </c>
-      <c r="H186" s="2">
-        <f>G186/1000</f>
+      <c r="H186" s="13">
+        <f t="shared" si="2"/>
         <v>126</v>
       </c>
       <c r="I186" s="2" t="s">
@@ -7563,8 +7619,8 @@
       <c r="G187" s="2">
         <v>101730</v>
       </c>
-      <c r="H187" s="2">
-        <f>G187/1000</f>
+      <c r="H187" s="13">
+        <f t="shared" si="2"/>
         <v>101.73</v>
       </c>
       <c r="I187" s="2" t="s">
@@ -7599,8 +7655,8 @@
       <c r="G188" s="2">
         <v>74919.81</v>
       </c>
-      <c r="H188" s="2">
-        <f>G188/1000</f>
+      <c r="H188" s="13">
+        <f t="shared" si="2"/>
         <v>74.919809999999998</v>
       </c>
       <c r="I188" s="2" t="s">
@@ -7635,8 +7691,8 @@
       <c r="G189" s="2">
         <v>175344.14</v>
       </c>
-      <c r="H189" s="2">
-        <f>G189/1000</f>
+      <c r="H189" s="13">
+        <f t="shared" si="2"/>
         <v>175.34414000000001</v>
       </c>
       <c r="I189" s="2" t="s">
@@ -7671,8 +7727,8 @@
       <c r="G190" s="2">
         <v>118629.95</v>
       </c>
-      <c r="H190" s="2">
-        <f>G190/1000</f>
+      <c r="H190" s="13">
+        <f t="shared" si="2"/>
         <v>118.62994999999999</v>
       </c>
       <c r="I190" s="2" t="s">
@@ -7707,8 +7763,8 @@
       <c r="G191" s="2">
         <v>50400</v>
       </c>
-      <c r="H191" s="2">
-        <f>G191/1000</f>
+      <c r="H191" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I191" s="2" t="s">
@@ -7743,8 +7799,8 @@
       <c r="G192" s="2">
         <v>126080</v>
       </c>
-      <c r="H192" s="2">
-        <f>G192/1000</f>
+      <c r="H192" s="13">
+        <f t="shared" si="2"/>
         <v>126.08</v>
       </c>
       <c r="I192" s="2" t="s">
@@ -7779,8 +7835,8 @@
       <c r="G193" s="2">
         <v>50440</v>
       </c>
-      <c r="H193" s="2">
-        <f>G193/1000</f>
+      <c r="H193" s="13">
+        <f t="shared" si="2"/>
         <v>50.44</v>
       </c>
       <c r="I193" s="2" t="s">
@@ -7815,8 +7871,8 @@
       <c r="G194" s="2">
         <v>25220</v>
       </c>
-      <c r="H194" s="2">
-        <f>G194/1000</f>
+      <c r="H194" s="13">
+        <f t="shared" ref="H194:H257" si="3">G194/1000</f>
         <v>25.22</v>
       </c>
       <c r="I194" s="2" t="s">
@@ -7851,8 +7907,8 @@
       <c r="G195" s="2">
         <v>67566.14</v>
       </c>
-      <c r="H195" s="2">
-        <f>G195/1000</f>
+      <c r="H195" s="13">
+        <f t="shared" si="3"/>
         <v>67.566140000000004</v>
       </c>
       <c r="I195" s="2" t="s">
@@ -7887,8 +7943,8 @@
       <c r="G196" s="2">
         <v>50440</v>
       </c>
-      <c r="H196" s="2">
-        <f>G196/1000</f>
+      <c r="H196" s="13">
+        <f t="shared" si="3"/>
         <v>50.44</v>
       </c>
       <c r="I196" s="2" t="s">
@@ -7923,8 +7979,8 @@
       <c r="G197" s="2">
         <v>50200</v>
       </c>
-      <c r="H197" s="2">
-        <f>G197/1000</f>
+      <c r="H197" s="13">
+        <f t="shared" si="3"/>
         <v>50.2</v>
       </c>
       <c r="I197" s="2" t="s">
@@ -7959,8 +8015,8 @@
       <c r="G198" s="2">
         <v>25690</v>
       </c>
-      <c r="H198" s="2">
-        <f>G198/1000</f>
+      <c r="H198" s="13">
+        <f t="shared" si="3"/>
         <v>25.69</v>
       </c>
       <c r="I198" s="2" t="s">
@@ -7995,8 +8051,8 @@
       <c r="G199" s="2">
         <v>25100</v>
       </c>
-      <c r="H199" s="2">
-        <f>G199/1000</f>
+      <c r="H199" s="13">
+        <f t="shared" si="3"/>
         <v>25.1</v>
       </c>
       <c r="I199" s="2" t="s">
@@ -8031,8 +8087,8 @@
       <c r="G200" s="2">
         <v>51208</v>
       </c>
-      <c r="H200" s="2">
-        <f>G200/1000</f>
+      <c r="H200" s="13">
+        <f t="shared" si="3"/>
         <v>51.207999999999998</v>
       </c>
       <c r="I200" s="2" t="s">
@@ -8067,8 +8123,8 @@
       <c r="G201" s="2">
         <v>70000</v>
       </c>
-      <c r="H201" s="2">
-        <f>G201/1000</f>
+      <c r="H201" s="13">
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="I201" s="2" t="s">
@@ -8103,8 +8159,8 @@
       <c r="G202" s="2">
         <v>39558</v>
       </c>
-      <c r="H202" s="2">
-        <f>G202/1000</f>
+      <c r="H202" s="13">
+        <f t="shared" si="3"/>
         <v>39.558</v>
       </c>
       <c r="I202" s="2" t="s">
@@ -8139,8 +8195,8 @@
       <c r="G203" s="2">
         <v>22000</v>
       </c>
-      <c r="H203" s="2">
-        <f>G203/1000</f>
+      <c r="H203" s="13">
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="I203" s="2" t="s">
@@ -8175,8 +8231,8 @@
       <c r="G204" s="2">
         <v>100660</v>
       </c>
-      <c r="H204" s="2">
-        <f>G204/1000</f>
+      <c r="H204" s="13">
+        <f t="shared" si="3"/>
         <v>100.66</v>
       </c>
       <c r="I204" s="2" t="s">
@@ -8211,8 +8267,8 @@
       <c r="G205" s="2">
         <v>36600</v>
       </c>
-      <c r="H205" s="2">
-        <f>G205/1000</f>
+      <c r="H205" s="13">
+        <f t="shared" si="3"/>
         <v>36.6</v>
       </c>
       <c r="I205" s="2" t="s">
@@ -8247,8 +8303,8 @@
       <c r="G206" s="2">
         <v>50080</v>
       </c>
-      <c r="H206" s="2">
-        <f>G206/1000</f>
+      <c r="H206" s="13">
+        <f t="shared" si="3"/>
         <v>50.08</v>
       </c>
       <c r="I206" s="2" t="s">
@@ -8283,8 +8339,8 @@
       <c r="G207" s="2">
         <v>68160</v>
       </c>
-      <c r="H207" s="2">
-        <f>G207/1000</f>
+      <c r="H207" s="13">
+        <f t="shared" si="3"/>
         <v>68.16</v>
       </c>
       <c r="I207" s="2" t="s">
@@ -8319,8 +8375,8 @@
       <c r="G208" s="2">
         <v>43300</v>
       </c>
-      <c r="H208" s="2">
-        <f>G208/1000</f>
+      <c r="H208" s="13">
+        <f t="shared" si="3"/>
         <v>43.3</v>
       </c>
       <c r="I208" s="2" t="s">
@@ -8355,8 +8411,8 @@
       <c r="G209" s="2">
         <v>25060</v>
       </c>
-      <c r="H209" s="2">
-        <f>G209/1000</f>
+      <c r="H209" s="13">
+        <f t="shared" si="3"/>
         <v>25.06</v>
       </c>
       <c r="I209" s="2" t="s">
@@ -8391,8 +8447,8 @@
       <c r="G210" s="2">
         <v>125380</v>
       </c>
-      <c r="H210" s="2">
-        <f>G210/1000</f>
+      <c r="H210" s="13">
+        <f t="shared" si="3"/>
         <v>125.38</v>
       </c>
       <c r="I210" s="2" t="s">
@@ -8427,8 +8483,8 @@
       <c r="G211" s="2">
         <v>251000</v>
       </c>
-      <c r="H211" s="2">
-        <f>G211/1000</f>
+      <c r="H211" s="13">
+        <f t="shared" si="3"/>
         <v>251</v>
       </c>
       <c r="I211" s="2" t="s">
@@ -8463,8 +8519,8 @@
       <c r="G212" s="2">
         <v>25080</v>
       </c>
-      <c r="H212" s="2">
-        <f>G212/1000</f>
+      <c r="H212" s="13">
+        <f t="shared" si="3"/>
         <v>25.08</v>
       </c>
       <c r="I212" s="2" t="s">
@@ -8499,8 +8555,8 @@
       <c r="G213" s="2">
         <v>22710</v>
       </c>
-      <c r="H213" s="2">
-        <f>G213/1000</f>
+      <c r="H213" s="13">
+        <f t="shared" si="3"/>
         <v>22.71</v>
       </c>
       <c r="I213" s="2" t="s">
@@ -8535,8 +8591,8 @@
       <c r="G214" s="2">
         <v>47340</v>
       </c>
-      <c r="H214" s="2">
-        <f>G214/1000</f>
+      <c r="H214" s="13">
+        <f t="shared" si="3"/>
         <v>47.34</v>
       </c>
       <c r="I214" s="2" t="s">
@@ -8571,8 +8627,8 @@
       <c r="G215" s="2">
         <v>125780</v>
       </c>
-      <c r="H215" s="2">
-        <f>G215/1000</f>
+      <c r="H215" s="13">
+        <f t="shared" si="3"/>
         <v>125.78</v>
       </c>
       <c r="I215" s="2" t="s">
@@ -8607,8 +8663,8 @@
       <c r="G216" s="2">
         <v>250960</v>
       </c>
-      <c r="H216" s="2">
-        <f>G216/1000</f>
+      <c r="H216" s="13">
+        <f t="shared" si="3"/>
         <v>250.96</v>
       </c>
       <c r="I216" s="2" t="s">
@@ -8643,8 +8699,8 @@
       <c r="G217" s="2">
         <v>250720</v>
       </c>
-      <c r="H217" s="2">
-        <f>G217/1000</f>
+      <c r="H217" s="13">
+        <f t="shared" si="3"/>
         <v>250.72</v>
       </c>
       <c r="I217" s="2" t="s">
@@ -8679,8 +8735,8 @@
       <c r="G218" s="2">
         <v>5374.8</v>
       </c>
-      <c r="H218" s="2">
-        <f>G218/1000</f>
+      <c r="H218" s="13">
+        <f t="shared" si="3"/>
         <v>5.3748000000000005</v>
       </c>
       <c r="I218" s="2" t="s">
@@ -8715,8 +8771,8 @@
       <c r="G219" s="2">
         <v>72160</v>
       </c>
-      <c r="H219" s="2">
-        <f>G219/1000</f>
+      <c r="H219" s="13">
+        <f t="shared" si="3"/>
         <v>72.16</v>
       </c>
       <c r="I219" s="2" t="s">
@@ -8751,8 +8807,8 @@
       <c r="G220" s="2">
         <v>50200</v>
       </c>
-      <c r="H220" s="2">
-        <f>G220/1000</f>
+      <c r="H220" s="13">
+        <f t="shared" si="3"/>
         <v>50.2</v>
       </c>
       <c r="I220" s="2" t="s">
@@ -8787,8 +8843,8 @@
       <c r="G221" s="2">
         <v>40480</v>
       </c>
-      <c r="H221" s="2">
-        <f>G221/1000</f>
+      <c r="H221" s="13">
+        <f t="shared" si="3"/>
         <v>40.479999999999997</v>
       </c>
       <c r="I221" s="2" t="s">
@@ -8823,8 +8879,8 @@
       <c r="G222" s="2">
         <v>50040</v>
       </c>
-      <c r="H222" s="2">
-        <f>G222/1000</f>
+      <c r="H222" s="13">
+        <f t="shared" si="3"/>
         <v>50.04</v>
       </c>
       <c r="I222" s="2" t="s">
@@ -8859,8 +8915,8 @@
       <c r="G223" s="2">
         <v>50200</v>
       </c>
-      <c r="H223" s="2">
-        <f>G223/1000</f>
+      <c r="H223" s="13">
+        <f t="shared" si="3"/>
         <v>50.2</v>
       </c>
       <c r="I223" s="2" t="s">
@@ -8895,8 +8951,8 @@
       <c r="G224" s="2">
         <v>45440</v>
       </c>
-      <c r="H224" s="2">
-        <f>G224/1000</f>
+      <c r="H224" s="13">
+        <f t="shared" si="3"/>
         <v>45.44</v>
       </c>
       <c r="I224" s="2" t="s">
@@ -8931,8 +8987,8 @@
       <c r="G225" s="2">
         <v>40000</v>
       </c>
-      <c r="H225" s="2">
-        <f>G225/1000</f>
+      <c r="H225" s="13">
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="I225" s="2" t="s">
@@ -8967,8 +9023,8 @@
       <c r="G226" s="2">
         <v>75000</v>
       </c>
-      <c r="H226" s="2">
-        <f>G226/1000</f>
+      <c r="H226" s="13">
+        <f t="shared" si="3"/>
         <v>75</v>
       </c>
       <c r="I226" s="2" t="s">
@@ -9003,8 +9059,8 @@
       <c r="G227" s="2">
         <v>50000</v>
       </c>
-      <c r="H227" s="2">
-        <f>G227/1000</f>
+      <c r="H227" s="13">
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="I227" s="2" t="s">
@@ -9039,8 +9095,8 @@
       <c r="G228" s="2">
         <v>23250</v>
       </c>
-      <c r="H228" s="2">
-        <f>G228/1000</f>
+      <c r="H228" s="13">
+        <f t="shared" si="3"/>
         <v>23.25</v>
       </c>
       <c r="I228" s="2" t="s">
@@ -9075,8 +9131,8 @@
       <c r="G229" s="2">
         <v>75000</v>
       </c>
-      <c r="H229" s="2">
-        <f>G229/1000</f>
+      <c r="H229" s="13">
+        <f t="shared" si="3"/>
         <v>75</v>
       </c>
       <c r="I229" s="2" t="s">
@@ -9111,8 +9167,8 @@
       <c r="G230" s="2">
         <v>50200</v>
       </c>
-      <c r="H230" s="2">
-        <f>G230/1000</f>
+      <c r="H230" s="13">
+        <f t="shared" si="3"/>
         <v>50.2</v>
       </c>
       <c r="I230" s="2" t="s">
@@ -9147,8 +9203,8 @@
       <c r="G231" s="2">
         <v>251000</v>
       </c>
-      <c r="H231" s="2">
-        <f>G231/1000</f>
+      <c r="H231" s="13">
+        <f t="shared" si="3"/>
         <v>251</v>
       </c>
       <c r="I231" s="2" t="s">
@@ -9183,8 +9239,8 @@
       <c r="G232" s="2">
         <v>75300</v>
       </c>
-      <c r="H232" s="2">
-        <f>G232/1000</f>
+      <c r="H232" s="13">
+        <f t="shared" si="3"/>
         <v>75.3</v>
       </c>
       <c r="I232" s="2" t="s">
@@ -9219,8 +9275,8 @@
       <c r="G233" s="2">
         <v>125500</v>
       </c>
-      <c r="H233" s="2">
-        <f>G233/1000</f>
+      <c r="H233" s="13">
+        <f t="shared" si="3"/>
         <v>125.5</v>
       </c>
       <c r="I233" s="2" t="s">
@@ -9255,8 +9311,8 @@
       <c r="G234" s="2">
         <v>251000</v>
       </c>
-      <c r="H234" s="2">
-        <f>G234/1000</f>
+      <c r="H234" s="13">
+        <f t="shared" si="3"/>
         <v>251</v>
       </c>
       <c r="I234" s="2" t="s">
@@ -9291,8 +9347,8 @@
       <c r="G235" s="2">
         <v>251000</v>
       </c>
-      <c r="H235" s="2">
-        <f>G235/1000</f>
+      <c r="H235" s="13">
+        <f t="shared" si="3"/>
         <v>251</v>
       </c>
       <c r="I235" s="2" t="s">
@@ -9327,8 +9383,8 @@
       <c r="G236" s="2">
         <v>251000</v>
       </c>
-      <c r="H236" s="2">
-        <f>G236/1000</f>
+      <c r="H236" s="13">
+        <f t="shared" si="3"/>
         <v>251</v>
       </c>
       <c r="I236" s="2" t="s">
@@ -9363,8 +9419,8 @@
       <c r="G237" s="2">
         <v>23680</v>
       </c>
-      <c r="H237" s="2">
-        <f>G237/1000</f>
+      <c r="H237" s="13">
+        <f t="shared" si="3"/>
         <v>23.68</v>
       </c>
       <c r="I237" s="2" t="s">
@@ -9399,8 +9455,8 @@
       <c r="G238" s="2">
         <v>1500</v>
       </c>
-      <c r="H238" s="2">
-        <f>G238/1000</f>
+      <c r="H238" s="13">
+        <f t="shared" si="3"/>
         <v>1.5</v>
       </c>
       <c r="I238" s="2" t="s">
@@ -9435,8 +9491,8 @@
       <c r="G239" s="2">
         <v>50200</v>
       </c>
-      <c r="H239" s="2">
-        <f>G239/1000</f>
+      <c r="H239" s="13">
+        <f t="shared" si="3"/>
         <v>50.2</v>
       </c>
       <c r="I239" s="2" t="s">
@@ -9471,8 +9527,8 @@
       <c r="G240" s="2">
         <v>200800</v>
       </c>
-      <c r="H240" s="2">
-        <f>G240/1000</f>
+      <c r="H240" s="13">
+        <f t="shared" si="3"/>
         <v>200.8</v>
       </c>
       <c r="I240" s="2" t="s">
@@ -9507,8 +9563,8 @@
       <c r="G241" s="2">
         <v>100400</v>
       </c>
-      <c r="H241" s="2">
-        <f>G241/1000</f>
+      <c r="H241" s="13">
+        <f t="shared" si="3"/>
         <v>100.4</v>
       </c>
       <c r="I241" s="2" t="s">
@@ -9543,8 +9599,8 @@
       <c r="G242" s="2">
         <v>75300</v>
       </c>
-      <c r="H242" s="2">
-        <f>G242/1000</f>
+      <c r="H242" s="13">
+        <f t="shared" si="3"/>
         <v>75.3</v>
       </c>
       <c r="I242" s="2" t="s">
@@ -9579,8 +9635,8 @@
       <c r="G243" s="2">
         <v>25840</v>
       </c>
-      <c r="H243" s="2">
-        <f>G243/1000</f>
+      <c r="H243" s="13">
+        <f t="shared" si="3"/>
         <v>25.84</v>
       </c>
       <c r="I243" s="2" t="s">
@@ -9615,8 +9671,8 @@
       <c r="G244" s="2">
         <v>251000</v>
       </c>
-      <c r="H244" s="2">
-        <f>G244/1000</f>
+      <c r="H244" s="13">
+        <f t="shared" si="3"/>
         <v>251</v>
       </c>
       <c r="I244" s="2" t="s">
@@ -9651,8 +9707,8 @@
       <c r="G245" s="2">
         <v>150600</v>
       </c>
-      <c r="H245" s="2">
-        <f>G245/1000</f>
+      <c r="H245" s="13">
+        <f t="shared" si="3"/>
         <v>150.6</v>
       </c>
       <c r="I245" s="2" t="s">
@@ -9687,8 +9743,8 @@
       <c r="G246" s="2">
         <v>50040</v>
       </c>
-      <c r="H246" s="2">
-        <f>G246/1000</f>
+      <c r="H246" s="13">
+        <f t="shared" si="3"/>
         <v>50.04</v>
       </c>
       <c r="I246" s="2" t="s">
@@ -9723,8 +9779,8 @@
       <c r="G247" s="2">
         <v>9529</v>
       </c>
-      <c r="H247" s="2">
-        <f>G247/1000</f>
+      <c r="H247" s="13">
+        <f t="shared" si="3"/>
         <v>9.5289999999999999</v>
       </c>
       <c r="I247" s="2" t="s">
@@ -9759,8 +9815,8 @@
       <c r="G248" s="2">
         <v>367500</v>
       </c>
-      <c r="H248" s="2">
-        <f>G248/1000</f>
+      <c r="H248" s="13">
+        <f t="shared" si="3"/>
         <v>367.5</v>
       </c>
       <c r="I248" s="2" t="s">
@@ -9795,8 +9851,8 @@
       <c r="G249" s="2">
         <v>0</v>
       </c>
-      <c r="H249" s="2">
-        <f>G249/1000</f>
+      <c r="H249" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I249" t="s">
@@ -9831,8 +9887,8 @@
       <c r="G250" s="2">
         <v>0</v>
       </c>
-      <c r="H250" s="2">
-        <f>G250/1000</f>
+      <c r="H250" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I250" s="2" t="s">
@@ -9867,8 +9923,8 @@
       <c r="G251" s="2">
         <v>0</v>
       </c>
-      <c r="H251" s="2">
-        <f>G251/1000</f>
+      <c r="H251" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I251" s="2" t="s">
@@ -9903,8 +9959,8 @@
       <c r="G252" s="2">
         <v>0</v>
       </c>
-      <c r="H252" s="2">
-        <f>G252/1000</f>
+      <c r="H252" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I252" s="2" t="s">
@@ -9939,8 +9995,8 @@
       <c r="G253" s="2">
         <v>0</v>
       </c>
-      <c r="H253" s="2">
-        <f>G253/1000</f>
+      <c r="H253" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I253" s="2" t="s">
@@ -9975,8 +10031,8 @@
       <c r="G254" s="2">
         <v>0</v>
       </c>
-      <c r="H254" s="2">
-        <f>G254/1000</f>
+      <c r="H254" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I254" s="2" t="s">
@@ -10011,8 +10067,8 @@
       <c r="G255" s="2">
         <v>0</v>
       </c>
-      <c r="H255" s="2">
-        <f>G255/1000</f>
+      <c r="H255" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I255" s="2" t="s">
@@ -10047,8 +10103,8 @@
       <c r="G256" s="2">
         <v>0</v>
       </c>
-      <c r="H256" s="2">
-        <f>G256/1000</f>
+      <c r="H256" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I256" s="2" t="s">
@@ -10083,8 +10139,8 @@
       <c r="G257" s="2">
         <v>0</v>
       </c>
-      <c r="H257" s="2">
-        <f>G257/1000</f>
+      <c r="H257" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I257" s="2" t="s">
@@ -10119,8 +10175,8 @@
       <c r="G258" s="2">
         <v>0</v>
       </c>
-      <c r="H258" s="2">
-        <f>G258/1000</f>
+      <c r="H258" s="13">
+        <f t="shared" ref="H258:H321" si="4">G258/1000</f>
         <v>0</v>
       </c>
       <c r="I258" s="2" t="s">
@@ -10155,8 +10211,8 @@
       <c r="G259" s="2">
         <v>0</v>
       </c>
-      <c r="H259" s="2">
-        <f>G259/1000</f>
+      <c r="H259" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I259" t="s">
@@ -10191,8 +10247,8 @@
       <c r="G260" s="2">
         <v>0</v>
       </c>
-      <c r="H260" s="2">
-        <f>G260/1000</f>
+      <c r="H260" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I260" t="s">
@@ -10227,8 +10283,8 @@
       <c r="G261" s="2">
         <v>0</v>
       </c>
-      <c r="H261" s="2">
-        <f>G261/1000</f>
+      <c r="H261" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I261" t="s">
@@ -10263,8 +10319,8 @@
       <c r="G262" s="2">
         <v>140000</v>
       </c>
-      <c r="H262" s="2">
-        <f>G262/1000</f>
+      <c r="H262" s="13">
+        <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="I262" s="2" t="s">
@@ -10299,8 +10355,8 @@
       <c r="G263" s="2">
         <v>0</v>
       </c>
-      <c r="H263" s="2">
-        <f>G263/1000</f>
+      <c r="H263" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I263" t="s">
@@ -10335,8 +10391,8 @@
       <c r="G264" s="2">
         <v>44760</v>
       </c>
-      <c r="H264" s="2">
-        <f>G264/1000</f>
+      <c r="H264" s="13">
+        <f t="shared" si="4"/>
         <v>44.76</v>
       </c>
       <c r="I264" s="2" t="s">
@@ -10371,8 +10427,8 @@
       <c r="G265" s="2">
         <v>25140</v>
       </c>
-      <c r="H265" s="2">
-        <f>G265/1000</f>
+      <c r="H265" s="13">
+        <f t="shared" si="4"/>
         <v>25.14</v>
       </c>
       <c r="I265" s="2" t="s">
@@ -10407,8 +10463,8 @@
       <c r="G266" s="2">
         <v>44360</v>
       </c>
-      <c r="H266" s="2">
-        <f>G266/1000</f>
+      <c r="H266" s="13">
+        <f t="shared" si="4"/>
         <v>44.36</v>
       </c>
       <c r="I266" s="2" t="s">
@@ -10443,8 +10499,8 @@
       <c r="G267" s="2">
         <v>70000</v>
       </c>
-      <c r="H267" s="2">
-        <f>G267/1000</f>
+      <c r="H267" s="13">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I267" s="2" t="s">
@@ -10479,8 +10535,8 @@
       <c r="G268" s="2">
         <v>25140</v>
       </c>
-      <c r="H268" s="2">
-        <f>G268/1000</f>
+      <c r="H268" s="13">
+        <f t="shared" si="4"/>
         <v>25.14</v>
       </c>
       <c r="I268" s="2" t="s">
@@ -10515,8 +10571,8 @@
       <c r="G269" s="2">
         <v>75000</v>
       </c>
-      <c r="H269" s="2">
-        <f>G269/1000</f>
+      <c r="H269" s="13">
+        <f t="shared" si="4"/>
         <v>75</v>
       </c>
       <c r="I269" s="2" t="s">
@@ -10551,8 +10607,8 @@
       <c r="G270" s="2">
         <v>25000</v>
       </c>
-      <c r="H270" s="2">
-        <f>G270/1000</f>
+      <c r="H270" s="13">
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="I270" s="2" t="s">
@@ -10587,8 +10643,8 @@
       <c r="G271" s="2">
         <v>125000</v>
       </c>
-      <c r="H271" s="2">
-        <f>G271/1000</f>
+      <c r="H271" s="13">
+        <f t="shared" si="4"/>
         <v>125</v>
       </c>
       <c r="I271" s="2" t="s">
@@ -10623,8 +10679,8 @@
       <c r="G272" s="2">
         <v>43000</v>
       </c>
-      <c r="H272" s="2">
-        <f>G272/1000</f>
+      <c r="H272" s="13">
+        <f t="shared" si="4"/>
         <v>43</v>
       </c>
       <c r="I272" s="2" t="s">
@@ -10659,8 +10715,8 @@
       <c r="G273" s="2">
         <v>70000</v>
       </c>
-      <c r="H273" s="2">
-        <f>G273/1000</f>
+      <c r="H273" s="13">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I273" s="2" t="s">
@@ -10695,8 +10751,8 @@
       <c r="G274" s="2">
         <v>125000</v>
       </c>
-      <c r="H274" s="2">
-        <f>G274/1000</f>
+      <c r="H274" s="13">
+        <f t="shared" si="4"/>
         <v>125</v>
       </c>
       <c r="I274" s="2" t="s">
@@ -10731,8 +10787,8 @@
       <c r="G275" s="2">
         <v>70000</v>
       </c>
-      <c r="H275" s="2">
-        <f>G275/1000</f>
+      <c r="H275" s="13">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I275" s="2" t="s">
@@ -10767,8 +10823,8 @@
       <c r="G276" s="2">
         <v>250000</v>
       </c>
-      <c r="H276" s="2">
-        <f>G276/1000</f>
+      <c r="H276" s="13">
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
       <c r="I276" s="2" t="s">
@@ -10803,8 +10859,8 @@
       <c r="G277" s="2">
         <v>9000</v>
       </c>
-      <c r="H277" s="2">
-        <f>G277/1000</f>
+      <c r="H277" s="13">
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="I277" s="2" t="s">
@@ -10839,8 +10895,8 @@
       <c r="G278" s="2">
         <v>19200</v>
       </c>
-      <c r="H278" s="2">
-        <f>G278/1000</f>
+      <c r="H278" s="13">
+        <f t="shared" si="4"/>
         <v>19.2</v>
       </c>
       <c r="I278" s="2" t="s">
@@ -10875,8 +10931,8 @@
       <c r="G279" s="2">
         <v>250000</v>
       </c>
-      <c r="H279" s="2">
-        <f>G279/1000</f>
+      <c r="H279" s="13">
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
       <c r="I279" s="2" t="s">
@@ -10911,8 +10967,8 @@
       <c r="G280" s="2">
         <v>140000</v>
       </c>
-      <c r="H280" s="2">
-        <f>G280/1000</f>
+      <c r="H280" s="13">
+        <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="I280" s="2" t="s">
@@ -10947,8 +11003,8 @@
       <c r="G281" s="2">
         <v>125000</v>
       </c>
-      <c r="H281" s="2">
-        <f>G281/1000</f>
+      <c r="H281" s="13">
+        <f t="shared" si="4"/>
         <v>125</v>
       </c>
       <c r="I281" s="2" t="s">
@@ -10983,8 +11039,8 @@
       <c r="G282" s="2">
         <v>19250</v>
       </c>
-      <c r="H282" s="2">
-        <f>G282/1000</f>
+      <c r="H282" s="13">
+        <f t="shared" si="4"/>
         <v>19.25</v>
       </c>
       <c r="I282" s="2" t="s">
@@ -11019,8 +11075,8 @@
       <c r="G283" s="2">
         <v>25000</v>
       </c>
-      <c r="H283" s="2">
-        <f>G283/1000</f>
+      <c r="H283" s="13">
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="I283" s="2" t="s">
@@ -11055,8 +11111,8 @@
       <c r="G284" s="2">
         <v>150000</v>
       </c>
-      <c r="H284" s="2">
-        <f>G284/1000</f>
+      <c r="H284" s="13">
+        <f t="shared" si="4"/>
         <v>150</v>
       </c>
       <c r="I284" s="2" t="s">
@@ -11091,8 +11147,8 @@
       <c r="G285" s="2">
         <v>75000</v>
       </c>
-      <c r="H285" s="2">
-        <f>G285/1000</f>
+      <c r="H285" s="13">
+        <f t="shared" si="4"/>
         <v>75</v>
       </c>
       <c r="I285" s="2" t="s">
@@ -11127,8 +11183,8 @@
       <c r="G286" s="2">
         <v>70000</v>
       </c>
-      <c r="H286" s="2">
-        <f>G286/1000</f>
+      <c r="H286" s="13">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I286" s="2" t="s">
@@ -11163,8 +11219,8 @@
       <c r="G287" s="2">
         <v>75000</v>
       </c>
-      <c r="H287" s="2">
-        <f>G287/1000</f>
+      <c r="H287" s="13">
+        <f t="shared" si="4"/>
         <v>75</v>
       </c>
       <c r="I287" s="2" t="s">
@@ -11199,8 +11255,8 @@
       <c r="G288" s="2">
         <v>0</v>
       </c>
-      <c r="H288" s="2">
-        <f>G288/1000</f>
+      <c r="H288" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I288" s="2" t="s">
@@ -11235,8 +11291,8 @@
       <c r="G289" s="2">
         <v>0</v>
       </c>
-      <c r="H289" s="2">
-        <f>G289/1000</f>
+      <c r="H289" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I289" s="2" t="s">
@@ -11271,8 +11327,8 @@
       <c r="G290" s="2">
         <v>0</v>
       </c>
-      <c r="H290" s="2">
-        <f>G290/1000</f>
+      <c r="H290" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I290" s="2" t="s">
@@ -11307,8 +11363,8 @@
       <c r="G291" s="2">
         <v>0</v>
       </c>
-      <c r="H291" s="2">
-        <f>G291/1000</f>
+      <c r="H291" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I291" s="2" t="s">
@@ -11343,8 +11399,8 @@
       <c r="G292" s="2">
         <v>0</v>
       </c>
-      <c r="H292" s="2">
-        <f>G292/1000</f>
+      <c r="H292" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I292" s="2" t="s">
@@ -11379,8 +11435,8 @@
       <c r="G293" s="2">
         <v>0</v>
       </c>
-      <c r="H293" s="2">
-        <f>G293/1000</f>
+      <c r="H293" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I293" s="2" t="s">
@@ -11415,8 +11471,8 @@
       <c r="G294" s="2">
         <v>0</v>
       </c>
-      <c r="H294" s="2">
-        <f>G294/1000</f>
+      <c r="H294" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I294" s="2" t="s">
@@ -11451,8 +11507,8 @@
       <c r="G295" s="2">
         <v>0</v>
       </c>
-      <c r="H295" s="2">
-        <f>G295/1000</f>
+      <c r="H295" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I295" s="2" t="s">
@@ -11487,8 +11543,8 @@
       <c r="G296" s="2">
         <v>0</v>
       </c>
-      <c r="H296" s="2">
-        <f>G296/1000</f>
+      <c r="H296" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I296" s="2" t="s">
@@ -11523,8 +11579,8 @@
       <c r="G297" s="2">
         <v>140000</v>
       </c>
-      <c r="H297" s="2">
-        <f>G297/1000</f>
+      <c r="H297" s="13">
+        <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="I297" s="2" t="s">
@@ -11559,8 +11615,8 @@
       <c r="G298" s="2">
         <v>24600</v>
       </c>
-      <c r="H298" s="2">
-        <f>G298/1000</f>
+      <c r="H298" s="13">
+        <f t="shared" si="4"/>
         <v>24.6</v>
       </c>
       <c r="I298" s="2" t="s">
@@ -11595,8 +11651,8 @@
       <c r="G299" s="2">
         <v>44360</v>
       </c>
-      <c r="H299" s="2">
-        <f>G299/1000</f>
+      <c r="H299" s="13">
+        <f t="shared" si="4"/>
         <v>44.36</v>
       </c>
       <c r="I299" s="2" t="s">
@@ -11631,8 +11687,8 @@
       <c r="G300" s="2">
         <v>5000000</v>
       </c>
-      <c r="H300" s="2">
-        <f>G300/1000</f>
+      <c r="H300" s="13">
+        <f t="shared" si="4"/>
         <v>5000</v>
       </c>
       <c r="I300" s="2" t="s">
@@ -11667,8 +11723,8 @@
       <c r="G301" s="2">
         <v>25000</v>
       </c>
-      <c r="H301" s="2">
-        <f>G301/1000</f>
+      <c r="H301" s="13">
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="I301" s="2" t="s">
@@ -11703,8 +11759,8 @@
       <c r="G302" s="2">
         <v>24600</v>
       </c>
-      <c r="H302" s="2">
-        <f>G302/1000</f>
+      <c r="H302" s="13">
+        <f t="shared" si="4"/>
         <v>24.6</v>
       </c>
       <c r="I302" s="2" t="s">
@@ -11739,8 +11795,8 @@
       <c r="G303" s="2">
         <v>70000</v>
       </c>
-      <c r="H303" s="2">
-        <f>G303/1000</f>
+      <c r="H303" s="13">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I303" s="2" t="s">
@@ -11775,8 +11831,8 @@
       <c r="G304" s="2">
         <v>70000</v>
       </c>
-      <c r="H304" s="2">
-        <f>G304/1000</f>
+      <c r="H304" s="13">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I304" s="2" t="s">
@@ -11811,8 +11867,8 @@
       <c r="G305" s="2">
         <v>70000</v>
       </c>
-      <c r="H305" s="2">
-        <f>G305/1000</f>
+      <c r="H305" s="13">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I305" s="2" t="s">
@@ -11847,8 +11903,8 @@
       <c r="G306" s="2">
         <v>4000</v>
       </c>
-      <c r="H306" s="2">
-        <f>G306/1000</f>
+      <c r="H306" s="13">
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="I306" s="2" t="s">
@@ -11883,8 +11939,8 @@
       <c r="G307" s="2">
         <v>22180</v>
       </c>
-      <c r="H307" s="2">
-        <f>G307/1000</f>
+      <c r="H307" s="13">
+        <f t="shared" si="4"/>
         <v>22.18</v>
       </c>
       <c r="I307" s="2" t="s">
@@ -11919,8 +11975,8 @@
       <c r="G308" s="2">
         <v>19250</v>
       </c>
-      <c r="H308" s="2">
-        <f>G308/1000</f>
+      <c r="H308" s="13">
+        <f t="shared" si="4"/>
         <v>19.25</v>
       </c>
       <c r="I308" s="2" t="s">
@@ -11955,8 +12011,8 @@
       <c r="G309" s="2">
         <v>0</v>
       </c>
-      <c r="H309" s="2">
-        <f>G309/1000</f>
+      <c r="H309" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I309" s="2" t="s">
@@ -11991,8 +12047,8 @@
       <c r="G310" s="2">
         <v>0</v>
       </c>
-      <c r="H310" s="2">
-        <f>G310/1000</f>
+      <c r="H310" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I310" s="2" t="s">
@@ -12027,8 +12083,8 @@
       <c r="G311" s="2">
         <v>0</v>
       </c>
-      <c r="H311" s="2">
-        <f>G311/1000</f>
+      <c r="H311" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I311" s="2" t="s">
@@ -12063,8 +12119,8 @@
       <c r="G312" s="2">
         <v>7335</v>
       </c>
-      <c r="H312" s="2">
-        <f>G312/1000</f>
+      <c r="H312" s="13">
+        <f t="shared" si="4"/>
         <v>7.335</v>
       </c>
       <c r="I312" s="2" t="s">
@@ -12099,8 +12155,8 @@
       <c r="G313" s="2">
         <v>7716</v>
       </c>
-      <c r="H313" s="2">
-        <f>G313/1000</f>
+      <c r="H313" s="13">
+        <f t="shared" si="4"/>
         <v>7.7160000000000002</v>
       </c>
       <c r="I313" s="2" t="s">
@@ -12135,8 +12191,8 @@
       <c r="G314" s="2">
         <v>22760</v>
       </c>
-      <c r="H314" s="2">
-        <f>G314/1000</f>
+      <c r="H314" s="13">
+        <f t="shared" si="4"/>
         <v>22.76</v>
       </c>
       <c r="I314" s="2" t="s">
@@ -12171,8 +12227,8 @@
       <c r="G315" s="2">
         <v>70000</v>
       </c>
-      <c r="H315" s="2">
-        <f>G315/1000</f>
+      <c r="H315" s="13">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I315" s="2" t="s">
@@ -12207,8 +12263,8 @@
       <c r="G316" s="2">
         <v>21113</v>
       </c>
-      <c r="H316" s="2">
-        <f>G316/1000</f>
+      <c r="H316" s="13">
+        <f t="shared" si="4"/>
         <v>21.113</v>
       </c>
       <c r="I316" s="2" t="s">
@@ -12243,8 +12299,8 @@
       <c r="G317" s="2">
         <v>9720</v>
       </c>
-      <c r="H317" s="2">
-        <f>G317/1000</f>
+      <c r="H317" s="13">
+        <f t="shared" si="4"/>
         <v>9.7200000000000006</v>
       </c>
       <c r="I317" s="2" t="s">
@@ -12279,8 +12335,8 @@
       <c r="G318" s="2">
         <v>9720</v>
       </c>
-      <c r="H318" s="2">
-        <f>G318/1000</f>
+      <c r="H318" s="13">
+        <f t="shared" si="4"/>
         <v>9.7200000000000006</v>
       </c>
       <c r="I318" s="2" t="s">
@@ -12315,8 +12371,8 @@
       <c r="G319" s="2">
         <v>87500</v>
       </c>
-      <c r="H319" s="2">
-        <f>G319/1000</f>
+      <c r="H319" s="13">
+        <f t="shared" si="4"/>
         <v>87.5</v>
       </c>
       <c r="I319" s="2" t="s">
@@ -12351,8 +12407,8 @@
       <c r="G320" s="2">
         <v>9720</v>
       </c>
-      <c r="H320" s="2">
-        <f>G320/1000</f>
+      <c r="H320" s="13">
+        <f t="shared" si="4"/>
         <v>9.7200000000000006</v>
       </c>
       <c r="I320" s="2" t="s">
@@ -12387,8 +12443,8 @@
       <c r="G321" s="2">
         <v>3600</v>
       </c>
-      <c r="H321" s="2">
-        <f>G321/1000</f>
+      <c r="H321" s="13">
+        <f t="shared" si="4"/>
         <v>3.6</v>
       </c>
       <c r="I321" s="2" t="s">
@@ -12423,8 +12479,8 @@
       <c r="G322" s="2">
         <v>7797.6</v>
       </c>
-      <c r="H322" s="2">
-        <f>G322/1000</f>
+      <c r="H322" s="13">
+        <f t="shared" ref="H322:H340" si="5">G322/1000</f>
         <v>7.7976000000000001</v>
       </c>
       <c r="I322" s="2" t="s">
@@ -12459,8 +12515,8 @@
       <c r="G323" s="2">
         <v>4800</v>
       </c>
-      <c r="H323" s="2">
-        <f>G323/1000</f>
+      <c r="H323" s="13">
+        <f t="shared" si="5"/>
         <v>4.8</v>
       </c>
       <c r="I323" s="2" t="s">
@@ -12495,8 +12551,8 @@
       <c r="G324" s="2">
         <v>1500</v>
       </c>
-      <c r="H324" s="2">
-        <f>G324/1000</f>
+      <c r="H324" s="13">
+        <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
       <c r="I324" s="2" t="s">
@@ -12531,8 +12587,8 @@
       <c r="G325" s="2">
         <v>10665</v>
       </c>
-      <c r="H325" s="2">
-        <f>G325/1000</f>
+      <c r="H325" s="13">
+        <f t="shared" si="5"/>
         <v>10.664999999999999</v>
       </c>
       <c r="I325" s="2" t="s">
@@ -12567,8 +12623,8 @@
       <c r="G326" s="2">
         <v>10665</v>
       </c>
-      <c r="H326" s="2">
-        <f>G326/1000</f>
+      <c r="H326" s="13">
+        <f t="shared" si="5"/>
         <v>10.664999999999999</v>
       </c>
       <c r="I326" s="2" t="s">
@@ -12603,8 +12659,8 @@
       <c r="G327" s="2">
         <v>8921.2999999999993</v>
       </c>
-      <c r="H327" s="2">
-        <f>G327/1000</f>
+      <c r="H327" s="13">
+        <f t="shared" si="5"/>
         <v>8.9212999999999987</v>
       </c>
       <c r="I327" s="2" t="s">
@@ -12639,8 +12695,8 @@
       <c r="G328" s="2">
         <v>10665</v>
       </c>
-      <c r="H328" s="2">
-        <f>G328/1000</f>
+      <c r="H328" s="13">
+        <f t="shared" si="5"/>
         <v>10.664999999999999</v>
       </c>
       <c r="I328" s="2" t="s">
@@ -12675,8 +12731,8 @@
       <c r="G329" s="2">
         <v>5193</v>
       </c>
-      <c r="H329" s="2">
-        <f>G329/1000</f>
+      <c r="H329" s="13">
+        <f t="shared" si="5"/>
         <v>5.1929999999999996</v>
       </c>
       <c r="I329" s="2" t="s">
@@ -12711,8 +12767,8 @@
       <c r="G330" s="2">
         <v>93450</v>
       </c>
-      <c r="H330" s="2">
-        <f>G330/1000</f>
+      <c r="H330" s="13">
+        <f t="shared" si="5"/>
         <v>93.45</v>
       </c>
       <c r="I330" s="2" t="s">
@@ -12747,8 +12803,8 @@
       <c r="G331" s="2">
         <v>70070</v>
       </c>
-      <c r="H331" s="2">
-        <f>G331/1000</f>
+      <c r="H331" s="13">
+        <f t="shared" si="5"/>
         <v>70.069999999999993</v>
       </c>
       <c r="I331" s="2" t="s">
@@ -12783,8 +12839,8 @@
       <c r="G332" s="2">
         <v>8560</v>
       </c>
-      <c r="H332" s="2">
-        <f>G332/1000</f>
+      <c r="H332" s="13">
+        <f t="shared" si="5"/>
         <v>8.56</v>
       </c>
       <c r="I332" s="2" t="s">
@@ -12819,8 +12875,8 @@
       <c r="G333" s="2">
         <v>75000</v>
       </c>
-      <c r="H333" s="2">
-        <f>G333/1000</f>
+      <c r="H333" s="13">
+        <f t="shared" si="5"/>
         <v>75</v>
       </c>
       <c r="I333" s="2" t="s">
@@ -12855,8 +12911,8 @@
       <c r="G334" s="2">
         <v>70000</v>
       </c>
-      <c r="H334" s="2">
-        <f>G334/1000</f>
+      <c r="H334" s="13">
+        <f t="shared" si="5"/>
         <v>70</v>
       </c>
       <c r="I334" s="2" t="s">
@@ -12891,8 +12947,8 @@
       <c r="G335" s="2">
         <v>0</v>
       </c>
-      <c r="H335" s="2">
-        <f>G335/1000</f>
+      <c r="H335" s="13">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I335" s="2" t="s">
@@ -12927,8 +12983,8 @@
       <c r="G336" s="2">
         <v>19380</v>
       </c>
-      <c r="H336" s="2">
-        <f>G336/1000</f>
+      <c r="H336" s="13">
+        <f t="shared" si="5"/>
         <v>19.38</v>
       </c>
       <c r="I336" s="2" t="s">
@@ -12963,8 +13019,8 @@
       <c r="G337" s="2">
         <v>22400</v>
       </c>
-      <c r="H337" s="2">
-        <f>G337/1000</f>
+      <c r="H337" s="13">
+        <f t="shared" si="5"/>
         <v>22.4</v>
       </c>
       <c r="I337" s="2" t="s">
@@ -12999,8 +13055,8 @@
       <c r="G338" s="2">
         <v>10665</v>
       </c>
-      <c r="H338" s="2">
-        <f>G338/1000</f>
+      <c r="H338" s="13">
+        <f t="shared" si="5"/>
         <v>10.664999999999999</v>
       </c>
       <c r="I338" s="2" t="s">
@@ -13035,8 +13091,8 @@
       <c r="G339" s="2">
         <v>210000</v>
       </c>
-      <c r="H339" s="2">
-        <f>G339/1000</f>
+      <c r="H339" s="13">
+        <f t="shared" si="5"/>
         <v>210</v>
       </c>
       <c r="I339" s="2" t="s">
@@ -13071,8 +13127,8 @@
       <c r="G340" s="2">
         <v>20480</v>
       </c>
-      <c r="H340" s="2">
-        <f>G340/1000</f>
+      <c r="H340" s="13">
+        <f t="shared" si="5"/>
         <v>20.48</v>
       </c>
       <c r="I340" s="2" t="s">
@@ -13107,7 +13163,7 @@
       <c r="G341" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H341" s="2">
+      <c r="H341" s="13">
         <v>7.6</v>
       </c>
       <c r="I341" s="2" t="s">
@@ -13142,8 +13198,8 @@
       <c r="G342" s="2">
         <v>70000</v>
       </c>
-      <c r="H342" s="2">
-        <f>G342/1000</f>
+      <c r="H342" s="13">
+        <f t="shared" ref="H342:H367" si="6">G342/1000</f>
         <v>70</v>
       </c>
       <c r="I342" s="2" t="s">
@@ -13178,8 +13234,8 @@
       <c r="G343" s="2">
         <v>70000</v>
       </c>
-      <c r="H343" s="2">
-        <f>G343/1000</f>
+      <c r="H343" s="13">
+        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="I343" s="2" t="s">
@@ -13214,8 +13270,8 @@
       <c r="G344" s="2">
         <v>210000</v>
       </c>
-      <c r="H344" s="2">
-        <f>G344/1000</f>
+      <c r="H344" s="13">
+        <f t="shared" si="6"/>
         <v>210</v>
       </c>
       <c r="I344" s="2" t="s">
@@ -13250,8 +13306,8 @@
       <c r="G345" s="2">
         <v>93380</v>
       </c>
-      <c r="H345" s="2">
-        <f>G345/1000</f>
+      <c r="H345" s="13">
+        <f t="shared" si="6"/>
         <v>93.38</v>
       </c>
       <c r="I345" s="2" t="s">
@@ -13286,8 +13342,8 @@
       <c r="G346" s="2">
         <v>64120</v>
       </c>
-      <c r="H346" s="2">
-        <f>G346/1000</f>
+      <c r="H346" s="13">
+        <f t="shared" si="6"/>
         <v>64.12</v>
       </c>
       <c r="I346" s="2" t="s">
@@ -13322,8 +13378,8 @@
       <c r="G347" s="2">
         <v>4500</v>
       </c>
-      <c r="H347" s="2">
-        <f>G347/1000</f>
+      <c r="H347" s="13">
+        <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
       <c r="I347" s="2" t="s">
@@ -13358,8 +13414,8 @@
       <c r="G348" s="2">
         <v>10692.65</v>
       </c>
-      <c r="H348" s="2">
-        <f>G348/1000</f>
+      <c r="H348" s="13">
+        <f t="shared" si="6"/>
         <v>10.69265</v>
       </c>
       <c r="I348" s="2" t="s">
@@ -13394,8 +13450,8 @@
       <c r="G349" s="2">
         <v>140000</v>
       </c>
-      <c r="H349" s="2">
-        <f>G349/1000</f>
+      <c r="H349" s="13">
+        <f t="shared" si="6"/>
         <v>140</v>
       </c>
       <c r="I349" s="2" t="s">
@@ -13430,8 +13486,8 @@
       <c r="G350" s="2">
         <v>10844.2</v>
       </c>
-      <c r="H350" s="2">
-        <f>G350/1000</f>
+      <c r="H350" s="13">
+        <f t="shared" si="6"/>
         <v>10.844200000000001</v>
       </c>
       <c r="I350" s="2" t="s">
@@ -13466,8 +13522,8 @@
       <c r="G351" s="2">
         <v>9602.7999999999993</v>
       </c>
-      <c r="H351" s="2">
-        <f>G351/1000</f>
+      <c r="H351" s="13">
+        <f t="shared" si="6"/>
         <v>9.6027999999999984</v>
       </c>
       <c r="I351" s="2" t="s">
@@ -13502,8 +13558,8 @@
       <c r="G352" s="2">
         <v>140000</v>
       </c>
-      <c r="H352" s="2">
-        <f>G352/1000</f>
+      <c r="H352" s="13">
+        <f t="shared" si="6"/>
         <v>140</v>
       </c>
       <c r="I352" s="2" t="s">
@@ -13538,8 +13594,8 @@
       <c r="G353" s="2">
         <v>70000</v>
       </c>
-      <c r="H353" s="2">
-        <f>G353/1000</f>
+      <c r="H353" s="13">
+        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="I353" s="2" t="s">
@@ -13574,8 +13630,8 @@
       <c r="G354" s="2">
         <v>10665</v>
       </c>
-      <c r="H354" s="2">
-        <f>G354/1000</f>
+      <c r="H354" s="13">
+        <f t="shared" si="6"/>
         <v>10.664999999999999</v>
       </c>
       <c r="I354" s="2" t="s">
@@ -13610,8 +13666,8 @@
       <c r="G355" s="2">
         <v>70000</v>
       </c>
-      <c r="H355" s="2">
-        <f>G355/1000</f>
+      <c r="H355" s="13">
+        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="I355" s="2" t="s">
@@ -13646,8 +13702,8 @@
       <c r="G356" s="2">
         <v>18960</v>
       </c>
-      <c r="H356" s="2">
-        <f>G356/1000</f>
+      <c r="H356" s="13">
+        <f t="shared" si="6"/>
         <v>18.96</v>
       </c>
       <c r="I356" s="2" t="s">
@@ -13682,8 +13738,8 @@
       <c r="G357" s="2">
         <v>70000</v>
       </c>
-      <c r="H357" s="2">
-        <f>G357/1000</f>
+      <c r="H357" s="13">
+        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="I357" s="2" t="s">
@@ -13718,8 +13774,8 @@
       <c r="G358" s="2">
         <v>20050.599999999999</v>
       </c>
-      <c r="H358" s="2">
-        <f>G358/1000</f>
+      <c r="H358" s="13">
+        <f t="shared" si="6"/>
         <v>20.050599999999999</v>
       </c>
       <c r="I358" s="2" t="s">
@@ -13754,8 +13810,8 @@
       <c r="G359" s="2">
         <v>10554.18</v>
       </c>
-      <c r="H359" s="2">
-        <f>G359/1000</f>
+      <c r="H359" s="13">
+        <f t="shared" si="6"/>
         <v>10.554180000000001</v>
       </c>
       <c r="I359" s="2" t="s">
@@ -13790,8 +13846,8 @@
       <c r="G360" s="2">
         <v>7044.75</v>
       </c>
-      <c r="H360" s="2">
-        <f>G360/1000</f>
+      <c r="H360" s="13">
+        <f t="shared" si="6"/>
         <v>7.0447499999999996</v>
       </c>
       <c r="I360" s="2" t="s">
@@ -13826,8 +13882,8 @@
       <c r="G361" s="2">
         <v>50000</v>
       </c>
-      <c r="H361" s="2">
-        <f>G361/1000</f>
+      <c r="H361" s="13">
+        <f t="shared" si="6"/>
         <v>50</v>
       </c>
       <c r="I361" s="2" t="s">
@@ -13862,8 +13918,8 @@
       <c r="G362" s="2">
         <v>26000</v>
       </c>
-      <c r="H362" s="2">
-        <f>G362/1000</f>
+      <c r="H362" s="13">
+        <f t="shared" si="6"/>
         <v>26</v>
       </c>
       <c r="I362" s="2" t="s">
@@ -13898,8 +13954,8 @@
       <c r="G363" s="2">
         <v>9620</v>
       </c>
-      <c r="H363" s="2">
-        <f>G363/1000</f>
+      <c r="H363" s="13">
+        <f t="shared" si="6"/>
         <v>9.6199999999999992</v>
       </c>
       <c r="I363" s="2" t="s">
@@ -13934,8 +13990,8 @@
       <c r="G364" s="2">
         <v>125000</v>
       </c>
-      <c r="H364" s="2">
-        <f>G364/1000</f>
+      <c r="H364" s="13">
+        <f t="shared" si="6"/>
         <v>125</v>
       </c>
       <c r="I364" s="2" t="s">
@@ -13970,8 +14026,8 @@
       <c r="G365" s="2">
         <v>10665</v>
       </c>
-      <c r="H365" s="2">
-        <f>G365/1000</f>
+      <c r="H365" s="13">
+        <f t="shared" si="6"/>
         <v>10.664999999999999</v>
       </c>
       <c r="I365" s="2" t="s">
@@ -14006,8 +14062,8 @@
       <c r="G366" s="2">
         <v>9065.25</v>
       </c>
-      <c r="H366" s="2">
-        <f>G366/1000</f>
+      <c r="H366" s="13">
+        <f t="shared" si="6"/>
         <v>9.0652500000000007</v>
       </c>
       <c r="I366" s="2" t="s">
@@ -14042,8 +14098,8 @@
       <c r="G367" s="2">
         <v>150000</v>
       </c>
-      <c r="H367" s="2">
-        <f>G367/1000</f>
+      <c r="H367" s="13">
+        <f t="shared" si="6"/>
         <v>150</v>
       </c>
       <c r="I367" s="2" t="s">
@@ -14054,13 +14110,1152 @@
       </c>
       <c r="K367" s="12">
         <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:11">
+      <c r="A368">
+        <v>367</v>
+      </c>
+      <c r="B368" s="5">
+        <v>46106</v>
+      </c>
+      <c r="C368" t="s">
+        <v>7</v>
+      </c>
+      <c r="D368" t="s">
+        <v>55</v>
+      </c>
+      <c r="E368" s="2">
+        <v>3</v>
+      </c>
+      <c r="F368" t="s">
+        <v>90</v>
+      </c>
+      <c r="H368" s="13">
+        <v>75</v>
+      </c>
+      <c r="I368" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J368">
+        <v>0</v>
+      </c>
+      <c r="K368" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:11">
+      <c r="A369">
+        <v>368</v>
+      </c>
+      <c r="B369" s="5">
+        <v>46106</v>
+      </c>
+      <c r="C369" t="s">
+        <v>7</v>
+      </c>
+      <c r="D369" t="s">
+        <v>55</v>
+      </c>
+      <c r="E369" s="2">
+        <v>3</v>
+      </c>
+      <c r="F369" t="s">
+        <v>90</v>
+      </c>
+      <c r="H369" s="13">
+        <v>75</v>
+      </c>
+      <c r="I369" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J369">
+        <v>0</v>
+      </c>
+      <c r="K369" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:11">
+      <c r="A370">
+        <v>369</v>
+      </c>
+      <c r="B370" s="5">
+        <v>46107</v>
+      </c>
+      <c r="C370" t="s">
+        <v>7</v>
+      </c>
+      <c r="D370" t="s">
+        <v>8</v>
+      </c>
+      <c r="E370" s="2">
+        <v>3</v>
+      </c>
+      <c r="F370" t="s">
+        <v>91</v>
+      </c>
+      <c r="H370" s="13">
+        <v>70</v>
+      </c>
+      <c r="I370" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J370">
+        <v>0</v>
+      </c>
+      <c r="K370" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:11">
+      <c r="A371">
+        <v>370</v>
+      </c>
+      <c r="B371" s="5">
+        <v>46107</v>
+      </c>
+      <c r="C371" t="s">
+        <v>7</v>
+      </c>
+      <c r="D371" t="s">
+        <v>8</v>
+      </c>
+      <c r="E371" s="2">
+        <v>3</v>
+      </c>
+      <c r="F371" t="s">
+        <v>92</v>
+      </c>
+      <c r="H371" s="13">
+        <v>70</v>
+      </c>
+      <c r="I371" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J371">
+        <v>0</v>
+      </c>
+      <c r="K371" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:11">
+      <c r="A372">
+        <v>371</v>
+      </c>
+      <c r="B372" s="5">
+        <v>46120</v>
+      </c>
+      <c r="C372" t="s">
+        <v>7</v>
+      </c>
+      <c r="D372" t="s">
+        <v>8</v>
+      </c>
+      <c r="E372" s="2">
+        <v>1</v>
+      </c>
+      <c r="F372" t="s">
+        <v>23</v>
+      </c>
+      <c r="H372" s="13">
+        <v>19380</v>
+      </c>
+      <c r="I372" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J372">
+        <v>0</v>
+      </c>
+      <c r="K372" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:11">
+      <c r="A373">
+        <v>372</v>
+      </c>
+      <c r="B373" s="5">
+        <v>46120</v>
+      </c>
+      <c r="C373" t="s">
+        <v>7</v>
+      </c>
+      <c r="D373" t="s">
+        <v>55</v>
+      </c>
+      <c r="E373" s="2">
+        <v>2</v>
+      </c>
+      <c r="F373" t="s">
+        <v>9</v>
+      </c>
+      <c r="H373" s="13">
+        <v>50000</v>
+      </c>
+      <c r="I373" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J373">
+        <v>0</v>
+      </c>
+      <c r="K373" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:11">
+      <c r="A374">
+        <v>373</v>
+      </c>
+      <c r="B374" s="5">
+        <v>46121</v>
+      </c>
+      <c r="C374" t="s">
+        <v>7</v>
+      </c>
+      <c r="D374" t="s">
+        <v>8</v>
+      </c>
+      <c r="E374" s="2">
+        <v>1</v>
+      </c>
+      <c r="F374" t="s">
+        <v>23</v>
+      </c>
+      <c r="H374" s="13">
+        <v>28420</v>
+      </c>
+      <c r="I374" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J374">
+        <v>0</v>
+      </c>
+      <c r="K374" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:11">
+      <c r="A375">
+        <v>374</v>
+      </c>
+      <c r="B375" s="5">
+        <v>46121</v>
+      </c>
+      <c r="C375" t="s">
+        <v>7</v>
+      </c>
+      <c r="D375" t="s">
+        <v>55</v>
+      </c>
+      <c r="E375" s="2">
+        <v>1</v>
+      </c>
+      <c r="F375" t="s">
+        <v>77</v>
+      </c>
+      <c r="H375" s="13">
+        <v>10665</v>
+      </c>
+      <c r="I375" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J375">
+        <v>0</v>
+      </c>
+      <c r="K375" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:11">
+      <c r="A376">
+        <v>375</v>
+      </c>
+      <c r="B376" s="5">
+        <v>46126</v>
+      </c>
+      <c r="C376" t="s">
+        <v>7</v>
+      </c>
+      <c r="D376" t="s">
+        <v>55</v>
+      </c>
+      <c r="E376" s="2">
+        <v>2</v>
+      </c>
+      <c r="F376" t="s">
+        <v>96</v>
+      </c>
+      <c r="H376" s="13">
+        <v>41340</v>
+      </c>
+      <c r="I376" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J376" s="2">
+        <v>0</v>
+      </c>
+      <c r="K376" s="15"/>
+    </row>
+    <row r="377" spans="1:11">
+      <c r="A377">
+        <v>376</v>
+      </c>
+      <c r="B377" s="5">
+        <v>46127</v>
+      </c>
+      <c r="C377" t="s">
+        <v>7</v>
+      </c>
+      <c r="D377" t="s">
+        <v>55</v>
+      </c>
+      <c r="F377" t="s">
+        <v>96</v>
+      </c>
+      <c r="I377" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J377" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K377" s="15"/>
+    </row>
+    <row r="378" spans="1:11">
+      <c r="A378">
+        <v>377</v>
+      </c>
+      <c r="B378" s="5">
+        <v>46127</v>
+      </c>
+      <c r="C378" t="s">
+        <v>7</v>
+      </c>
+      <c r="D378" t="s">
+        <v>55</v>
+      </c>
+      <c r="F378" t="s">
+        <v>96</v>
+      </c>
+      <c r="I378" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J378" s="2">
+        <v>44229</v>
+      </c>
+      <c r="K378" s="15"/>
+    </row>
+    <row r="379" spans="1:11">
+      <c r="A379">
+        <v>378</v>
+      </c>
+      <c r="B379" s="5">
+        <v>46127</v>
+      </c>
+      <c r="C379" t="s">
+        <v>7</v>
+      </c>
+      <c r="D379" t="s">
+        <v>55</v>
+      </c>
+      <c r="F379" t="s">
+        <v>96</v>
+      </c>
+      <c r="I379" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J379" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K379" s="15"/>
+    </row>
+    <row r="380" spans="1:11">
+      <c r="A380">
+        <v>379</v>
+      </c>
+      <c r="B380" s="5">
+        <v>46127</v>
+      </c>
+      <c r="C380" t="s">
+        <v>7</v>
+      </c>
+      <c r="D380" t="s">
+        <v>55</v>
+      </c>
+      <c r="F380" t="s">
+        <v>96</v>
+      </c>
+      <c r="I380" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J380" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="K380">
+        <f>SUM(K2:K371)/1000</f>
+        <v>1494.36</v>
+      </c>
+    </row>
+    <row r="381" spans="1:11">
+      <c r="A381">
+        <v>380</v>
+      </c>
+      <c r="B381" s="5">
+        <v>46128</v>
+      </c>
+      <c r="C381" t="s">
+        <v>7</v>
+      </c>
+      <c r="D381" t="s">
+        <v>55</v>
+      </c>
+      <c r="E381" s="2">
+        <v>1</v>
+      </c>
+      <c r="F381" t="s">
+        <v>97</v>
+      </c>
+      <c r="H381" s="13">
+        <v>8337</v>
+      </c>
+      <c r="I381" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J381" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:11">
+      <c r="A382">
+        <v>381</v>
+      </c>
+      <c r="B382" s="5">
+        <v>46128</v>
+      </c>
+      <c r="C382" t="s">
+        <v>7</v>
+      </c>
+      <c r="D382" t="s">
+        <v>55</v>
+      </c>
+      <c r="E382" s="2">
+        <v>1</v>
+      </c>
+      <c r="F382" t="s">
+        <v>97</v>
+      </c>
+      <c r="H382" s="13">
+        <v>10665</v>
+      </c>
+      <c r="I382" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J382" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:11">
+      <c r="A383">
+        <v>382</v>
+      </c>
+      <c r="B383" s="5">
+        <v>46134</v>
+      </c>
+      <c r="C383" t="s">
+        <v>7</v>
+      </c>
+      <c r="D383" t="s">
+        <v>55</v>
+      </c>
+      <c r="E383" s="2">
+        <v>4</v>
+      </c>
+      <c r="F383" t="s">
+        <v>97</v>
+      </c>
+      <c r="H383" s="13">
+        <v>100000</v>
+      </c>
+      <c r="I383" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J383" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:11">
+      <c r="A384">
+        <v>383</v>
+      </c>
+      <c r="B384" s="5">
+        <v>46139</v>
+      </c>
+      <c r="C384" t="s">
+        <v>7</v>
+      </c>
+      <c r="D384" t="s">
+        <v>55</v>
+      </c>
+      <c r="E384" s="2">
+        <v>1</v>
+      </c>
+      <c r="F384" t="s">
+        <v>97</v>
+      </c>
+      <c r="H384" s="13">
+        <v>9290</v>
+      </c>
+      <c r="I384" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J384" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10">
+      <c r="A385">
+        <v>384</v>
+      </c>
+      <c r="B385" s="5">
+        <v>46139</v>
+      </c>
+      <c r="C385" t="s">
+        <v>7</v>
+      </c>
+      <c r="D385" t="s">
+        <v>55</v>
+      </c>
+      <c r="E385" s="2">
+        <v>1</v>
+      </c>
+      <c r="F385" t="s">
+        <v>97</v>
+      </c>
+      <c r="H385" s="13">
+        <v>8560</v>
+      </c>
+      <c r="I385" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J385" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10">
+      <c r="A386">
+        <v>385</v>
+      </c>
+      <c r="B386" s="5">
+        <v>46140</v>
+      </c>
+      <c r="C386" t="s">
+        <v>7</v>
+      </c>
+      <c r="D386" t="s">
+        <v>55</v>
+      </c>
+      <c r="E386" s="2">
+        <v>1</v>
+      </c>
+      <c r="F386" t="s">
+        <v>97</v>
+      </c>
+      <c r="H386" s="13">
+        <v>8652</v>
+      </c>
+      <c r="I386" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J386" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10">
+      <c r="A387">
+        <v>386</v>
+      </c>
+      <c r="B387" s="5">
+        <v>46149</v>
+      </c>
+      <c r="C387" t="s">
+        <v>7</v>
+      </c>
+      <c r="D387" t="s">
+        <v>55</v>
+      </c>
+      <c r="E387" s="2">
+        <v>1</v>
+      </c>
+      <c r="F387" t="s">
+        <v>96</v>
+      </c>
+      <c r="H387" s="13">
+        <v>11520</v>
+      </c>
+      <c r="I387" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J387" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10">
+      <c r="A388">
+        <v>387</v>
+      </c>
+      <c r="B388" s="5">
+        <v>45790</v>
+      </c>
+      <c r="C388" t="s">
+        <v>7</v>
+      </c>
+      <c r="D388" t="s">
+        <v>55</v>
+      </c>
+      <c r="E388" s="2">
+        <v>1</v>
+      </c>
+      <c r="F388" t="s">
+        <v>97</v>
+      </c>
+      <c r="H388" s="13">
+        <v>9447.5</v>
+      </c>
+      <c r="I388" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J388" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10">
+      <c r="A389">
+        <v>388</v>
+      </c>
+      <c r="B389" s="5">
+        <v>46156</v>
+      </c>
+      <c r="C389" t="s">
+        <v>7</v>
+      </c>
+      <c r="D389" t="s">
+        <v>55</v>
+      </c>
+      <c r="E389" s="2">
+        <v>3</v>
+      </c>
+      <c r="F389" t="s">
+        <v>96</v>
+      </c>
+      <c r="H389" s="13">
+        <v>0</v>
+      </c>
+      <c r="I389" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J389" s="2">
+        <v>52995.600000000006</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10">
+      <c r="A390">
+        <v>389</v>
+      </c>
+      <c r="B390" s="5">
+        <v>46156</v>
+      </c>
+      <c r="C390" t="s">
+        <v>7</v>
+      </c>
+      <c r="D390" t="s">
+        <v>55</v>
+      </c>
+      <c r="E390" s="2">
+        <v>3</v>
+      </c>
+      <c r="F390" t="s">
+        <v>96</v>
+      </c>
+      <c r="H390" s="13">
+        <v>0</v>
+      </c>
+      <c r="I390" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J390" s="2">
+        <v>52995.600000000006</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10">
+      <c r="A391">
+        <v>390</v>
+      </c>
+      <c r="B391" s="5">
+        <v>46157</v>
+      </c>
+      <c r="C391" t="s">
+        <v>7</v>
+      </c>
+      <c r="D391" t="s">
+        <v>55</v>
+      </c>
+      <c r="E391" s="2">
+        <v>1</v>
+      </c>
+      <c r="F391" t="s">
+        <v>96</v>
+      </c>
+      <c r="H391" s="13">
+        <v>0</v>
+      </c>
+      <c r="I391" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J391" s="2">
+        <v>4356</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10">
+      <c r="A392">
+        <v>391</v>
+      </c>
+      <c r="B392" s="5">
+        <v>46157</v>
+      </c>
+      <c r="C392" t="s">
+        <v>95</v>
+      </c>
+      <c r="D392" t="s">
+        <v>55</v>
+      </c>
+      <c r="F392" t="s">
+        <v>97</v>
+      </c>
+      <c r="H392" s="13">
+        <v>1175</v>
+      </c>
+      <c r="I392" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J392" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10">
+      <c r="A393">
+        <v>392</v>
+      </c>
+      <c r="B393" s="5">
+        <v>46169</v>
+      </c>
+      <c r="C393" t="s">
+        <v>7</v>
+      </c>
+      <c r="D393" t="s">
+        <v>55</v>
+      </c>
+      <c r="E393" s="2">
+        <v>1</v>
+      </c>
+      <c r="F393" t="s">
+        <v>97</v>
+      </c>
+      <c r="H393" s="13">
+        <v>8500</v>
+      </c>
+      <c r="I393" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J393" s="2"/>
+    </row>
+    <row r="394" spans="1:10">
+      <c r="A394">
+        <v>393</v>
+      </c>
+      <c r="B394" s="5">
+        <v>46169</v>
+      </c>
+      <c r="C394" t="s">
+        <v>7</v>
+      </c>
+      <c r="D394" t="s">
+        <v>55</v>
+      </c>
+      <c r="E394" s="2">
+        <v>1</v>
+      </c>
+      <c r="F394" t="s">
+        <v>97</v>
+      </c>
+      <c r="H394" s="13">
+        <v>9718</v>
+      </c>
+      <c r="I394" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J394" s="2"/>
+    </row>
+    <row r="395" spans="1:10">
+      <c r="A395">
+        <v>394</v>
+      </c>
+      <c r="B395" s="5">
+        <v>46170</v>
+      </c>
+      <c r="C395" t="s">
+        <v>7</v>
+      </c>
+      <c r="D395" t="s">
+        <v>55</v>
+      </c>
+      <c r="E395" s="2">
+        <v>1</v>
+      </c>
+      <c r="F395" t="s">
+        <v>97</v>
+      </c>
+      <c r="H395" s="13">
+        <v>10340</v>
+      </c>
+      <c r="I395" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J395" s="2"/>
+    </row>
+    <row r="396" spans="1:10">
+      <c r="A396">
+        <v>395</v>
+      </c>
+      <c r="B396" s="5">
+        <v>46176</v>
+      </c>
+      <c r="C396" t="s">
+        <v>7</v>
+      </c>
+      <c r="D396" t="s">
+        <v>55</v>
+      </c>
+      <c r="E396" s="2">
+        <v>2</v>
+      </c>
+      <c r="F396" t="s">
+        <v>98</v>
+      </c>
+      <c r="H396" s="13">
+        <v>46000</v>
+      </c>
+      <c r="I396" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J396" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:10">
+      <c r="A397">
+        <v>396</v>
+      </c>
+      <c r="B397" s="5">
+        <v>46178</v>
+      </c>
+      <c r="C397" t="s">
+        <v>7</v>
+      </c>
+      <c r="D397" t="s">
+        <v>8</v>
+      </c>
+      <c r="E397" s="2">
+        <v>1</v>
+      </c>
+      <c r="F397" t="s">
+        <v>98</v>
+      </c>
+      <c r="H397" s="13">
+        <v>25340</v>
+      </c>
+      <c r="I397" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J397" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:10">
+      <c r="A398">
+        <v>397</v>
+      </c>
+      <c r="B398" s="5">
+        <v>46178</v>
+      </c>
+      <c r="C398" t="s">
+        <v>7</v>
+      </c>
+      <c r="D398" t="s">
+        <v>55</v>
+      </c>
+      <c r="F398" t="s">
+        <v>96</v>
+      </c>
+      <c r="H398" s="13">
+        <v>0</v>
+      </c>
+      <c r="I398" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J398" s="2">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="399" spans="1:10">
+      <c r="A399">
+        <v>398</v>
+      </c>
+      <c r="B399" s="5">
+        <v>46183</v>
+      </c>
+      <c r="C399" t="s">
+        <v>7</v>
+      </c>
+      <c r="D399" t="s">
+        <v>8</v>
+      </c>
+      <c r="E399" s="2">
+        <v>1</v>
+      </c>
+      <c r="F399" t="s">
+        <v>99</v>
+      </c>
+      <c r="H399" s="13">
+        <v>19200</v>
+      </c>
+      <c r="I399" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J399" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:10">
+      <c r="A400">
+        <v>399</v>
+      </c>
+      <c r="B400" s="5">
+        <v>46183</v>
+      </c>
+      <c r="C400" t="s">
+        <v>7</v>
+      </c>
+      <c r="D400" t="s">
+        <v>55</v>
+      </c>
+      <c r="E400" s="2">
+        <v>1</v>
+      </c>
+      <c r="F400" t="s">
+        <v>99</v>
+      </c>
+      <c r="H400" s="13">
+        <v>10665</v>
+      </c>
+      <c r="I400" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J400" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:10">
+      <c r="A401">
+        <v>400</v>
+      </c>
+      <c r="B401" s="5">
+        <v>46183</v>
+      </c>
+      <c r="C401" t="s">
+        <v>7</v>
+      </c>
+      <c r="D401" t="s">
+        <v>55</v>
+      </c>
+      <c r="E401" s="2">
+        <v>1</v>
+      </c>
+      <c r="F401" t="s">
+        <v>99</v>
+      </c>
+      <c r="H401" s="13">
+        <v>10665</v>
+      </c>
+      <c r="I401" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J401" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:10">
+      <c r="A402">
+        <v>401</v>
+      </c>
+      <c r="B402" s="5">
+        <v>46184</v>
+      </c>
+      <c r="C402" t="s">
+        <v>7</v>
+      </c>
+      <c r="D402" t="s">
+        <v>8</v>
+      </c>
+      <c r="E402" s="2">
+        <v>1</v>
+      </c>
+      <c r="F402" t="s">
+        <v>98</v>
+      </c>
+      <c r="H402" s="13">
+        <v>28420</v>
+      </c>
+      <c r="I402" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J402" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:10">
+      <c r="A403">
+        <v>402</v>
+      </c>
+      <c r="B403" s="5">
+        <v>46184</v>
+      </c>
+      <c r="C403" t="s">
+        <v>7</v>
+      </c>
+      <c r="D403" t="s">
+        <v>8</v>
+      </c>
+      <c r="E403" s="2">
+        <v>1</v>
+      </c>
+      <c r="F403" t="s">
+        <v>98</v>
+      </c>
+      <c r="H403" s="13">
+        <v>28420</v>
+      </c>
+      <c r="I403" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J403" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:10">
+      <c r="A404">
+        <v>403</v>
+      </c>
+      <c r="B404" s="5">
+        <v>46184</v>
+      </c>
+      <c r="C404" t="s">
+        <v>7</v>
+      </c>
+      <c r="D404" t="s">
+        <v>55</v>
+      </c>
+      <c r="E404" s="2">
+        <v>1</v>
+      </c>
+      <c r="F404" t="s">
+        <v>99</v>
+      </c>
+      <c r="H404" s="13">
+        <v>8304</v>
+      </c>
+      <c r="I404" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J404" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10">
+      <c r="A405">
+        <v>404</v>
+      </c>
+      <c r="B405" s="5">
+        <v>46184</v>
+      </c>
+      <c r="C405" t="s">
+        <v>7</v>
+      </c>
+      <c r="D405" t="s">
+        <v>55</v>
+      </c>
+      <c r="E405" s="2">
+        <v>1</v>
+      </c>
+      <c r="F405" t="s">
+        <v>99</v>
+      </c>
+      <c r="H405" s="13">
+        <v>3510</v>
+      </c>
+      <c r="I405" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J405" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10">
+      <c r="A406">
+        <v>405</v>
+      </c>
+      <c r="B406" s="5">
+        <v>45825</v>
+      </c>
+      <c r="C406" t="s">
+        <v>7</v>
+      </c>
+      <c r="D406" t="s">
+        <v>55</v>
+      </c>
+      <c r="E406" s="2">
+        <v>1</v>
+      </c>
+      <c r="F406" t="s">
+        <v>96</v>
+      </c>
+      <c r="H406" s="13">
+        <v>9000</v>
+      </c>
+      <c r="I406" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J406" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:10">
+      <c r="B407" s="5"/>
+      <c r="H407" s="13">
+        <f>SUBTOTAL(109,Tabla1[Peso Neto Exportado2])</f>
+        <v>570077.42800000007</v>
+      </c>
+      <c r="J407">
+        <f>SUBTOTAL(109,Tabla1[[Peso Neto Importado ]])/1000</f>
+        <v>291.99020000000002</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANGELA\Desktop\MiDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E6A443-5692-4682-93D1-B5180C35C260}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C47432D-B01F-4370-9C04-64D5E84307A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8805" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="109">
   <si>
     <t>N° DE OPERACIÓN</t>
   </si>
@@ -344,6 +344,15 @@
   <si>
     <t>FIRST INTERNATIONAL TRANSPORT</t>
   </si>
+  <si>
+    <t>ADUANERA NUEVA SEGOVIA</t>
+  </si>
+  <si>
+    <t>ITALIA (SUSPENDIDA POR CONTAMINACION DE LA CARGA)</t>
+  </si>
+  <si>
+    <t>FRANCIA</t>
+  </si>
 </sst>
 </file>
 
@@ -438,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,11 +487,32 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -564,18 +594,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A1:J407" totalsRowCount="1">
-  <autoFilter ref="A1:J406" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A1:J435" totalsRowCount="1">
+  <autoFilter ref="A1:J434" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="N° DE OPERACIÓN"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="FECHA"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="FECHA" totalsRowDxfId="4"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="TIPO DE CARGA"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="TIPO DE SERVICIO"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LLENOS RECIBIDOS (EXPORTADOS)"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LLENOS RECIBIDOS (EXPORTADOS)" totalsRowDxfId="3"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CONTENIDO"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Peso Neto Exportado"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Peso Neto Exportado2" totalsRowFunction="sum"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DESTINO "/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Peso Neto Exportado" totalsRowDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Peso Neto Exportado2" totalsRowFunction="sum" totalsRowDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DESTINO " totalsRowDxfId="0"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Peso Neto Importado " totalsRowFunction="custom">
       <totalsRowFormula>SUBTOTAL(109,Tabla1[[Peso Neto Importado ]])/1000</totalsRowFormula>
     </tableColumn>
@@ -760,7 +790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K407"/>
+  <dimension ref="A1:K435"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -12354,7 +12384,7 @@
         <v>7797.6</v>
       </c>
       <c r="H322" s="2">
-        <f t="shared" ref="H322:H385" si="5">G322/1000</f>
+        <f t="shared" ref="H322:H340" si="5">G322/1000</f>
         <v>7.7976000000000001</v>
       </c>
       <c r="I322" s="1" t="s">
@@ -15097,7 +15127,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="11">
-        <v>45825</v>
+        <v>46190</v>
       </c>
       <c r="C406" t="s">
         <v>11</v>
@@ -15122,14 +15152,802 @@
       </c>
     </row>
     <row r="407" spans="1:10">
-      <c r="B407" s="11"/>
+      <c r="A407">
+        <v>406</v>
+      </c>
+      <c r="B407" s="17">
+        <v>46203</v>
+      </c>
+      <c r="C407" t="s">
+        <v>11</v>
+      </c>
+      <c r="D407" t="s">
+        <v>59</v>
+      </c>
+      <c r="F407" t="s">
+        <v>95</v>
+      </c>
       <c r="H407" s="2">
+        <v>0</v>
+      </c>
+      <c r="I407" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J407">
+        <v>15079.58</v>
+      </c>
+    </row>
+    <row r="408" spans="1:10">
+      <c r="A408">
+        <v>407</v>
+      </c>
+      <c r="B408" s="17">
+        <v>46203</v>
+      </c>
+      <c r="C408" t="s">
+        <v>11</v>
+      </c>
+      <c r="D408" t="s">
+        <v>59</v>
+      </c>
+      <c r="E408" s="1">
+        <v>1</v>
+      </c>
+      <c r="F408" t="s">
+        <v>95</v>
+      </c>
+      <c r="H408" s="2">
+        <v>0</v>
+      </c>
+      <c r="I408" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J408">
+        <v>15079.58</v>
+      </c>
+    </row>
+    <row r="409" spans="1:10">
+      <c r="A409">
+        <v>408</v>
+      </c>
+      <c r="B409" s="17">
+        <v>46210</v>
+      </c>
+      <c r="C409" t="s">
+        <v>11</v>
+      </c>
+      <c r="D409" t="s">
+        <v>59</v>
+      </c>
+      <c r="F409" t="s">
+        <v>95</v>
+      </c>
+      <c r="H409" s="2">
+        <v>0</v>
+      </c>
+      <c r="I409" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J409">
+        <v>15079.58</v>
+      </c>
+    </row>
+    <row r="410" spans="1:10">
+      <c r="A410">
+        <v>409</v>
+      </c>
+      <c r="B410" s="17">
+        <v>46210</v>
+      </c>
+      <c r="C410" t="s">
+        <v>11</v>
+      </c>
+      <c r="D410" t="s">
+        <v>12</v>
+      </c>
+      <c r="E410" s="1">
+        <v>1</v>
+      </c>
+      <c r="F410" t="s">
+        <v>95</v>
+      </c>
+      <c r="H410" s="2">
+        <v>10080</v>
+      </c>
+      <c r="I410" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:10">
+      <c r="A411">
+        <v>410</v>
+      </c>
+      <c r="B411" s="17">
+        <v>46211</v>
+      </c>
+      <c r="C411" t="s">
+        <v>11</v>
+      </c>
+      <c r="D411" t="s">
+        <v>59</v>
+      </c>
+      <c r="E411" s="1">
+        <v>1</v>
+      </c>
+      <c r="F411" t="s">
+        <v>95</v>
+      </c>
+      <c r="I411" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:10">
+      <c r="A412">
+        <v>411</v>
+      </c>
+      <c r="B412" s="17">
+        <v>46211</v>
+      </c>
+      <c r="C412" t="s">
+        <v>11</v>
+      </c>
+      <c r="D412" t="s">
+        <v>59</v>
+      </c>
+      <c r="E412" s="1">
+        <v>1</v>
+      </c>
+      <c r="F412" t="s">
+        <v>106</v>
+      </c>
+      <c r="H412" s="2">
+        <v>10665</v>
+      </c>
+      <c r="I412" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:10">
+      <c r="A413">
+        <v>412</v>
+      </c>
+      <c r="B413" s="17">
+        <v>46212</v>
+      </c>
+      <c r="C413" t="s">
+        <v>11</v>
+      </c>
+      <c r="D413" t="s">
+        <v>59</v>
+      </c>
+      <c r="E413" s="1">
+        <v>1</v>
+      </c>
+      <c r="F413" t="s">
+        <v>105</v>
+      </c>
+      <c r="H413" s="2">
+        <v>3308</v>
+      </c>
+      <c r="I413" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:10">
+      <c r="A414">
+        <v>413</v>
+      </c>
+      <c r="B414" s="17">
+        <v>46219</v>
+      </c>
+      <c r="C414" t="s">
+        <v>11</v>
+      </c>
+      <c r="D414" t="s">
+        <v>59</v>
+      </c>
+      <c r="E414" s="1">
+        <v>1</v>
+      </c>
+      <c r="F414" t="s">
+        <v>105</v>
+      </c>
+      <c r="H414" s="2">
+        <v>10665</v>
+      </c>
+      <c r="I414" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:10">
+      <c r="A415">
+        <v>414</v>
+      </c>
+      <c r="B415" s="17">
+        <v>46219</v>
+      </c>
+      <c r="C415" t="s">
+        <v>11</v>
+      </c>
+      <c r="D415" t="s">
+        <v>59</v>
+      </c>
+      <c r="E415" s="1">
+        <v>1</v>
+      </c>
+      <c r="F415" t="s">
+        <v>105</v>
+      </c>
+      <c r="H415" s="2">
+        <v>9710.7000000000007</v>
+      </c>
+      <c r="I415" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:10">
+      <c r="A416">
+        <v>415</v>
+      </c>
+      <c r="B416" s="17">
+        <v>46225</v>
+      </c>
+      <c r="C416" t="s">
+        <v>11</v>
+      </c>
+      <c r="D416" t="s">
+        <v>12</v>
+      </c>
+      <c r="E416" s="1">
+        <v>1</v>
+      </c>
+      <c r="F416" t="s">
+        <v>105</v>
+      </c>
+      <c r="H416" s="2">
+        <v>4447.1000000000004</v>
+      </c>
+      <c r="I416" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:10">
+      <c r="A417">
+        <v>416</v>
+      </c>
+      <c r="B417" s="17">
+        <v>46225</v>
+      </c>
+      <c r="C417" t="s">
+        <v>11</v>
+      </c>
+      <c r="D417" t="s">
+        <v>59</v>
+      </c>
+      <c r="E417" s="1">
+        <v>1</v>
+      </c>
+      <c r="F417" t="s">
+        <v>105</v>
+      </c>
+      <c r="H417" s="2">
+        <v>24000</v>
+      </c>
+      <c r="I417" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:10">
+      <c r="A418">
+        <v>417</v>
+      </c>
+      <c r="B418" s="17">
+        <v>46232</v>
+      </c>
+      <c r="C418" t="s">
+        <v>11</v>
+      </c>
+      <c r="D418" t="s">
+        <v>12</v>
+      </c>
+      <c r="E418" s="1">
+        <v>2</v>
+      </c>
+      <c r="F418" t="s">
+        <v>103</v>
+      </c>
+      <c r="H418" s="2">
+        <v>10063</v>
+      </c>
+      <c r="I418" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:10">
+      <c r="A419">
+        <v>418</v>
+      </c>
+      <c r="B419" s="17">
+        <v>46233</v>
+      </c>
+      <c r="C419" t="s">
+        <v>11</v>
+      </c>
+      <c r="D419" t="s">
+        <v>59</v>
+      </c>
+      <c r="E419" s="1">
+        <v>1</v>
+      </c>
+      <c r="F419" t="s">
+        <v>105</v>
+      </c>
+      <c r="H419" s="2">
+        <v>19200</v>
+      </c>
+      <c r="I419" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:10">
+      <c r="A420">
+        <v>419</v>
+      </c>
+      <c r="B420" s="17">
+        <v>46116</v>
+      </c>
+      <c r="C420" t="s">
+        <v>11</v>
+      </c>
+      <c r="D420" t="s">
+        <v>12</v>
+      </c>
+      <c r="F420" t="s">
+        <v>105</v>
+      </c>
+      <c r="H420" s="2">
+        <v>43500</v>
+      </c>
+      <c r="I420" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:10">
+      <c r="A421">
+        <v>420</v>
+      </c>
+      <c r="B421" s="17">
+        <v>46241</v>
+      </c>
+      <c r="C421" t="s">
+        <v>11</v>
+      </c>
+      <c r="D421" t="s">
+        <v>59</v>
+      </c>
+      <c r="E421" s="1">
+        <v>1</v>
+      </c>
+      <c r="F421" t="s">
+        <v>103</v>
+      </c>
+      <c r="H421" s="2">
+        <v>24900</v>
+      </c>
+      <c r="I421" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:10">
+      <c r="A422">
+        <v>421</v>
+      </c>
+      <c r="B422" s="17">
+        <v>46245</v>
+      </c>
+      <c r="C422" t="s">
+        <v>11</v>
+      </c>
+      <c r="D422" t="s">
+        <v>59</v>
+      </c>
+      <c r="E422" s="1">
+        <v>1</v>
+      </c>
+      <c r="F422" t="s">
+        <v>106</v>
+      </c>
+      <c r="H422" s="2">
+        <v>0</v>
+      </c>
+      <c r="I422" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J422">
+        <v>15600</v>
+      </c>
+    </row>
+    <row r="423" spans="1:10">
+      <c r="A423">
+        <v>422</v>
+      </c>
+      <c r="B423" s="17">
+        <v>46245</v>
+      </c>
+      <c r="C423" t="s">
+        <v>11</v>
+      </c>
+      <c r="D423" t="s">
+        <v>59</v>
+      </c>
+      <c r="E423" s="1">
+        <v>1</v>
+      </c>
+      <c r="F423" t="s">
+        <v>95</v>
+      </c>
+      <c r="H423" s="2">
+        <v>4770</v>
+      </c>
+      <c r="I423" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:10">
+      <c r="A424">
+        <v>423</v>
+      </c>
+      <c r="B424" s="17">
+        <v>46246</v>
+      </c>
+      <c r="C424" t="s">
+        <v>11</v>
+      </c>
+      <c r="D424" t="s">
+        <v>59</v>
+      </c>
+      <c r="E424" s="1">
+        <v>1</v>
+      </c>
+      <c r="F424" t="s">
+        <v>105</v>
+      </c>
+      <c r="H424" s="2">
+        <v>8800</v>
+      </c>
+      <c r="I424" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:10">
+      <c r="A425">
+        <v>424</v>
+      </c>
+      <c r="B425" s="17">
+        <v>46246</v>
+      </c>
+      <c r="C425" t="s">
+        <v>11</v>
+      </c>
+      <c r="D425" t="s">
+        <v>59</v>
+      </c>
+      <c r="E425" s="1">
+        <v>1</v>
+      </c>
+      <c r="F425" t="s">
+        <v>105</v>
+      </c>
+      <c r="H425" s="2">
+        <v>10433.85</v>
+      </c>
+      <c r="I425" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10">
+      <c r="A426">
+        <v>425</v>
+      </c>
+      <c r="B426" s="17">
+        <v>46252</v>
+      </c>
+      <c r="C426" t="s">
+        <v>11</v>
+      </c>
+      <c r="D426" t="s">
+        <v>12</v>
+      </c>
+      <c r="E426" s="1">
+        <v>2</v>
+      </c>
+      <c r="F426" t="s">
+        <v>105</v>
+      </c>
+      <c r="H426" s="2">
+        <v>3975.15</v>
+      </c>
+      <c r="I426" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10">
+      <c r="A427">
+        <v>426</v>
+      </c>
+      <c r="B427" s="17">
+        <v>46252</v>
+      </c>
+      <c r="C427" t="s">
+        <v>11</v>
+      </c>
+      <c r="D427" t="s">
+        <v>59</v>
+      </c>
+      <c r="E427" s="1">
+        <v>1</v>
+      </c>
+      <c r="F427" t="s">
+        <v>105</v>
+      </c>
+      <c r="H427" s="2">
+        <v>19200</v>
+      </c>
+      <c r="I427" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:10">
+      <c r="A428">
+        <v>427</v>
+      </c>
+      <c r="B428" s="17">
+        <v>46253</v>
+      </c>
+      <c r="C428" t="s">
+        <v>11</v>
+      </c>
+      <c r="D428" t="s">
+        <v>59</v>
+      </c>
+      <c r="F428" t="s">
+        <v>103</v>
+      </c>
+      <c r="H428" s="2">
+        <v>55067</v>
+      </c>
+      <c r="I428" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:10">
+      <c r="A429">
+        <v>428</v>
+      </c>
+      <c r="B429" s="17">
+        <v>46258</v>
+      </c>
+      <c r="C429" t="s">
+        <v>11</v>
+      </c>
+      <c r="D429" t="s">
+        <v>59</v>
+      </c>
+      <c r="F429" t="s">
+        <v>105</v>
+      </c>
+      <c r="H429" s="2">
+        <v>10360</v>
+      </c>
+      <c r="I429" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10">
+      <c r="A430">
+        <v>429</v>
+      </c>
+      <c r="B430" s="17">
+        <v>46258</v>
+      </c>
+      <c r="C430" t="s">
+        <v>11</v>
+      </c>
+      <c r="D430" t="s">
+        <v>59</v>
+      </c>
+      <c r="F430" t="s">
+        <v>95</v>
+      </c>
+      <c r="H430" s="2">
+        <v>0</v>
+      </c>
+      <c r="I430" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J430">
+        <v>19005</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10">
+      <c r="A431">
+        <v>430</v>
+      </c>
+      <c r="B431" s="17">
+        <v>46258</v>
+      </c>
+      <c r="C431" t="s">
+        <v>11</v>
+      </c>
+      <c r="D431" t="s">
+        <v>59</v>
+      </c>
+      <c r="E431" s="1">
+        <v>1</v>
+      </c>
+      <c r="F431" t="s">
+        <v>95</v>
+      </c>
+      <c r="H431" s="2">
+        <v>0</v>
+      </c>
+      <c r="I431" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J431">
+        <v>36670</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10">
+      <c r="A432">
+        <v>431</v>
+      </c>
+      <c r="B432" s="17">
+        <v>46260</v>
+      </c>
+      <c r="C432" t="s">
+        <v>11</v>
+      </c>
+      <c r="D432" t="s">
+        <v>59</v>
+      </c>
+      <c r="E432" s="1">
+        <v>1</v>
+      </c>
+      <c r="F432" t="s">
+        <v>95</v>
+      </c>
+      <c r="H432" s="2">
+        <v>0</v>
+      </c>
+      <c r="I432" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J432">
+        <v>105990</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10">
+      <c r="A433">
+        <v>432</v>
+      </c>
+      <c r="B433" s="17">
+        <v>46260</v>
+      </c>
+      <c r="C433" t="s">
+        <v>11</v>
+      </c>
+      <c r="D433" t="s">
+        <v>59</v>
+      </c>
+      <c r="E433" s="1">
+        <v>1</v>
+      </c>
+      <c r="F433" t="s">
+        <v>95</v>
+      </c>
+      <c r="H433" s="2">
+        <v>4683</v>
+      </c>
+      <c r="I433" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:10">
+      <c r="A434">
+        <v>433</v>
+      </c>
+      <c r="B434" s="17">
+        <v>46262</v>
+      </c>
+      <c r="C434" t="s">
+        <v>11</v>
+      </c>
+      <c r="D434" t="s">
+        <v>59</v>
+      </c>
+      <c r="F434" t="s">
+        <v>105</v>
+      </c>
+      <c r="H434" s="2">
+        <v>10525</v>
+      </c>
+      <c r="I434" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10">
+      <c r="B435" s="11"/>
+      <c r="H435" s="2">
         <f>SUBTOTAL(109,Tabla1[Peso Neto Exportado2])</f>
-        <v>468798.80800000002</v>
-      </c>
-      <c r="J407">
+        <v>767151.60800000001</v>
+      </c>
+      <c r="J435">
         <f>SUBTOTAL(109,Tabla1[[Peso Neto Importado ]])/1000</f>
-        <v>291.99020000000002</v>
+        <v>514.49394000000007</v>
       </c>
     </row>
   </sheetData>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANGELA\Desktop\MiDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C47432D-B01F-4370-9C04-64D5E84307A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B611CDD5-81AF-43BA-8759-FA67F57FD899}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8805" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -447,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -488,6 +488,16 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -604,11 +614,9 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LLENOS RECIBIDOS (EXPORTADOS)" totalsRowDxfId="3"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CONTENIDO"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Peso Neto Exportado" totalsRowDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Peso Neto Exportado2" totalsRowFunction="sum" totalsRowDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Peso Neto Exportado2" totalsRowDxfId="1"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DESTINO " totalsRowDxfId="0"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Peso Neto Importado " totalsRowFunction="custom">
-      <totalsRowFormula>SUBTOTAL(109,Tabla1[[Peso Neto Importado ]])/1000</totalsRowFormula>
-    </tableColumn>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Peso Neto Importado "/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15151,29 +15159,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:10">
-      <c r="A407">
+    <row r="407" spans="1:10" s="18" customFormat="1">
+      <c r="A407" s="18">
         <v>406</v>
       </c>
-      <c r="B407" s="17">
+      <c r="B407" s="19">
         <v>46203</v>
       </c>
-      <c r="C407" t="s">
-        <v>11</v>
-      </c>
-      <c r="D407" t="s">
+      <c r="C407" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D407" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F407" t="s">
+      <c r="E407" s="20"/>
+      <c r="F407" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="H407" s="2">
-        <v>0</v>
-      </c>
-      <c r="I407" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J407">
+      <c r="G407" s="20"/>
+      <c r="H407" s="21">
+        <v>0</v>
+      </c>
+      <c r="I407" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="J407" s="18">
         <v>15079.58</v>
       </c>
     </row>
@@ -15190,9 +15200,6 @@
       <c r="D408" t="s">
         <v>59</v>
       </c>
-      <c r="E408" s="1">
-        <v>1</v>
-      </c>
       <c r="F408" t="s">
         <v>95</v>
       </c>
@@ -15200,7 +15207,7 @@
         <v>0</v>
       </c>
       <c r="I408" s="1" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="J408">
         <v>15079.58</v>
@@ -15219,17 +15226,20 @@
       <c r="D409" t="s">
         <v>59</v>
       </c>
+      <c r="E409" s="1">
+        <v>1</v>
+      </c>
       <c r="F409" t="s">
         <v>95</v>
       </c>
       <c r="H409" s="2">
-        <v>0</v>
+        <v>10080</v>
       </c>
       <c r="I409" s="1" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="J409">
-        <v>15079.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="410" spans="1:10">
@@ -15245,17 +15255,11 @@
       <c r="D410" t="s">
         <v>12</v>
       </c>
-      <c r="E410" s="1">
-        <v>1</v>
-      </c>
       <c r="F410" t="s">
-        <v>95</v>
-      </c>
-      <c r="H410" s="2">
-        <v>10080</v>
+        <v>106</v>
       </c>
       <c r="I410" s="1" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="J410">
         <v>0</v>
@@ -15278,10 +15282,13 @@
         <v>1</v>
       </c>
       <c r="F411" t="s">
-        <v>95</v>
+        <v>105</v>
+      </c>
+      <c r="H411" s="2">
+        <v>10665</v>
       </c>
       <c r="I411" s="1" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="J411">
         <v>0</v>
@@ -15304,13 +15311,13 @@
         <v>1</v>
       </c>
       <c r="F412" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H412" s="2">
-        <v>10665</v>
+        <v>3308</v>
       </c>
       <c r="I412" s="1" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="J412">
         <v>0</v>
@@ -15336,7 +15343,7 @@
         <v>105</v>
       </c>
       <c r="H413" s="2">
-        <v>3308</v>
+        <v>10665</v>
       </c>
       <c r="I413" s="1" t="s">
         <v>24</v>
@@ -15365,7 +15372,7 @@
         <v>105</v>
       </c>
       <c r="H414" s="2">
-        <v>10665</v>
+        <v>9710.7000000000007</v>
       </c>
       <c r="I414" s="1" t="s">
         <v>24</v>
@@ -15394,7 +15401,7 @@
         <v>105</v>
       </c>
       <c r="H415" s="2">
-        <v>9710.7000000000007</v>
+        <v>4447.1000000000004</v>
       </c>
       <c r="I415" s="1" t="s">
         <v>24</v>
@@ -15420,13 +15427,13 @@
         <v>1</v>
       </c>
       <c r="F416" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H416" s="2">
-        <v>4447.1000000000004</v>
+        <v>24000</v>
       </c>
       <c r="I416" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J416">
         <v>0</v>
@@ -15452,10 +15459,10 @@
         <v>105</v>
       </c>
       <c r="H417" s="2">
-        <v>24000</v>
+        <v>10063</v>
       </c>
       <c r="I417" s="1" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="J417">
         <v>0</v>
@@ -15475,16 +15482,16 @@
         <v>12</v>
       </c>
       <c r="E418" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F418" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H418" s="2">
-        <v>10063</v>
+        <v>19200</v>
       </c>
       <c r="I418" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J418">
         <v>0</v>
@@ -15504,16 +15511,16 @@
         <v>59</v>
       </c>
       <c r="E419" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F419" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H419" s="2">
-        <v>19200</v>
+        <v>43500</v>
       </c>
       <c r="I419" s="1" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="J419">
         <v>0</v>
@@ -15532,11 +15539,14 @@
       <c r="D420" t="s">
         <v>12</v>
       </c>
+      <c r="E420" s="1">
+        <v>1</v>
+      </c>
       <c r="F420" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H420" s="2">
-        <v>43500</v>
+        <v>24900</v>
       </c>
       <c r="I420" s="1" t="s">
         <v>34</v>
@@ -15558,20 +15568,17 @@
       <c r="D421" t="s">
         <v>59</v>
       </c>
-      <c r="E421" s="1">
-        <v>1</v>
-      </c>
       <c r="F421" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="H421" s="2">
-        <v>24900</v>
+        <v>0</v>
       </c>
       <c r="I421" s="1" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="J421">
-        <v>0</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="422" spans="1:10">
@@ -15591,16 +15598,16 @@
         <v>1</v>
       </c>
       <c r="F422" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H422" s="2">
-        <v>0</v>
+        <v>4770</v>
       </c>
       <c r="I422" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J422">
-        <v>15600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="423" spans="1:10">
@@ -15620,13 +15627,13 @@
         <v>1</v>
       </c>
       <c r="F423" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H423" s="2">
-        <v>4770</v>
+        <v>8800</v>
       </c>
       <c r="I423" s="1" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="J423">
         <v>0</v>
@@ -15652,7 +15659,7 @@
         <v>105</v>
       </c>
       <c r="H424" s="2">
-        <v>8800</v>
+        <v>10433.85</v>
       </c>
       <c r="I424" s="1" t="s">
         <v>24</v>
@@ -15681,10 +15688,10 @@
         <v>105</v>
       </c>
       <c r="H425" s="2">
-        <v>10433.85</v>
+        <v>3975.15</v>
       </c>
       <c r="I425" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J425">
         <v>0</v>
@@ -15704,13 +15711,13 @@
         <v>12</v>
       </c>
       <c r="E426" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F426" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H426" s="2">
-        <v>3975.15</v>
+        <v>19200</v>
       </c>
       <c r="I426" s="1" t="s">
         <v>24</v>
@@ -15733,16 +15740,16 @@
         <v>59</v>
       </c>
       <c r="E427" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F427" t="s">
         <v>105</v>
       </c>
       <c r="H427" s="2">
-        <v>19200</v>
+        <v>55067</v>
       </c>
       <c r="I427" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="J427">
         <v>0</v>
@@ -15761,14 +15768,17 @@
       <c r="D428" t="s">
         <v>59</v>
       </c>
+      <c r="E428" s="1">
+        <v>1</v>
+      </c>
       <c r="F428" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="H428" s="2">
-        <v>55067</v>
+        <v>10360</v>
       </c>
       <c r="I428" s="1" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="J428">
         <v>0</v>
@@ -15788,16 +15798,16 @@
         <v>59</v>
       </c>
       <c r="F429" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H429" s="2">
-        <v>10360</v>
+        <v>0</v>
       </c>
       <c r="I429" s="1" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="J429">
-        <v>0</v>
+        <v>19005</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -15820,10 +15830,10 @@
         <v>0</v>
       </c>
       <c r="I430" s="1" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="J430">
-        <v>19005</v>
+        <v>36670</v>
       </c>
     </row>
     <row r="431" spans="1:10">
@@ -15839,9 +15849,6 @@
       <c r="D431" t="s">
         <v>59</v>
       </c>
-      <c r="E431" s="1">
-        <v>1</v>
-      </c>
       <c r="F431" t="s">
         <v>95</v>
       </c>
@@ -15852,7 +15859,7 @@
         <v>89</v>
       </c>
       <c r="J431">
-        <v>36670</v>
+        <v>105990</v>
       </c>
     </row>
     <row r="432" spans="1:10">
@@ -15872,16 +15879,16 @@
         <v>1</v>
       </c>
       <c r="F432" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H432" s="2">
-        <v>0</v>
+        <v>4683</v>
       </c>
       <c r="I432" s="1" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="J432">
-        <v>105990</v>
+        <v>0</v>
       </c>
     </row>
     <row r="433" spans="1:10">
@@ -15901,13 +15908,13 @@
         <v>1</v>
       </c>
       <c r="F433" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H433" s="2">
-        <v>4683</v>
+        <v>10525</v>
       </c>
       <c r="I433" s="1" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="J433">
         <v>0</v>
@@ -15926,14 +15933,17 @@
       <c r="D434" t="s">
         <v>59</v>
       </c>
+      <c r="E434" s="1">
+        <v>1</v>
+      </c>
       <c r="F434" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H434" s="2">
-        <v>10525</v>
+        <v>11140</v>
       </c>
       <c r="I434" s="1" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="J434">
         <v>0</v>
@@ -15941,14 +15951,6 @@
     </row>
     <row r="435" spans="1:10">
       <c r="B435" s="11"/>
-      <c r="H435" s="2">
-        <f>SUBTOTAL(109,Tabla1[Peso Neto Exportado2])</f>
-        <v>767151.60800000001</v>
-      </c>
-      <c r="J435">
-        <f>SUBTOTAL(109,Tabla1[[Peso Neto Importado ]])/1000</f>
-        <v>514.49394000000007</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANGELA\Desktop\MiDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B611CDD5-81AF-43BA-8759-FA67F57FD899}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCCAFFC-025F-4BBE-9039-37A8955EFF04}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8805" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="109">
   <si>
     <t>N° DE OPERACIÓN</t>
   </si>
@@ -604,8 +604,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A1:J435" totalsRowCount="1">
-  <autoFilter ref="A1:J434" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A1:J437" totalsRowCount="1">
+  <autoFilter ref="A1:J436" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="N° DE OPERACIÓN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="FECHA" totalsRowDxfId="4"/>
@@ -798,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K435"/>
+  <dimension ref="A1:K437"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -15950,7 +15950,65 @@
       </c>
     </row>
     <row r="435" spans="1:10">
-      <c r="B435" s="11"/>
+      <c r="A435">
+        <v>434</v>
+      </c>
+      <c r="B435" s="1">
+        <v>46274</v>
+      </c>
+      <c r="C435" t="s">
+        <v>11</v>
+      </c>
+      <c r="D435" t="s">
+        <v>12</v>
+      </c>
+      <c r="E435" s="1">
+        <v>1</v>
+      </c>
+      <c r="F435" t="s">
+        <v>103</v>
+      </c>
+      <c r="H435" s="2">
+        <v>28320</v>
+      </c>
+      <c r="I435" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10">
+      <c r="A436">
+        <v>435</v>
+      </c>
+      <c r="B436" s="1">
+        <v>46275</v>
+      </c>
+      <c r="C436" t="s">
+        <v>11</v>
+      </c>
+      <c r="D436" t="s">
+        <v>59</v>
+      </c>
+      <c r="E436" s="1">
+        <v>1</v>
+      </c>
+      <c r="F436" t="s">
+        <v>105</v>
+      </c>
+      <c r="H436" s="2">
+        <v>8608</v>
+      </c>
+      <c r="I436" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10">
+      <c r="B437" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
